--- a/areas_land_bank_com_id.xlsx
+++ b/areas_land_bank_com_id.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EsteLivro" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Departamento Controladoria\3 - BT 360º\Levantamento Landbank\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.castro\Documents\01 Profissional\Buriti Empreendimentos\Repositórios\land-bank-mapa-brasil-terrenos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B679CB8E-ADE7-46CE-B9BB-0C01C9397E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D12AF5C-8017-48DC-8234-6A6A405B2C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="960" windowWidth="29040" windowHeight="15720" xr2:uid="{2D7381EB-1656-47BB-A82F-14AB3B13CCCD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D7381EB-1656-47BB-A82F-14AB3B13CCCD}"/>
   </bookViews>
   <sheets>
     <sheet name="AREAS" sheetId="1" r:id="rId1"/>
@@ -5306,7 +5306,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="737">
   <si>
     <t>Nome</t>
   </si>
@@ -7519,6 +7519,9 @@
   </si>
   <si>
     <t>CALDAS NOVAS</t>
+  </si>
+  <si>
+    <t>MAP133</t>
   </si>
 </sst>
 </file>
@@ -7526,17 +7529,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="11">
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0%_);\(0.0%\);0.0%_);@_)"/>
-    <numFmt numFmtId="165" formatCode="0.00%_);\(0.00%\);0.00%_);@_)"/>
-    <numFmt numFmtId="166" formatCode="0%_);\(0%\);0%_);@_)"/>
-    <numFmt numFmtId="167" formatCode="[$-416]mmm\-yy;@"/>
-    <numFmt numFmtId="168" formatCode="&quot;Ativo&quot;;\-#,##0;[Red]&quot;Inativo&quot;"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="0.0%"/>
-    <numFmt numFmtId="172" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.0%_);\(0.0%\);0.0%_);@_)"/>
+    <numFmt numFmtId="167" formatCode="0.00%_);\(0.00%\);0.00%_);@_)"/>
+    <numFmt numFmtId="168" formatCode="0%_);\(0%\);0%_);@_)"/>
+    <numFmt numFmtId="169" formatCode="[$-416]mmm\-yy;@"/>
+    <numFmt numFmtId="170" formatCode="&quot;Ativo&quot;;\-#,##0;[Red]&quot;Inativo&quot;"/>
+    <numFmt numFmtId="171" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="173" formatCode="0.0%"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -7858,8 +7861,8 @@
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="121">
@@ -7885,25 +7888,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
@@ -7918,32 +7921,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="3" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -7955,37 +7958,37 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -7998,50 +8001,50 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="6" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="6" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="3" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8071,13 +8074,13 @@
     <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="8" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="8" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8093,7 +8096,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -8101,7 +8104,7 @@
     <xf numFmtId="37" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8124,21 +8127,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8150,7 +8153,7 @@
     <xf numFmtId="10" fontId="11" fillId="3" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8160,16 +8163,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
     <cellStyle name="Moeda" xfId="3" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentagem" xfId="4" builtinId="5"/>
+    <cellStyle name="Percentagem" xfId="4" builtinId="5"/>
     <cellStyle name="Vírgula" xfId="2" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -8190,10 +8193,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8515,49 +8514,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB1E7F9-B7E0-4EE5-A96E-08F27078CA81}">
   <sheetPr codeName="Folha1"/>
   <dimension ref="A1:AP241"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" customWidth="1"/>
-    <col min="2" max="2" width="58.453125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7265625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="22.453125" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.54296875" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" customWidth="1"/>
-    <col min="11" max="11" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.26953125" style="108" customWidth="1"/>
-    <col min="14" max="14" width="53.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.08984375" style="29" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.81640625" customWidth="1"/>
-    <col min="20" max="20" width="11.54296875" customWidth="1"/>
-    <col min="21" max="21" width="11.26953125" customWidth="1"/>
+    <col min="1" max="1" width="15.21875" customWidth="1"/>
+    <col min="2" max="2" width="58.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="22.44140625" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.21875" style="108" customWidth="1"/>
+    <col min="14" max="14" width="53.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.77734375" customWidth="1"/>
+    <col min="20" max="20" width="11.5546875" customWidth="1"/>
+    <col min="21" max="21" width="11.21875" customWidth="1"/>
     <col min="22" max="22" width="14" customWidth="1"/>
-    <col min="23" max="23" width="10.26953125" customWidth="1"/>
-    <col min="24" max="24" width="10.81640625" customWidth="1"/>
-    <col min="25" max="25" width="12.7265625" customWidth="1"/>
+    <col min="23" max="23" width="10.21875" customWidth="1"/>
+    <col min="24" max="24" width="10.77734375" customWidth="1"/>
+    <col min="25" max="25" width="12.77734375" customWidth="1"/>
     <col min="26" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="11.54296875" customWidth="1"/>
-    <col min="28" max="28" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.81640625" customWidth="1"/>
-    <col min="31" max="31" width="11.1796875" customWidth="1"/>
-    <col min="32" max="32" width="12.26953125" customWidth="1"/>
-    <col min="33" max="33" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.54296875" customWidth="1"/>
+    <col min="27" max="27" width="11.5546875" customWidth="1"/>
+    <col min="28" max="28" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.77734375" customWidth="1"/>
+    <col min="31" max="31" width="11.21875" customWidth="1"/>
+    <col min="32" max="32" width="12.21875" customWidth="1"/>
+    <col min="33" max="33" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="9.5546875" customWidth="1"/>
     <col min="37" max="38" width="9" customWidth="1"/>
     <col min="39" max="39" width="16" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="12.81640625" customWidth="1"/>
-    <col min="42" max="42" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="12.77734375" customWidth="1"/>
+    <col min="42" max="42" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="52" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>571</v>
       </c>
@@ -8685,7 +8684,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>579</v>
       </c>
@@ -8804,7 +8803,7 @@
         <v>3.3809797786673061</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>580</v>
       </c>
@@ -8925,7 +8924,7 @@
         <v>4.8097271922736544</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>580</v>
       </c>
@@ -9046,7 +9045,7 @@
         <v>5.3580126643935699</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>581</v>
       </c>
@@ -9165,7 +9164,7 @@
         <v>4.5078888054094666</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>582</v>
       </c>
@@ -9284,7 +9283,7 @@
         <v>4.5078888054094675</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>582</v>
       </c>
@@ -9403,7 +9402,7 @@
         <v>4.5078888054094666</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>582</v>
       </c>
@@ -9522,7 +9521,7 @@
         <v>4.5078888054094683</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>582</v>
       </c>
@@ -9641,7 +9640,7 @@
         <v>4.5078888054094683</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>582</v>
       </c>
@@ -9760,7 +9759,7 @@
         <v>4.5078888054094683</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>573</v>
       </c>
@@ -9877,7 +9876,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>574</v>
       </c>
@@ -9994,7 +9993,7 @@
         <v>3.2306536438767841</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>575</v>
       </c>
@@ -10111,7 +10110,7 @@
         <v>4.883546205860255</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>575</v>
       </c>
@@ -10228,7 +10227,7 @@
         <v>4.883546205860255</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>576</v>
       </c>
@@ -10345,7 +10344,7 @@
         <v>3.7565740045078888</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>577</v>
       </c>
@@ -10462,7 +10461,7 @@
         <v>3.7565740045078897</v>
       </c>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>578</v>
       </c>
@@ -10579,7 +10578,7 @@
         <v>3.7565740045078893</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>583</v>
       </c>
@@ -10696,7 +10695,7 @@
         <v>3.230653643876785</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>584</v>
       </c>
@@ -10813,7 +10812,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>584</v>
       </c>
@@ -10930,7 +10929,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>584</v>
       </c>
@@ -11047,7 +11046,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>584</v>
       </c>
@@ -11164,7 +11163,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>584</v>
       </c>
@@ -11281,7 +11280,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>584</v>
       </c>
@@ -11398,7 +11397,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>584</v>
       </c>
@@ -11515,7 +11514,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>585</v>
       </c>
@@ -11634,7 +11633,7 @@
         <v>0.83115017886351839</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>586</v>
       </c>
@@ -11751,7 +11750,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>586</v>
       </c>
@@ -11867,7 +11866,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>586</v>
       </c>
@@ -11984,7 +11983,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>586</v>
       </c>
@@ -12101,7 +12100,7 @@
         <v>4.140625</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>586</v>
       </c>
@@ -12218,7 +12217,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>586</v>
       </c>
@@ -12335,7 +12334,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>586</v>
       </c>
@@ -12452,7 +12451,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>586</v>
       </c>
@@ -12569,7 +12568,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>586</v>
       </c>
@@ -12686,7 +12685,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>586</v>
       </c>
@@ -12803,7 +12802,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>586</v>
       </c>
@@ -12920,7 +12919,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>586</v>
       </c>
@@ -13037,7 +13036,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>586</v>
       </c>
@@ -13154,7 +13153,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>586</v>
       </c>
@@ -13271,7 +13270,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>586</v>
       </c>
@@ -13388,7 +13387,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>586</v>
       </c>
@@ -13505,7 +13504,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>586</v>
       </c>
@@ -13622,7 +13621,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>586</v>
       </c>
@@ -13739,7 +13738,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>586</v>
       </c>
@@ -13856,7 +13855,7 @@
         <v>3.90625</v>
       </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>587</v>
       </c>
@@ -13979,7 +13978,7 @@
         <v>1.5033333068541384</v>
       </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>587</v>
       </c>
@@ -14102,7 +14101,7 @@
         <v>1.5033333068541381</v>
       </c>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>587</v>
       </c>
@@ -14225,7 +14224,7 @@
         <v>1.1881369949110563</v>
       </c>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>587</v>
       </c>
@@ -14348,7 +14347,7 @@
         <v>1.1629101414416052</v>
       </c>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>588</v>
       </c>
@@ -14464,7 +14463,7 @@
         <v>3.9062500000000004</v>
       </c>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>590</v>
       </c>
@@ -14581,7 +14580,7 @@
         <v>4.6875000000000009</v>
       </c>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>684</v>
       </c>
@@ -14698,7 +14697,7 @@
         <v>3.2407407407407409</v>
       </c>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>589</v>
       </c>
@@ -14815,7 +14814,7 @@
         <v>3.2407407407407409</v>
       </c>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>591</v>
       </c>
@@ -14932,7 +14931,7 @@
         <v>6.2499999999999991</v>
       </c>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>592</v>
       </c>
@@ -15050,7 +15049,7 @@
         <v>3.7037037037037033</v>
       </c>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>594</v>
       </c>
@@ -15175,7 +15174,7 @@
         <v>2.0794444816235882</v>
       </c>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>594</v>
       </c>
@@ -15299,7 +15298,7 @@
         <v>0.682062825375507</v>
       </c>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>593</v>
       </c>
@@ -15422,7 +15421,7 @@
         <v>1.584067227618178</v>
       </c>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>595</v>
       </c>
@@ -15545,7 +15544,7 @@
         <v>1.2626874796242238</v>
       </c>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>596</v>
       </c>
@@ -15668,7 +15667,7 @@
         <v>1.165542478997921</v>
       </c>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>596</v>
       </c>
@@ -15791,7 +15790,7 @@
         <v>1.1453025708336924</v>
       </c>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>597</v>
       </c>
@@ -15914,7 +15913,7 @@
         <v>1.0499523822058021</v>
       </c>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>598</v>
       </c>
@@ -16031,7 +16030,7 @@
         <v>3.9384920139218527</v>
       </c>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>598</v>
       </c>
@@ -16148,7 +16147,7 @@
         <v>3.9384920139218527</v>
       </c>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>598</v>
       </c>
@@ -16265,7 +16264,7 @@
         <v>3.9384920139218527</v>
       </c>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>599</v>
       </c>
@@ -16384,7 +16383,7 @@
         <v>3.5833333333333335</v>
       </c>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>600</v>
       </c>
@@ -16503,7 +16502,7 @@
         <v>3.8333333333333335</v>
       </c>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>601</v>
       </c>
@@ -16622,7 +16621,7 @@
         <v>3.5833333333333335</v>
       </c>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>601</v>
       </c>
@@ -16741,7 +16740,7 @@
         <v>3.5833333333333335</v>
       </c>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>602</v>
       </c>
@@ -16865,7 +16864,7 @@
         <v>1.6840907460634127</v>
       </c>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>603</v>
       </c>
@@ -16989,7 +16988,7 @@
         <v>1.7104564330775569</v>
       </c>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>603</v>
       </c>
@@ -17113,7 +17112,7 @@
         <v>1.6579735962048303</v>
       </c>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>604</v>
       </c>
@@ -17235,7 +17234,7 @@
         <v>2.5287610566591523</v>
       </c>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>604</v>
       </c>
@@ -17357,7 +17356,7 @@
         <v>2.4793535855822042</v>
       </c>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>605</v>
       </c>
@@ -17482,7 +17481,7 @@
         <v>1.890388055872956</v>
       </c>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>605</v>
       </c>
@@ -17607,7 +17606,7 @@
         <v>1.8605083275965164</v>
       </c>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>606</v>
       </c>
@@ -17732,7 +17731,7 @@
         <v>1.8523399895648596</v>
       </c>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>606</v>
       </c>
@@ -17857,7 +17856,7 @@
         <v>1.7669888872138106</v>
       </c>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>607</v>
       </c>
@@ -17980,7 +17979,7 @@
         <v>0.64100515446669049</v>
       </c>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>607</v>
       </c>
@@ -18103,7 +18102,7 @@
         <v>0.62670976763932151</v>
       </c>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>608</v>
       </c>
@@ -18226,7 +18225,7 @@
         <v>0.76883870310314895</v>
       </c>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>609</v>
       </c>
@@ -18349,7 +18348,7 @@
         <v>1.4269848890125221</v>
       </c>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>610</v>
       </c>
@@ -18472,7 +18471,7 @@
         <v>0.83525452781953513</v>
       </c>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>610</v>
       </c>
@@ -18595,7 +18594,7 @@
         <v>0.81799598953212038</v>
       </c>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>610</v>
       </c>
@@ -18718,7 +18717,7 @@
         <v>0.78388138912123639</v>
       </c>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>611</v>
       </c>
@@ -18841,7 +18840,7 @@
         <v>1.1501266268686077</v>
       </c>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>612</v>
       </c>
@@ -18966,7 +18965,7 @@
         <v>0.23299756298435631</v>
       </c>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>612</v>
       </c>
@@ -19091,7 +19090,7 @@
         <v>1.2387943662501089</v>
       </c>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>613</v>
       </c>
@@ -19214,7 +19213,7 @@
         <v>1.5149909654595908</v>
       </c>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>685</v>
       </c>
@@ -19337,7 +19336,7 @@
         <v>1.2046020634661616</v>
       </c>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>614</v>
       </c>
@@ -19460,7 +19459,7 @@
         <v>1.2072988815514583</v>
       </c>
     </row>
-    <row r="92" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>614</v>
       </c>
@@ -19583,7 +19582,7 @@
         <v>1.4090811331942312</v>
       </c>
     </row>
-    <row r="93" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>614</v>
       </c>
@@ -19706,7 +19705,7 @@
         <v>1.1397336017719824</v>
       </c>
     </row>
-    <row r="94" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>614</v>
       </c>
@@ -19829,7 +19828,7 @@
         <v>1.0959959051299162</v>
       </c>
     </row>
-    <row r="95" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>614</v>
       </c>
@@ -19952,7 +19951,7 @@
         <v>1.0527200029561115</v>
       </c>
     </row>
-    <row r="96" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>615</v>
       </c>
@@ -20077,7 +20076,7 @@
         <v>2.1202973983797322</v>
       </c>
     </row>
-    <row r="97" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>616</v>
       </c>
@@ -20202,7 +20201,7 @@
         <v>2.0772596632135061</v>
       </c>
     </row>
-    <row r="98" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>618</v>
       </c>
@@ -20325,7 +20324,7 @@
         <v>1.5361651825388483</v>
       </c>
     </row>
-    <row r="99" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>618</v>
       </c>
@@ -20448,7 +20447,7 @@
         <v>1.5065784699927574</v>
       </c>
     </row>
-    <row r="100" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>618</v>
       </c>
@@ -20571,7 +20570,7 @@
         <v>1.4478450040383797</v>
       </c>
     </row>
-    <row r="101" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>617</v>
       </c>
@@ -20694,7 +20693,7 @@
         <v>1.0994472988394468</v>
       </c>
     </row>
-    <row r="102" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>617</v>
       </c>
@@ -20817,7 +20816,7 @@
         <v>1.0586916755795146</v>
       </c>
     </row>
-    <row r="103" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>619</v>
       </c>
@@ -20940,7 +20939,7 @@
         <v>1.6691380981214541</v>
       </c>
     </row>
-    <row r="104" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>619</v>
       </c>
@@ -21063,7 +21062,7 @@
         <v>1.6065963825333243</v>
       </c>
     </row>
-    <row r="105" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>620</v>
       </c>
@@ -21186,7 +21185,7 @@
         <v>0.90690345120653837</v>
       </c>
     </row>
-    <row r="106" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>621</v>
       </c>
@@ -21309,7 +21308,7 @@
         <v>0.87259450365707092</v>
       </c>
     </row>
-    <row r="107" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>622</v>
       </c>
@@ -21432,7 +21431,7 @@
         <v>0.83860953776262182</v>
       </c>
     </row>
-    <row r="108" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>622</v>
       </c>
@@ -21555,7 +21554,7 @@
         <v>0.80502313984963059</v>
       </c>
     </row>
-    <row r="109" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>622</v>
       </c>
@@ -21678,7 +21677,7 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="110" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>622</v>
       </c>
@@ -21801,7 +21800,7 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="111" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>622</v>
       </c>
@@ -21924,7 +21923,7 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="112" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>622</v>
       </c>
@@ -22047,7 +22046,7 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="113" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>622</v>
       </c>
@@ -22170,7 +22169,7 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="114" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>623</v>
       </c>
@@ -22293,7 +22292,7 @@
         <v>0.73245167478536033</v>
       </c>
     </row>
-    <row r="115" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>624</v>
       </c>
@@ -22416,7 +22415,7 @@
         <v>0.70127185350915722</v>
       </c>
     </row>
-    <row r="116" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>624</v>
       </c>
@@ -22539,7 +22538,7 @@
         <v>0.6706877524292354</v>
       </c>
     </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>624</v>
       </c>
@@ -22662,7 +22661,7 @@
         <v>0.64075267145675929</v>
       </c>
     </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>624</v>
       </c>
@@ -22785,7 +22784,7 @@
         <v>0.61151467271213211</v>
       </c>
     </row>
-    <row r="119" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>624</v>
       </c>
@@ -22908,7 +22907,7 @@
         <v>1.9492775508164899</v>
       </c>
     </row>
-    <row r="120" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>625</v>
       </c>
@@ -23031,7 +23030,7 @@
         <v>1.2292115404911319</v>
       </c>
     </row>
-    <row r="121" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>626</v>
       </c>
@@ -23154,7 +23153,7 @@
         <v>1.2413630323963301</v>
       </c>
     </row>
-    <row r="122" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>627</v>
       </c>
@@ -23277,7 +23276,7 @@
         <v>1.2561653093904881</v>
       </c>
     </row>
-    <row r="123" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>628</v>
       </c>
@@ -23400,7 +23399,7 @@
         <v>1.2113560025023844</v>
       </c>
     </row>
-    <row r="124" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>629</v>
       </c>
@@ -23523,7 +23522,7 @@
         <v>2.613496932515337</v>
       </c>
     </row>
-    <row r="125" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>629</v>
       </c>
@@ -23646,7 +23645,7 @@
         <v>2.6134969325153379</v>
       </c>
     </row>
-    <row r="126" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>630</v>
       </c>
@@ -23769,7 +23768,7 @@
         <v>1.3821716627734322</v>
       </c>
     </row>
-    <row r="127" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>631</v>
       </c>
@@ -23892,7 +23891,7 @@
         <v>1.3508286832235206</v>
       </c>
     </row>
-    <row r="128" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>631</v>
       </c>
@@ -24015,7 +24014,7 @@
         <v>1.3273996567144928</v>
       </c>
     </row>
-    <row r="129" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>632</v>
       </c>
@@ -24138,7 +24137,7 @@
         <v>1.1478379123898736</v>
       </c>
     </row>
-    <row r="130" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>633</v>
       </c>
@@ -24261,7 +24260,7 @@
         <v>1.1873209657838852</v>
       </c>
     </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>633</v>
       </c>
@@ -24384,7 +24383,7 @@
         <v>1.1478379123898732</v>
       </c>
     </row>
-    <row r="132" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>634</v>
       </c>
@@ -24507,7 +24506,7 @@
         <v>1.1697737528257561</v>
       </c>
     </row>
-    <row r="133" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>635</v>
       </c>
@@ -24630,7 +24629,7 @@
         <v>1.1478379123898734</v>
       </c>
     </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>636</v>
       </c>
@@ -24753,7 +24752,7 @@
         <v>1.1917791466511929</v>
       </c>
     </row>
-    <row r="135" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>636</v>
       </c>
@@ -24876,7 +24875,7 @@
         <v>1.1697737528257561</v>
       </c>
     </row>
-    <row r="136" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>636</v>
       </c>
@@ -24999,7 +24998,7 @@
         <v>1.1478379123898732</v>
       </c>
     </row>
-    <row r="137" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>637</v>
       </c>
@@ -25121,7 +25120,7 @@
         <v>1.100201380402013</v>
       </c>
     </row>
-    <row r="138" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>637</v>
       </c>
@@ -25238,7 +25237,7 @@
         <v>3.4285714285714284</v>
       </c>
     </row>
-    <row r="139" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>637</v>
       </c>
@@ -25360,7 +25359,7 @@
         <v>1.5534532233799874</v>
       </c>
     </row>
-    <row r="140" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>637</v>
       </c>
@@ -25477,7 +25476,7 @@
         <v>3.4285714285714284</v>
       </c>
     </row>
-    <row r="141" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>638</v>
       </c>
@@ -25600,7 +25599,7 @@
         <v>1.3402722285622568</v>
       </c>
     </row>
-    <row r="142" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>638</v>
       </c>
@@ -25723,7 +25722,7 @@
         <v>1.1069472501692708</v>
       </c>
     </row>
-    <row r="143" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>638</v>
       </c>
@@ -25846,7 +25845,7 @@
         <v>1.3096934841312509</v>
       </c>
     </row>
-    <row r="144" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>639</v>
       </c>
@@ -25969,7 +25968,7 @@
         <v>1.2649802836537249</v>
       </c>
     </row>
-    <row r="145" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>640</v>
       </c>
@@ -26092,7 +26091,7 @@
         <v>1.242648133063637</v>
       </c>
     </row>
-    <row r="146" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>641</v>
       </c>
@@ -26215,7 +26214,7 @@
         <v>0.90074899958421728</v>
       </c>
     </row>
-    <row r="147" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>641</v>
       </c>
@@ -26338,7 +26337,7 @@
         <v>0.86471997316517379</v>
       </c>
     </row>
-    <row r="148" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>641</v>
       </c>
@@ -26461,7 +26460,7 @@
         <v>0.8291908931927453</v>
       </c>
     </row>
-    <row r="149" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>641</v>
       </c>
@@ -26584,7 +26583,7 @@
         <v>0.82391222601076908</v>
       </c>
     </row>
-    <row r="150" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>641</v>
       </c>
@@ -26707,7 +26706,7 @@
         <v>1.307592918802565</v>
       </c>
     </row>
-    <row r="151" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>641</v>
       </c>
@@ -26830,7 +26829,7 @@
         <v>1.259710619839457</v>
       </c>
     </row>
-    <row r="152" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>641</v>
       </c>
@@ -26947,7 +26946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>641</v>
       </c>
@@ -27070,7 +27069,7 @@
         <v>1.5199940748831153</v>
       </c>
     </row>
-    <row r="154" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>641</v>
       </c>
@@ -27193,7 +27192,7 @@
         <v>0.94841385595929528</v>
       </c>
     </row>
-    <row r="155" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>642</v>
       </c>
@@ -27316,7 +27315,7 @@
         <v>2.001711919813113</v>
       </c>
     </row>
-    <row r="156" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>642</v>
       </c>
@@ -27439,7 +27438,7 @@
         <v>2.7873981870831179</v>
       </c>
     </row>
-    <row r="157" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>642</v>
       </c>
@@ -27562,7 +27561,7 @@
         <v>1.8835744163813872</v>
       </c>
     </row>
-    <row r="158" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>687</v>
       </c>
@@ -27685,7 +27684,7 @@
         <v>1.3178084967631456</v>
       </c>
     </row>
-    <row r="159" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>686</v>
       </c>
@@ -27808,7 +27807,7 @@
         <v>1.3730404099510281</v>
       </c>
     </row>
-    <row r="160" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>643</v>
       </c>
@@ -27931,7 +27930,7 @@
         <v>1.3848749369337743</v>
       </c>
     </row>
-    <row r="161" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>644</v>
       </c>
@@ -28054,7 +28053,7 @@
         <v>1.3585676614027813</v>
       </c>
     </row>
-    <row r="162" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>645</v>
       </c>
@@ -28177,7 +28176,7 @@
         <v>1.372740519264412</v>
       </c>
     </row>
-    <row r="163" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>646</v>
       </c>
@@ -28300,7 +28299,7 @@
         <v>1.3209122633460484</v>
       </c>
     </row>
-    <row r="164" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>647</v>
       </c>
@@ -28423,7 +28422,7 @@
         <v>4.2857142857142856</v>
       </c>
     </row>
-    <row r="165" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>648</v>
       </c>
@@ -28546,7 +28545,7 @@
         <v>0.89768559755339483</v>
       </c>
     </row>
-    <row r="166" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>649</v>
       </c>
@@ -28669,7 +28668,7 @@
         <v>0.84488056240319498</v>
       </c>
     </row>
-    <row r="167" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>650</v>
       </c>
@@ -28792,7 +28791,7 @@
         <v>0.79115858344502654</v>
       </c>
     </row>
-    <row r="168" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>651</v>
       </c>
@@ -28915,7 +28914,7 @@
         <v>0.77406888933587614</v>
       </c>
     </row>
-    <row r="169" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>652</v>
       </c>
@@ -29038,7 +29037,7 @@
         <v>0.95007407159306967</v>
       </c>
     </row>
-    <row r="170" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>653</v>
       </c>
@@ -29161,7 +29160,7 @@
         <v>1.6504684110205614</v>
       </c>
     </row>
-    <row r="171" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>653</v>
       </c>
@@ -29284,7 +29283,7 @@
         <v>1.5959766651655141</v>
       </c>
     </row>
-    <row r="172" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>653</v>
       </c>
@@ -29407,7 +29406,7 @@
         <v>1.541459129098488</v>
       </c>
     </row>
-    <row r="173" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>653</v>
       </c>
@@ -29530,7 +29529,7 @@
         <v>1.4870446603133847</v>
       </c>
     </row>
-    <row r="174" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>654</v>
       </c>
@@ -29653,7 +29652,7 @@
         <v>1.29803634535601</v>
       </c>
     </row>
-    <row r="175" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>655</v>
       </c>
@@ -29776,7 +29775,7 @@
         <v>1.2979593269679877</v>
       </c>
     </row>
-    <row r="176" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>656</v>
       </c>
@@ -29899,7 +29898,7 @@
         <v>1.6263477020219728</v>
       </c>
     </row>
-    <row r="177" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>657</v>
       </c>
@@ -30022,7 +30021,7 @@
         <v>1.2592386722239013</v>
       </c>
     </row>
-    <row r="178" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>658</v>
       </c>
@@ -30145,7 +30144,7 @@
         <v>1.4641218723147973</v>
       </c>
     </row>
-    <row r="179" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>659</v>
       </c>
@@ -30268,7 +30267,7 @@
         <v>1.6857797571068185</v>
       </c>
     </row>
-    <row r="180" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>659</v>
       </c>
@@ -30391,7 +30390,7 @@
         <v>1.6461735009491525</v>
       </c>
     </row>
-    <row r="181" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>660</v>
       </c>
@@ -30514,7 +30513,7 @@
         <v>1.5931435361112869</v>
       </c>
     </row>
-    <row r="182" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>661</v>
       </c>
@@ -30637,7 +30636,7 @@
         <v>1.4757143571699876</v>
       </c>
     </row>
-    <row r="183" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>661</v>
       </c>
@@ -30760,7 +30759,7 @@
         <v>1.4374300869105257</v>
       </c>
     </row>
-    <row r="184" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>661</v>
       </c>
@@ -30883,7 +30882,7 @@
         <v>1.3985631033192503</v>
       </c>
     </row>
-    <row r="185" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>662</v>
       </c>
@@ -31006,7 +31005,7 @@
         <v>1.3826456374022646</v>
       </c>
     </row>
-    <row r="186" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>663</v>
       </c>
@@ -31129,7 +31128,7 @@
         <v>0.47357002940963111</v>
       </c>
     </row>
-    <row r="187" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>664</v>
       </c>
@@ -31252,7 +31251,7 @@
         <v>1.2597354394053424</v>
       </c>
     </row>
-    <row r="188" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>665</v>
       </c>
@@ -31375,7 +31374,7 @@
         <v>1.1675517449568096</v>
       </c>
     </row>
-    <row r="189" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>666</v>
       </c>
@@ -31498,7 +31497,7 @@
         <v>1.3696411756979359</v>
       </c>
     </row>
-    <row r="190" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>666</v>
       </c>
@@ -31621,7 +31620,7 @@
         <v>1.350214188462304</v>
       </c>
     </row>
-    <row r="191" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>667</v>
       </c>
@@ -31744,7 +31743,7 @@
         <v>1.2329454023052526</v>
       </c>
     </row>
-    <row r="192" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>667</v>
       </c>
@@ -31867,7 +31866,7 @@
         <v>1.1957801977735603</v>
       </c>
     </row>
-    <row r="193" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>668</v>
       </c>
@@ -31990,7 +31989,7 @@
         <v>1.1035853568830785</v>
       </c>
     </row>
-    <row r="194" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>668</v>
       </c>
@@ -32113,7 +32112,7 @@
         <v>1.0659650406849812</v>
       </c>
     </row>
-    <row r="195" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>668</v>
       </c>
@@ -32236,7 +32235,7 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="196" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>668</v>
       </c>
@@ -32359,7 +32358,7 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="197" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>668</v>
       </c>
@@ -32482,7 +32481,7 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="198" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>668</v>
       </c>
@@ -32605,7 +32604,7 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="199" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>668</v>
       </c>
@@ -32728,7 +32727,7 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="200" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>668</v>
       </c>
@@ -32851,7 +32850,7 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="201" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>669</v>
       </c>
@@ -32973,7 +32972,7 @@
         <v>1.6566885721095854</v>
       </c>
     </row>
-    <row r="202" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>669</v>
       </c>
@@ -33095,7 +33094,7 @@
         <v>1.6346161037144891</v>
       </c>
     </row>
-    <row r="203" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>670</v>
       </c>
@@ -33217,7 +33216,7 @@
         <v>1.5890770411330262</v>
       </c>
     </row>
-    <row r="204" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>671</v>
       </c>
@@ -33340,7 +33339,7 @@
         <v>1.6348488056211639</v>
       </c>
     </row>
-    <row r="205" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>672</v>
       </c>
@@ -33463,7 +33462,7 @@
         <v>1.3994784856987472</v>
       </c>
     </row>
-    <row r="206" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>672</v>
       </c>
@@ -33586,7 +33585,7 @@
         <v>1.3761547970799959</v>
       </c>
     </row>
-    <row r="207" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>673</v>
       </c>
@@ -33709,7 +33708,7 @@
         <v>1.2739382867033264</v>
       </c>
     </row>
-    <row r="208" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>673</v>
       </c>
@@ -33832,7 +33831,7 @@
         <v>1.2513432560545719</v>
       </c>
     </row>
-    <row r="209" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>673</v>
       </c>
@@ -33955,7 +33954,7 @@
         <v>1.2287862611479596</v>
       </c>
     </row>
-    <row r="210" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>673</v>
       </c>
@@ -34078,7 +34077,7 @@
         <v>1.1838391039622553</v>
       </c>
     </row>
-    <row r="211" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>674</v>
       </c>
@@ -34201,7 +34200,7 @@
         <v>1.3995973831143944</v>
       </c>
     </row>
-    <row r="212" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>674</v>
       </c>
@@ -34324,7 +34323,7 @@
         <v>1.4269474786562346</v>
       </c>
     </row>
-    <row r="213" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>675</v>
       </c>
@@ -34447,7 +34446,7 @@
         <v>1.4544075393871425</v>
       </c>
     </row>
-    <row r="214" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>676</v>
       </c>
@@ -34570,7 +34569,7 @@
         <v>1.1915152802141717</v>
       </c>
     </row>
-    <row r="215" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>677</v>
       </c>
@@ -34692,7 +34691,7 @@
         <v>1.3027775635825822</v>
       </c>
     </row>
-    <row r="216" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>678</v>
       </c>
@@ -34814,7 +34813,7 @@
         <v>0.81407876134588997</v>
       </c>
     </row>
-    <row r="217" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>679</v>
       </c>
@@ -34936,7 +34935,7 @@
         <v>1.1216996276148128</v>
       </c>
     </row>
-    <row r="218" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>680</v>
       </c>
@@ -35059,7 +35058,7 @@
         <v>1.1919024331549293</v>
       </c>
     </row>
-    <row r="219" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>681</v>
       </c>
@@ -35184,7 +35183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>572</v>
       </c>
@@ -35309,7 +35308,7 @@
         <v>1.4778743985473446</v>
       </c>
     </row>
-    <row r="221" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>572</v>
       </c>
@@ -35434,7 +35433,7 @@
         <v>1.4352282729652679</v>
       </c>
     </row>
-    <row r="222" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>682</v>
       </c>
@@ -35551,7 +35550,7 @@
         <v>2.6923076923076925</v>
       </c>
     </row>
-    <row r="223" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>683</v>
       </c>
@@ -35668,7 +35667,7 @@
         <v>3.378378378378379</v>
       </c>
     </row>
-    <row r="224" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>683</v>
       </c>
@@ -35785,7 +35784,7 @@
         <v>3.378378378378379</v>
       </c>
     </row>
-    <row r="225" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>683</v>
       </c>
@@ -35902,7 +35901,7 @@
         <v>3.3783783783783781</v>
       </c>
     </row>
-    <row r="226" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>683</v>
       </c>
@@ -36019,7 +36018,7 @@
         <v>3.3783783783783781</v>
       </c>
     </row>
-    <row r="227" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>683</v>
       </c>
@@ -36136,7 +36135,7 @@
         <v>3.3783783783783781</v>
       </c>
     </row>
-    <row r="228" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>683</v>
       </c>
@@ -36253,7 +36252,7 @@
         <v>3.3783783783783785</v>
       </c>
     </row>
-    <row r="229" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>683</v>
       </c>
@@ -36370,7 +36369,7 @@
         <v>3.3783783783783781</v>
       </c>
     </row>
-    <row r="230" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>683</v>
       </c>
@@ -36487,7 +36486,7 @@
         <v>3.3783783783783785</v>
       </c>
     </row>
-    <row r="231" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A231" s="98" t="s">
         <v>723</v>
       </c>
@@ -36592,7 +36591,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="232" spans="1:42" s="29" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:42" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A232" s="101" t="s">
         <v>724</v>
       </c>
@@ -36693,7 +36692,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="233" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>732</v>
       </c>
@@ -36796,7 +36795,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="234" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A234" s="98" t="s">
         <v>725</v>
       </c>
@@ -36898,7 +36897,7 @@
         <v>2.2839969947407965</v>
       </c>
     </row>
-    <row r="235" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A235" s="98" t="s">
         <v>726</v>
       </c>
@@ -36998,7 +36997,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="236" spans="1:42" s="81" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:42" s="81" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A236" s="98" t="s">
         <v>727</v>
       </c>
@@ -37098,7 +37097,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="237" spans="1:42" s="81" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:42" s="81" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A237" s="98" t="s">
         <v>728</v>
       </c>
@@ -37198,7 +37197,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="238" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A238" s="98" t="s">
         <v>729</v>
       </c>
@@ -37298,7 +37297,7 @@
         <v>3.2456799398948157</v>
       </c>
     </row>
-    <row r="239" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A239" s="98" t="s">
         <v>730</v>
       </c>
@@ -37398,7 +37397,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="240" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A240" s="98" t="s">
         <v>731</v>
       </c>
@@ -37496,9 +37495,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="241" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B241" s="72" t="s">
         <v>734</v>
@@ -37863,9 +37862,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA5B41D-754B-41F4-AE3E-2CEADDCF305E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>571</v>
       </c>

--- a/areas_land_bank_com_id.xlsx
+++ b/areas_land_bank_com_id.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EsteLivro" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.castro\Documents\01 Profissional\Buriti Empreendimentos\Repositórios\land-bank-mapa-brasil-terrenos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Departamento Controladoria\3 - BT 360º\Levantamento Landbank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D12AF5C-8017-48DC-8234-6A6A405B2C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DF66E9-7659-4B7A-BEF2-B442B06772FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D7381EB-1656-47BB-A82F-14AB3B13CCCD}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{2D7381EB-1656-47BB-A82F-14AB3B13CCCD}"/>
   </bookViews>
   <sheets>
     <sheet name="AREAS" sheetId="1" r:id="rId1"/>
@@ -5306,7 +5306,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="738">
   <si>
     <t>Nome</t>
   </si>
@@ -6069,9 +6069,6 @@
     <t>CENTRO OESTE</t>
   </si>
   <si>
-    <t>BELA VISTA</t>
-  </si>
-  <si>
     <t>CIDADE JARDIM - ETP I</t>
   </si>
   <si>
@@ -7522,6 +7519,12 @@
   </si>
   <si>
     <t>MAP133</t>
+  </si>
+  <si>
+    <t>Inativo</t>
+  </si>
+  <si>
+    <t>BELA VISTA DE GOIÁS</t>
   </si>
 </sst>
 </file>
@@ -7529,19 +7532,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="11">
-    <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="0.0%_);\(0.0%\);0.0%_);@_)"/>
-    <numFmt numFmtId="167" formatCode="0.00%_);\(0.00%\);0.00%_);@_)"/>
-    <numFmt numFmtId="168" formatCode="0%_);\(0%\);0%_);@_)"/>
-    <numFmt numFmtId="169" formatCode="[$-416]mmm\-yy;@"/>
-    <numFmt numFmtId="170" formatCode="&quot;Ativo&quot;;\-#,##0;[Red]&quot;Inativo&quot;"/>
-    <numFmt numFmtId="171" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="0.0%"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0%_);\(0.0%\);0.0%_);@_)"/>
+    <numFmt numFmtId="165" formatCode="0.00%_);\(0.00%\);0.00%_);@_)"/>
+    <numFmt numFmtId="166" formatCode="0%_);\(0%\);0%_);@_)"/>
+    <numFmt numFmtId="167" formatCode="[$-416]mmm\-yy;@"/>
+    <numFmt numFmtId="168" formatCode="&quot;Ativo&quot;;\-#,##0;[Red]&quot;Inativo&quot;"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="0.0%"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7637,6 +7640,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -7861,11 +7870,11 @@
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7888,25 +7897,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
@@ -7921,32 +7930,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -7958,37 +7967,37 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -8001,50 +8010,50 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="6" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="6" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8074,13 +8083,13 @@
     <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="8" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="8" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8096,7 +8105,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -8104,7 +8113,7 @@
     <xf numFmtId="37" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8127,21 +8136,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="11" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8153,7 +8162,7 @@
     <xf numFmtId="10" fontId="11" fillId="3" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8163,16 +8172,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Moeda" xfId="3" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percentagem" xfId="4" builtinId="5"/>
+    <cellStyle name="Porcentagem" xfId="4" builtinId="5"/>
     <cellStyle name="Vírgula" xfId="2" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -8193,6 +8205,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8514,78 +8530,78 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB1E7F9-B7E0-4EE5-A96E-08F27078CA81}">
   <sheetPr codeName="Folha1"/>
   <dimension ref="A1:AP241"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.21875" customWidth="1"/>
-    <col min="2" max="2" width="58.44140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="22.44140625" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.5546875" customWidth="1"/>
-    <col min="10" max="10" width="11.77734375" customWidth="1"/>
-    <col min="11" max="11" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.21875" style="108" customWidth="1"/>
-    <col min="14" max="14" width="53.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.109375" style="29" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.21875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.77734375" customWidth="1"/>
-    <col min="20" max="20" width="11.5546875" customWidth="1"/>
-    <col min="21" max="21" width="11.21875" customWidth="1"/>
+    <col min="1" max="1" width="15.26953125" customWidth="1"/>
+    <col min="2" max="2" width="58.453125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="22.453125" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.54296875" customWidth="1"/>
+    <col min="10" max="10" width="11.81640625" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.26953125" style="108" customWidth="1"/>
+    <col min="14" max="14" width="53.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.08984375" style="29" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.81640625" customWidth="1"/>
+    <col min="20" max="20" width="11.54296875" customWidth="1"/>
+    <col min="21" max="21" width="11.26953125" customWidth="1"/>
     <col min="22" max="22" width="14" customWidth="1"/>
-    <col min="23" max="23" width="10.21875" customWidth="1"/>
-    <col min="24" max="24" width="10.77734375" customWidth="1"/>
-    <col min="25" max="25" width="12.77734375" customWidth="1"/>
+    <col min="23" max="23" width="10.26953125" customWidth="1"/>
+    <col min="24" max="24" width="10.81640625" customWidth="1"/>
+    <col min="25" max="25" width="12.7265625" customWidth="1"/>
     <col min="26" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="11.5546875" customWidth="1"/>
-    <col min="28" max="28" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.77734375" customWidth="1"/>
-    <col min="31" max="31" width="11.21875" customWidth="1"/>
-    <col min="32" max="32" width="12.21875" customWidth="1"/>
-    <col min="33" max="33" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.5546875" customWidth="1"/>
+    <col min="27" max="27" width="11.54296875" customWidth="1"/>
+    <col min="28" max="28" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.81640625" customWidth="1"/>
+    <col min="31" max="31" width="11.1796875" customWidth="1"/>
+    <col min="32" max="32" width="12.26953125" customWidth="1"/>
+    <col min="33" max="33" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="9.54296875" customWidth="1"/>
     <col min="37" max="38" width="9" customWidth="1"/>
     <col min="39" max="39" width="16" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="12.77734375" customWidth="1"/>
-    <col min="42" max="42" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="12.81640625" customWidth="1"/>
+    <col min="42" max="42" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" ht="52" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>696</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>2</v>
@@ -8594,13 +8610,13 @@
         <v>3</v>
       </c>
       <c r="M1" s="103" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>5</v>
@@ -8639,10 +8655,10 @@
         <v>16</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AD1" s="21" t="s">
         <v>17</v>
@@ -8654,7 +8670,7 @@
         <v>19</v>
       </c>
       <c r="AG1" s="21" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AH1" s="21" t="s">
         <v>20</v>
@@ -8663,7 +8679,7 @@
         <v>21</v>
       </c>
       <c r="AJ1" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AK1" s="2" t="s">
         <v>22</v>
@@ -8672,30 +8688,30 @@
         <v>23</v>
       </c>
       <c r="AM1" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="AN1" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="AN1" s="2" t="s">
-        <v>694</v>
-      </c>
       <c r="AO1" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AP1" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E2" s="19">
         <v>0</v>
@@ -8720,7 +8736,7 @@
         <v>26</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P2" s="6" t="s">
         <v>27</v>
@@ -8803,18 +8819,18 @@
         <v>3.3809797786673061</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E3" s="19">
         <v>1</v>
@@ -8841,7 +8857,7 @@
         <v>30</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P3" s="6" t="s">
         <v>27</v>
@@ -8924,18 +8940,18 @@
         <v>4.8097271922736544</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E4" s="19">
         <v>1</v>
@@ -8962,7 +8978,7 @@
         <v>31</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P4" s="6" t="s">
         <v>27</v>
@@ -9045,18 +9061,18 @@
         <v>5.3580126643935699</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E5" s="19">
         <v>1</v>
@@ -9081,7 +9097,7 @@
         <v>33</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P5" s="6" t="s">
         <v>27</v>
@@ -9164,18 +9180,18 @@
         <v>4.5078888054094666</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E6" s="19">
         <v>0</v>
@@ -9200,7 +9216,7 @@
         <v>34</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P6" s="6" t="s">
         <v>27</v>
@@ -9283,18 +9299,18 @@
         <v>4.5078888054094675</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E7" s="19">
         <v>0</v>
@@ -9319,7 +9335,7 @@
         <v>35</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P7" s="6" t="s">
         <v>27</v>
@@ -9402,18 +9418,18 @@
         <v>4.5078888054094666</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E8" s="19">
         <v>0</v>
@@ -9438,7 +9454,7 @@
         <v>36</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P8" s="6" t="s">
         <v>27</v>
@@ -9521,18 +9537,18 @@
         <v>4.5078888054094683</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E9" s="19">
         <v>0</v>
@@ -9557,7 +9573,7 @@
         <v>37</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>27</v>
@@ -9640,18 +9656,18 @@
         <v>4.5078888054094683</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E10" s="19">
         <v>0</v>
@@ -9676,7 +9692,7 @@
         <v>38</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>27</v>
@@ -9759,18 +9775,18 @@
         <v>4.5078888054094683</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E11" s="19">
         <v>1</v>
@@ -9793,7 +9809,7 @@
         <v>40</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>27</v>
@@ -9876,18 +9892,18 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E12" s="19">
         <v>1</v>
@@ -9910,7 +9926,7 @@
         <v>41</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>27</v>
@@ -9993,18 +10009,18 @@
         <v>3.2306536438767841</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E13" s="19">
         <v>1</v>
@@ -10027,7 +10043,7 @@
         <v>43</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P13" s="6" t="s">
         <v>27</v>
@@ -10110,18 +10126,18 @@
         <v>4.883546205860255</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E14" s="19">
         <v>1</v>
@@ -10144,7 +10160,7 @@
         <v>44</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>27</v>
@@ -10227,18 +10243,18 @@
         <v>4.883546205860255</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E15" s="19">
         <v>1</v>
@@ -10261,7 +10277,7 @@
         <v>31</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>27</v>
@@ -10344,18 +10360,18 @@
         <v>3.7565740045078888</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E16" s="19">
         <v>1</v>
@@ -10378,7 +10394,7 @@
         <v>45</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>27</v>
@@ -10461,18 +10477,18 @@
         <v>3.7565740045078897</v>
       </c>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E17" s="19">
         <v>1</v>
@@ -10495,7 +10511,7 @@
         <v>46</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>27</v>
@@ -10578,18 +10594,18 @@
         <v>3.7565740045078893</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E18" s="19">
         <v>1</v>
@@ -10612,7 +10628,7 @@
         <v>48</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>27</v>
@@ -10695,18 +10711,18 @@
         <v>3.230653643876785</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E19" s="19">
         <v>1</v>
@@ -10729,7 +10745,7 @@
         <v>50</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P19" s="6" t="s">
         <v>27</v>
@@ -10812,18 +10828,18 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E20" s="19">
         <v>1</v>
@@ -10846,7 +10862,7 @@
         <v>51</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>27</v>
@@ -10929,18 +10945,18 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E21" s="19">
         <v>1</v>
@@ -10963,7 +10979,7 @@
         <v>52</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>27</v>
@@ -11046,18 +11062,18 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E22" s="19">
         <v>1</v>
@@ -11080,7 +11096,7 @@
         <v>53</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>27</v>
@@ -11163,18 +11179,18 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E23" s="19">
         <v>1</v>
@@ -11197,7 +11213,7 @@
         <v>54</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P23" s="6" t="s">
         <v>27</v>
@@ -11280,18 +11296,18 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E24" s="19">
         <v>1</v>
@@ -11314,7 +11330,7 @@
         <v>55</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>27</v>
@@ -11397,18 +11413,18 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E25" s="19">
         <v>1</v>
@@ -11431,7 +11447,7 @@
         <v>56</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>27</v>
@@ -11514,18 +11530,18 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E26" s="19">
         <v>1</v>
@@ -11550,7 +11566,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>27</v>
@@ -11633,18 +11649,18 @@
         <v>0.83115017886351839</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E27" s="19">
         <v>1</v>
@@ -11667,7 +11683,7 @@
         <v>60</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>27</v>
@@ -11750,18 +11766,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E28" s="19">
         <v>1</v>
@@ -11784,7 +11800,7 @@
         <v>61</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>27</v>
@@ -11866,18 +11882,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E29" s="19">
         <v>1</v>
@@ -11900,7 +11916,7 @@
         <v>62</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>27</v>
@@ -11983,18 +11999,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E30" s="19">
         <v>1</v>
@@ -12017,7 +12033,7 @@
         <v>63</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>27</v>
@@ -12100,18 +12116,18 @@
         <v>4.140625</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E31" s="19">
         <v>1</v>
@@ -12134,7 +12150,7 @@
         <v>64</v>
       </c>
       <c r="O31" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P31" s="6" t="s">
         <v>27</v>
@@ -12217,18 +12233,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E32" s="19">
         <v>1</v>
@@ -12251,7 +12267,7 @@
         <v>65</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>27</v>
@@ -12334,18 +12350,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E33" s="19">
         <v>1</v>
@@ -12368,7 +12384,7 @@
         <v>66</v>
       </c>
       <c r="O33" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P33" s="6" t="s">
         <v>27</v>
@@ -12451,18 +12467,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E34" s="19">
         <v>1</v>
@@ -12485,7 +12501,7 @@
         <v>67</v>
       </c>
       <c r="O34" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>27</v>
@@ -12568,18 +12584,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E35" s="19">
         <v>1</v>
@@ -12602,7 +12618,7 @@
         <v>68</v>
       </c>
       <c r="O35" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P35" s="6" t="s">
         <v>27</v>
@@ -12685,18 +12701,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E36" s="19">
         <v>1</v>
@@ -12719,7 +12735,7 @@
         <v>69</v>
       </c>
       <c r="O36" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>27</v>
@@ -12802,18 +12818,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E37" s="19">
         <v>1</v>
@@ -12836,7 +12852,7 @@
         <v>70</v>
       </c>
       <c r="O37" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P37" s="6" t="s">
         <v>27</v>
@@ -12919,18 +12935,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E38" s="19">
         <v>1</v>
@@ -12953,7 +12969,7 @@
         <v>71</v>
       </c>
       <c r="O38" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>27</v>
@@ -13036,18 +13052,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E39" s="19">
         <v>1</v>
@@ -13070,7 +13086,7 @@
         <v>72</v>
       </c>
       <c r="O39" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>27</v>
@@ -13153,18 +13169,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E40" s="19">
         <v>1</v>
@@ -13187,7 +13203,7 @@
         <v>73</v>
       </c>
       <c r="O40" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>27</v>
@@ -13270,18 +13286,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E41" s="19">
         <v>1</v>
@@ -13304,7 +13320,7 @@
         <v>74</v>
       </c>
       <c r="O41" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>27</v>
@@ -13387,18 +13403,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E42" s="19">
         <v>1</v>
@@ -13421,7 +13437,7 @@
         <v>75</v>
       </c>
       <c r="O42" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>27</v>
@@ -13504,18 +13520,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E43" s="19">
         <v>1</v>
@@ -13538,7 +13554,7 @@
         <v>76</v>
       </c>
       <c r="O43" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>27</v>
@@ -13621,18 +13637,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E44" s="19">
         <v>1</v>
@@ -13655,7 +13671,7 @@
         <v>77</v>
       </c>
       <c r="O44" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>27</v>
@@ -13738,18 +13754,18 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E45" s="19">
         <v>1</v>
@@ -13772,7 +13788,7 @@
         <v>78</v>
       </c>
       <c r="O45" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>27</v>
@@ -13855,18 +13871,18 @@
         <v>3.90625</v>
       </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E46" s="19">
         <v>1</v>
@@ -13889,7 +13905,7 @@
         <v>79</v>
       </c>
       <c r="O46" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>80</v>
@@ -13978,18 +13994,18 @@
         <v>1.5033333068541384</v>
       </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E47" s="19">
         <v>1</v>
@@ -14012,7 +14028,7 @@
         <v>81</v>
       </c>
       <c r="O47" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>80</v>
@@ -14101,18 +14117,18 @@
         <v>1.5033333068541381</v>
       </c>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E48" s="19">
         <v>1</v>
@@ -14135,7 +14151,7 @@
         <v>82</v>
       </c>
       <c r="O48" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>80</v>
@@ -14224,18 +14240,18 @@
         <v>1.1881369949110563</v>
       </c>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E49" s="19">
         <v>1</v>
@@ -14258,7 +14274,7 @@
         <v>83</v>
       </c>
       <c r="O49" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>80</v>
@@ -14347,18 +14363,18 @@
         <v>1.1629101414416052</v>
       </c>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E50" s="19">
         <v>1</v>
@@ -14381,7 +14397,7 @@
         <v>84</v>
       </c>
       <c r="O50" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>27</v>
@@ -14463,18 +14479,18 @@
         <v>3.9062500000000004</v>
       </c>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E51" s="19">
         <v>1</v>
@@ -14497,7 +14513,7 @@
         <v>85</v>
       </c>
       <c r="O51" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>27</v>
@@ -14580,18 +14596,18 @@
         <v>4.6875000000000009</v>
       </c>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E52" s="19">
         <v>1</v>
@@ -14614,7 +14630,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="5" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>27</v>
@@ -14697,18 +14713,18 @@
         <v>3.2407407407407409</v>
       </c>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E53" s="19">
         <v>1</v>
@@ -14731,7 +14747,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>27</v>
@@ -14814,18 +14830,18 @@
         <v>3.2407407407407409</v>
       </c>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E54" s="19">
         <v>1</v>
@@ -14848,7 +14864,7 @@
         <v>87</v>
       </c>
       <c r="O54" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>27</v>
@@ -14931,18 +14947,18 @@
         <v>6.2499999999999991</v>
       </c>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E55" s="19">
         <v>1</v>
@@ -14967,7 +14983,7 @@
         <v>89</v>
       </c>
       <c r="O55" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>27</v>
@@ -15049,18 +15065,18 @@
         <v>3.7037037037037033</v>
       </c>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E56" s="19">
         <v>1</v>
@@ -15085,7 +15101,7 @@
         <v>91</v>
       </c>
       <c r="O56" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>27</v>
@@ -15174,18 +15190,18 @@
         <v>2.0794444816235882</v>
       </c>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E57" s="19">
         <v>1</v>
@@ -15210,7 +15226,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>27</v>
@@ -15298,18 +15314,18 @@
         <v>0.682062825375507</v>
       </c>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E58" s="19">
         <v>1</v>
@@ -15332,7 +15348,7 @@
         <v>93</v>
       </c>
       <c r="O58" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>27</v>
@@ -15421,18 +15437,18 @@
         <v>1.584067227618178</v>
       </c>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E59" s="19">
         <v>1</v>
@@ -15455,7 +15471,7 @@
         <v>94</v>
       </c>
       <c r="O59" s="5" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>27</v>
@@ -15544,18 +15560,18 @@
         <v>1.2626874796242238</v>
       </c>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E60" s="19">
         <v>1</v>
@@ -15578,7 +15594,7 @@
         <v>97</v>
       </c>
       <c r="O60" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>27</v>
@@ -15667,18 +15683,18 @@
         <v>1.165542478997921</v>
       </c>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E61" s="19">
         <v>1</v>
@@ -15701,7 +15717,7 @@
         <v>98</v>
       </c>
       <c r="O61" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>27</v>
@@ -15790,18 +15806,18 @@
         <v>1.1453025708336924</v>
       </c>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E62" s="19">
         <v>1</v>
@@ -15824,7 +15840,7 @@
         <v>100</v>
       </c>
       <c r="O62" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>80</v>
@@ -15913,18 +15929,18 @@
         <v>1.0499523822058021</v>
       </c>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E63" s="19">
         <v>1</v>
@@ -15947,7 +15963,7 @@
         <v>51</v>
       </c>
       <c r="O63" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>27</v>
@@ -16030,18 +16046,18 @@
         <v>3.9384920139218527</v>
       </c>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E64" s="19">
         <v>1</v>
@@ -16064,7 +16080,7 @@
         <v>102</v>
       </c>
       <c r="O64" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>27</v>
@@ -16147,18 +16163,18 @@
         <v>3.9384920139218527</v>
       </c>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E65" s="19">
         <v>1</v>
@@ -16181,7 +16197,7 @@
         <v>103</v>
       </c>
       <c r="O65" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>27</v>
@@ -16264,18 +16280,18 @@
         <v>3.9384920139218527</v>
       </c>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E66" s="19">
         <v>1</v>
@@ -16300,7 +16316,7 @@
         <v>89</v>
       </c>
       <c r="O66" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>27</v>
@@ -16383,18 +16399,18 @@
         <v>3.5833333333333335</v>
       </c>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C67" s="15" t="s">
+        <v>548</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>549</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>550</v>
       </c>
       <c r="E67" s="19">
         <v>1</v>
@@ -16419,7 +16435,7 @@
         <v>106</v>
       </c>
       <c r="O67" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>27</v>
@@ -16502,18 +16518,18 @@
         <v>3.8333333333333335</v>
       </c>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E68" s="19">
         <v>1</v>
@@ -16538,7 +16554,7 @@
         <v>108</v>
       </c>
       <c r="O68" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>27</v>
@@ -16621,18 +16637,18 @@
         <v>3.5833333333333335</v>
       </c>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E69" s="19">
         <v>1</v>
@@ -16657,7 +16673,7 @@
         <v>108</v>
       </c>
       <c r="O69" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>27</v>
@@ -16740,18 +16756,18 @@
         <v>3.5833333333333335</v>
       </c>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E70" s="19">
         <v>1</v>
@@ -16776,7 +16792,7 @@
         <v>111</v>
       </c>
       <c r="O70" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>27</v>
@@ -16864,18 +16880,18 @@
         <v>1.6840907460634127</v>
       </c>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E71" s="19">
         <v>1</v>
@@ -16900,7 +16916,7 @@
         <v>111</v>
       </c>
       <c r="O71" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>27</v>
@@ -16988,18 +17004,18 @@
         <v>1.7104564330775569</v>
       </c>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E72" s="19">
         <v>1</v>
@@ -17024,7 +17040,7 @@
         <v>113</v>
       </c>
       <c r="O72" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>27</v>
@@ -17112,18 +17128,18 @@
         <v>1.6579735962048303</v>
       </c>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E73" s="19">
         <v>1</v>
@@ -17146,7 +17162,7 @@
         <v>115</v>
       </c>
       <c r="O73" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>27</v>
@@ -17234,18 +17250,18 @@
         <v>2.5287610566591523</v>
       </c>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E74" s="19">
         <v>1</v>
@@ -17268,7 +17284,7 @@
         <v>116</v>
       </c>
       <c r="O74" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>27</v>
@@ -17356,24 +17372,24 @@
         <v>2.4793535855822042</v>
       </c>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E75" s="19">
         <v>1</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G75" s="17"/>
       <c r="H75" s="17"/>
@@ -17389,10 +17405,10 @@
       </c>
       <c r="M75" s="104"/>
       <c r="N75" s="6" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="O75" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>27</v>
@@ -17481,24 +17497,24 @@
         <v>1.890388055872956</v>
       </c>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E76" s="19">
         <v>1</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G76" s="17"/>
       <c r="H76" s="17"/>
@@ -17517,7 +17533,7 @@
         <v>238</v>
       </c>
       <c r="O76" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>27</v>
@@ -17606,24 +17622,24 @@
         <v>1.8605083275965164</v>
       </c>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E77" s="19">
         <v>1</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G77" s="17"/>
       <c r="H77" s="17"/>
@@ -17642,7 +17658,7 @@
         <v>50</v>
       </c>
       <c r="O77" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>27</v>
@@ -17731,24 +17747,24 @@
         <v>1.8523399895648596</v>
       </c>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E78" s="19">
         <v>1</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G78" s="17"/>
       <c r="H78" s="17"/>
@@ -17767,7 +17783,7 @@
         <v>51</v>
       </c>
       <c r="O78" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>27</v>
@@ -17856,18 +17872,18 @@
         <v>1.7669888872138106</v>
       </c>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E79" s="19">
         <v>1</v>
@@ -17890,7 +17906,7 @@
         <v>50</v>
       </c>
       <c r="O79" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>27</v>
@@ -17979,18 +17995,18 @@
         <v>0.64100515446669049</v>
       </c>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E80" s="19">
         <v>1</v>
@@ -18013,7 +18029,7 @@
         <v>51</v>
       </c>
       <c r="O80" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>27</v>
@@ -18102,18 +18118,18 @@
         <v>0.62670976763932151</v>
       </c>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E81" s="19">
         <v>1</v>
@@ -18136,7 +18152,7 @@
         <v>121</v>
       </c>
       <c r="O81" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>27</v>
@@ -18225,18 +18241,18 @@
         <v>0.76883870310314895</v>
       </c>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B82" s="120" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E82" s="19">
         <v>1</v>
@@ -18259,7 +18275,7 @@
         <v>123</v>
       </c>
       <c r="O82" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>27</v>
@@ -18348,18 +18364,18 @@
         <v>1.4269848890125221</v>
       </c>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E83" s="19">
         <v>1</v>
@@ -18382,7 +18398,7 @@
         <v>125</v>
       </c>
       <c r="O83" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>27</v>
@@ -18471,18 +18487,18 @@
         <v>0.83525452781953513</v>
       </c>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E84" s="19">
         <v>1</v>
@@ -18505,7 +18521,7 @@
         <v>126</v>
       </c>
       <c r="O84" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>27</v>
@@ -18594,18 +18610,18 @@
         <v>0.81799598953212038</v>
       </c>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E85" s="19">
         <v>1</v>
@@ -18628,7 +18644,7 @@
         <v>127</v>
       </c>
       <c r="O85" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P85" s="6" t="s">
         <v>27</v>
@@ -18717,18 +18733,18 @@
         <v>0.78388138912123639</v>
       </c>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E86" s="19">
         <v>1</v>
@@ -18751,7 +18767,7 @@
         <v>129</v>
       </c>
       <c r="O86" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>80</v>
@@ -18840,18 +18856,18 @@
         <v>1.1501266268686077</v>
       </c>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E87" s="19">
         <v>1</v>
@@ -18876,7 +18892,7 @@
         <v>50</v>
       </c>
       <c r="O87" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>27</v>
@@ -18965,18 +18981,18 @@
         <v>0.23299756298435631</v>
       </c>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>28</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E88" s="19">
         <v>1</v>
@@ -19001,7 +19017,7 @@
         <v>51</v>
       </c>
       <c r="O88" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>27</v>
@@ -19090,18 +19106,18 @@
         <v>1.2387943662501089</v>
       </c>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E89" s="19">
         <v>1</v>
@@ -19124,7 +19140,7 @@
         <v>131</v>
       </c>
       <c r="O89" s="5" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P89" s="6" t="s">
         <v>80</v>
@@ -19213,18 +19229,18 @@
         <v>1.5149909654595908</v>
       </c>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>28</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E90" s="19">
         <v>1</v>
@@ -19247,7 +19263,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="5" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>27</v>
@@ -19336,18 +19352,18 @@
         <v>1.2046020634661616</v>
       </c>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E91" s="19">
         <v>1</v>
@@ -19370,7 +19386,7 @@
         <v>118</v>
       </c>
       <c r="O91" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P91" s="6" t="s">
         <v>27</v>
@@ -19459,18 +19475,18 @@
         <v>1.2072988815514583</v>
       </c>
     </row>
-    <row r="92" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E92" s="19">
         <v>1</v>
@@ -19493,7 +19509,7 @@
         <v>133</v>
       </c>
       <c r="O92" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>27</v>
@@ -19582,18 +19598,18 @@
         <v>1.4090811331942312</v>
       </c>
     </row>
-    <row r="93" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E93" s="19">
         <v>1</v>
@@ -19616,7 +19632,7 @@
         <v>50</v>
       </c>
       <c r="O93" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P93" s="6" t="s">
         <v>27</v>
@@ -19705,18 +19721,18 @@
         <v>1.1397336017719824</v>
       </c>
     </row>
-    <row r="94" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E94" s="19">
         <v>1</v>
@@ -19739,7 +19755,7 @@
         <v>51</v>
       </c>
       <c r="O94" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>27</v>
@@ -19828,18 +19844,18 @@
         <v>1.0959959051299162</v>
       </c>
     </row>
-    <row r="95" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E95" s="19">
         <v>1</v>
@@ -19862,7 +19878,7 @@
         <v>52</v>
       </c>
       <c r="O95" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P95" s="6" t="s">
         <v>27</v>
@@ -19951,18 +19967,18 @@
         <v>1.0527200029561115</v>
       </c>
     </row>
-    <row r="96" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E96" s="19">
         <v>1</v>
@@ -19987,7 +20003,7 @@
         <v>135</v>
       </c>
       <c r="O96" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>80</v>
@@ -20076,18 +20092,18 @@
         <v>2.1202973983797322</v>
       </c>
     </row>
-    <row r="97" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E97" s="19">
         <v>1</v>
@@ -20112,7 +20128,7 @@
         <v>136</v>
       </c>
       <c r="O97" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P97" s="6" t="s">
         <v>27</v>
@@ -20201,18 +20217,18 @@
         <v>2.0772596632135061</v>
       </c>
     </row>
-    <row r="98" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E98" s="19">
         <v>1</v>
@@ -20235,7 +20251,7 @@
         <v>138</v>
       </c>
       <c r="O98" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>27</v>
@@ -20324,18 +20340,18 @@
         <v>1.5361651825388483</v>
       </c>
     </row>
-    <row r="99" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E99" s="19">
         <v>1</v>
@@ -20358,7 +20374,7 @@
         <v>50</v>
       </c>
       <c r="O99" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P99" s="6" t="s">
         <v>27</v>
@@ -20447,18 +20463,18 @@
         <v>1.5065784699927574</v>
       </c>
     </row>
-    <row r="100" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E100" s="19">
         <v>1</v>
@@ -20481,7 +20497,7 @@
         <v>51</v>
       </c>
       <c r="O100" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>27</v>
@@ -20570,18 +20586,18 @@
         <v>1.4478450040383797</v>
       </c>
     </row>
-    <row r="101" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E101" s="19">
         <v>1</v>
@@ -20604,7 +20620,7 @@
         <v>121</v>
       </c>
       <c r="O101" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P101" s="6" t="s">
         <v>27</v>
@@ -20693,18 +20709,18 @@
         <v>1.0994472988394468</v>
       </c>
     </row>
-    <row r="102" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E102" s="19">
         <v>1</v>
@@ -20727,7 +20743,7 @@
         <v>139</v>
       </c>
       <c r="O102" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>27</v>
@@ -20816,18 +20832,18 @@
         <v>1.0586916755795146</v>
       </c>
     </row>
-    <row r="103" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E103" s="19">
         <v>1</v>
@@ -20850,7 +20866,7 @@
         <v>121</v>
       </c>
       <c r="O103" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P103" s="6" t="s">
         <v>27</v>
@@ -20939,18 +20955,18 @@
         <v>1.6691380981214541</v>
       </c>
     </row>
-    <row r="104" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E104" s="19">
         <v>1</v>
@@ -20973,7 +20989,7 @@
         <v>139</v>
       </c>
       <c r="O104" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>27</v>
@@ -21062,18 +21078,18 @@
         <v>1.6065963825333243</v>
       </c>
     </row>
-    <row r="105" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E105" s="19">
         <v>1</v>
@@ -21096,7 +21112,7 @@
         <v>138</v>
       </c>
       <c r="O105" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P105" s="6" t="s">
         <v>27</v>
@@ -21185,18 +21201,18 @@
         <v>0.90690345120653837</v>
       </c>
     </row>
-    <row r="106" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E106" s="19">
         <v>1</v>
@@ -21219,7 +21235,7 @@
         <v>50</v>
       </c>
       <c r="O106" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>27</v>
@@ -21308,18 +21324,18 @@
         <v>0.87259450365707092</v>
       </c>
     </row>
-    <row r="107" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E107" s="19">
         <v>1</v>
@@ -21342,7 +21358,7 @@
         <v>142</v>
       </c>
       <c r="O107" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P107" s="6" t="s">
         <v>27</v>
@@ -21431,18 +21447,18 @@
         <v>0.83860953776262182</v>
       </c>
     </row>
-    <row r="108" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E108" s="19">
         <v>1</v>
@@ -21465,7 +21481,7 @@
         <v>143</v>
       </c>
       <c r="O108" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>27</v>
@@ -21554,18 +21570,18 @@
         <v>0.80502313984963059</v>
       </c>
     </row>
-    <row r="109" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E109" s="19">
         <v>1</v>
@@ -21588,7 +21604,7 @@
         <v>144</v>
       </c>
       <c r="O109" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P109" s="6" t="s">
         <v>27</v>
@@ -21677,18 +21693,18 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="110" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E110" s="19">
         <v>1</v>
@@ -21711,7 +21727,7 @@
         <v>145</v>
       </c>
       <c r="O110" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>27</v>
@@ -21800,18 +21816,18 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="111" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E111" s="19">
         <v>1</v>
@@ -21834,7 +21850,7 @@
         <v>146</v>
       </c>
       <c r="O111" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P111" s="6" t="s">
         <v>27</v>
@@ -21923,18 +21939,18 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="112" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E112" s="19">
         <v>1</v>
@@ -21957,7 +21973,7 @@
         <v>147</v>
       </c>
       <c r="O112" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>27</v>
@@ -22046,18 +22062,18 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="113" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E113" s="19">
         <v>1</v>
@@ -22080,7 +22096,7 @@
         <v>148</v>
       </c>
       <c r="O113" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P113" s="6" t="s">
         <v>27</v>
@@ -22169,18 +22185,18 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="114" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E114" s="19">
         <v>1</v>
@@ -22203,7 +22219,7 @@
         <v>118</v>
       </c>
       <c r="O114" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>27</v>
@@ -22292,18 +22308,18 @@
         <v>0.73245167478536033</v>
       </c>
     </row>
-    <row r="115" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E115" s="19">
         <v>1</v>
@@ -22326,7 +22342,7 @@
         <v>50</v>
       </c>
       <c r="O115" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P115" s="6" t="s">
         <v>27</v>
@@ -22415,18 +22431,18 @@
         <v>0.70127185350915722</v>
       </c>
     </row>
-    <row r="116" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E116" s="19">
         <v>1</v>
@@ -22449,7 +22465,7 @@
         <v>51</v>
       </c>
       <c r="O116" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>27</v>
@@ -22538,18 +22554,18 @@
         <v>0.6706877524292354</v>
       </c>
     </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E117" s="19">
         <v>1</v>
@@ -22572,7 +22588,7 @@
         <v>52</v>
       </c>
       <c r="O117" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P117" s="6" t="s">
         <v>27</v>
@@ -22661,18 +22677,18 @@
         <v>0.64075267145675929</v>
       </c>
     </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E118" s="19">
         <v>1</v>
@@ -22695,7 +22711,7 @@
         <v>53</v>
       </c>
       <c r="O118" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>27</v>
@@ -22784,18 +22800,18 @@
         <v>0.61151467271213211</v>
       </c>
     </row>
-    <row r="119" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E119" s="19">
         <v>1</v>
@@ -22818,7 +22834,7 @@
         <v>54</v>
       </c>
       <c r="O119" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P119" s="6" t="s">
         <v>27</v>
@@ -22907,18 +22923,18 @@
         <v>1.9492775508164899</v>
       </c>
     </row>
-    <row r="120" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E120" s="19">
         <v>1</v>
@@ -22941,7 +22957,7 @@
         <v>151</v>
       </c>
       <c r="O120" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>27</v>
@@ -23030,18 +23046,18 @@
         <v>1.2292115404911319</v>
       </c>
     </row>
-    <row r="121" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E121" s="19">
         <v>1</v>
@@ -23064,7 +23080,7 @@
         <v>152</v>
       </c>
       <c r="O121" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P121" s="6" t="s">
         <v>27</v>
@@ -23153,18 +23169,18 @@
         <v>1.2413630323963301</v>
       </c>
     </row>
-    <row r="122" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E122" s="19">
         <v>1</v>
@@ -23187,7 +23203,7 @@
         <v>153</v>
       </c>
       <c r="O122" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>27</v>
@@ -23276,18 +23292,18 @@
         <v>1.2561653093904881</v>
       </c>
     </row>
-    <row r="123" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E123" s="19">
         <v>1</v>
@@ -23310,7 +23326,7 @@
         <v>154</v>
       </c>
       <c r="O123" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P123" s="6" t="s">
         <v>27</v>
@@ -23399,18 +23415,18 @@
         <v>1.2113560025023844</v>
       </c>
     </row>
-    <row r="124" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E124" s="19">
         <v>1</v>
@@ -23433,7 +23449,7 @@
         <v>155</v>
       </c>
       <c r="O124" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>27</v>
@@ -23522,18 +23538,18 @@
         <v>2.613496932515337</v>
       </c>
     </row>
-    <row r="125" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E125" s="19">
         <v>1</v>
@@ -23556,7 +23572,7 @@
         <v>156</v>
       </c>
       <c r="O125" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P125" s="6" t="s">
         <v>27</v>
@@ -23645,18 +23661,18 @@
         <v>2.6134969325153379</v>
       </c>
     </row>
-    <row r="126" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E126" s="19">
         <v>1</v>
@@ -23679,7 +23695,7 @@
         <v>158</v>
       </c>
       <c r="O126" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>27</v>
@@ -23768,18 +23784,18 @@
         <v>1.3821716627734322</v>
       </c>
     </row>
-    <row r="127" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E127" s="19">
         <v>1</v>
@@ -23802,7 +23818,7 @@
         <v>160</v>
       </c>
       <c r="O127" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P127" s="6" t="s">
         <v>27</v>
@@ -23891,18 +23907,18 @@
         <v>1.3508286832235206</v>
       </c>
     </row>
-    <row r="128" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E128" s="19">
         <v>1</v>
@@ -23925,7 +23941,7 @@
         <v>161</v>
       </c>
       <c r="O128" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>27</v>
@@ -24014,18 +24030,18 @@
         <v>1.3273996567144928</v>
       </c>
     </row>
-    <row r="129" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E129" s="19">
         <v>1</v>
@@ -24048,7 +24064,7 @@
         <v>26</v>
       </c>
       <c r="O129" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P129" s="6" t="s">
         <v>27</v>
@@ -24137,21 +24153,21 @@
         <v>1.1478379123898736</v>
       </c>
     </row>
-    <row r="130" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="E130" s="19">
-        <v>1</v>
+        <v>549</v>
+      </c>
+      <c r="E130" s="121" t="s">
+        <v>736</v>
       </c>
       <c r="F130" s="17"/>
       <c r="G130" s="17"/>
@@ -24171,7 +24187,7 @@
         <v>26</v>
       </c>
       <c r="O130" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>27</v>
@@ -24260,21 +24276,21 @@
         <v>1.1873209657838852</v>
       </c>
     </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="E131" s="19">
-        <v>1</v>
+        <v>549</v>
+      </c>
+      <c r="E131" s="121" t="s">
+        <v>736</v>
       </c>
       <c r="F131" s="17"/>
       <c r="G131" s="17"/>
@@ -24294,7 +24310,7 @@
         <v>143</v>
       </c>
       <c r="O131" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P131" s="6" t="s">
         <v>27</v>
@@ -24383,18 +24399,18 @@
         <v>1.1478379123898732</v>
       </c>
     </row>
-    <row r="132" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E132" s="19">
         <v>1</v>
@@ -24417,7 +24433,7 @@
         <v>165</v>
       </c>
       <c r="O132" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>27</v>
@@ -24506,18 +24522,18 @@
         <v>1.1697737528257561</v>
       </c>
     </row>
-    <row r="133" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E133" s="19">
         <v>1</v>
@@ -24540,7 +24556,7 @@
         <v>26</v>
       </c>
       <c r="O133" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P133" s="6" t="s">
         <v>27</v>
@@ -24629,18 +24645,18 @@
         <v>1.1478379123898734</v>
       </c>
     </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E134" s="19">
         <v>1</v>
@@ -24663,7 +24679,7 @@
         <v>26</v>
       </c>
       <c r="O134" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>27</v>
@@ -24752,18 +24768,18 @@
         <v>1.1917791466511929</v>
       </c>
     </row>
-    <row r="135" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E135" s="19">
         <v>1</v>
@@ -24786,7 +24802,7 @@
         <v>26</v>
       </c>
       <c r="O135" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P135" s="6" t="s">
         <v>27</v>
@@ -24875,18 +24891,18 @@
         <v>1.1697737528257561</v>
       </c>
     </row>
-    <row r="136" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E136" s="19">
         <v>1</v>
@@ -24909,7 +24925,7 @@
         <v>26</v>
       </c>
       <c r="O136" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>27</v>
@@ -24998,18 +25014,18 @@
         <v>1.1478379123898732</v>
       </c>
     </row>
-    <row r="137" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E137" s="19">
         <v>1</v>
@@ -25032,7 +25048,7 @@
         <v>170</v>
       </c>
       <c r="O137" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P137" s="6" t="s">
         <v>27</v>
@@ -25120,18 +25136,18 @@
         <v>1.100201380402013</v>
       </c>
     </row>
-    <row r="138" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E138" s="19">
         <v>1</v>
@@ -25154,7 +25170,7 @@
         <v>171</v>
       </c>
       <c r="O138" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>27</v>
@@ -25237,18 +25253,18 @@
         <v>3.4285714285714284</v>
       </c>
     </row>
-    <row r="139" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E139" s="19">
         <v>1</v>
@@ -25271,7 +25287,7 @@
         <v>172</v>
       </c>
       <c r="O139" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P139" s="6" t="s">
         <v>27</v>
@@ -25359,18 +25375,18 @@
         <v>1.5534532233799874</v>
       </c>
     </row>
-    <row r="140" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E140" s="19">
         <v>1</v>
@@ -25393,7 +25409,7 @@
         <v>173</v>
       </c>
       <c r="O140" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>27</v>
@@ -25476,18 +25492,18 @@
         <v>3.4285714285714284</v>
       </c>
     </row>
-    <row r="141" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E141" s="19">
         <v>1</v>
@@ -25510,7 +25526,7 @@
         <v>175</v>
       </c>
       <c r="O141" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P141" s="6" t="s">
         <v>27</v>
@@ -25599,18 +25615,18 @@
         <v>1.3402722285622568</v>
       </c>
     </row>
-    <row r="142" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E142" s="19">
         <v>1</v>
@@ -25633,7 +25649,7 @@
         <v>176</v>
       </c>
       <c r="O142" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>27</v>
@@ -25722,18 +25738,18 @@
         <v>1.1069472501692708</v>
       </c>
     </row>
-    <row r="143" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E143" s="19">
         <v>1</v>
@@ -25756,7 +25772,7 @@
         <v>177</v>
       </c>
       <c r="O143" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P143" s="6" t="s">
         <v>27</v>
@@ -25845,18 +25861,18 @@
         <v>1.3096934841312509</v>
       </c>
     </row>
-    <row r="144" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E144" s="19">
         <v>1</v>
@@ -25879,7 +25895,7 @@
         <v>178</v>
       </c>
       <c r="O144" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>27</v>
@@ -25968,18 +25984,18 @@
         <v>1.2649802836537249</v>
       </c>
     </row>
-    <row r="145" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E145" s="19">
         <v>1</v>
@@ -26002,7 +26018,7 @@
         <v>179</v>
       </c>
       <c r="O145" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P145" s="6" t="s">
         <v>27</v>
@@ -26091,18 +26107,18 @@
         <v>1.242648133063637</v>
       </c>
     </row>
-    <row r="146" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E146" s="19">
         <v>1</v>
@@ -26125,7 +26141,7 @@
         <v>181</v>
       </c>
       <c r="O146" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>80</v>
@@ -26214,18 +26230,18 @@
         <v>0.90074899958421728</v>
       </c>
     </row>
-    <row r="147" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E147" s="19">
         <v>1</v>
@@ -26248,7 +26264,7 @@
         <v>181</v>
       </c>
       <c r="O147" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P147" s="6" t="s">
         <v>80</v>
@@ -26337,18 +26353,18 @@
         <v>0.86471997316517379</v>
       </c>
     </row>
-    <row r="148" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E148" s="19">
         <v>1</v>
@@ -26371,7 +26387,7 @@
         <v>181</v>
       </c>
       <c r="O148" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>80</v>
@@ -26460,18 +26476,18 @@
         <v>0.8291908931927453</v>
       </c>
     </row>
-    <row r="149" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E149" s="19">
         <v>1</v>
@@ -26494,7 +26510,7 @@
         <v>182</v>
       </c>
       <c r="O149" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="P149" s="6" t="s">
         <v>27</v>
@@ -26583,18 +26599,18 @@
         <v>0.82391222601076908</v>
       </c>
     </row>
-    <row r="150" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E150" s="19">
         <v>1</v>
@@ -26617,7 +26633,7 @@
         <v>182</v>
       </c>
       <c r="O150" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>27</v>
@@ -26706,18 +26722,18 @@
         <v>1.307592918802565</v>
       </c>
     </row>
-    <row r="151" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E151" s="19">
         <v>1</v>
@@ -26740,7 +26756,7 @@
         <v>182</v>
       </c>
       <c r="O151" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="P151" s="6" t="s">
         <v>27</v>
@@ -26829,18 +26845,18 @@
         <v>1.259710619839457</v>
       </c>
     </row>
-    <row r="152" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E152" s="19">
         <v>1</v>
@@ -26863,7 +26879,7 @@
         <v>183</v>
       </c>
       <c r="O152" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>80</v>
@@ -26946,18 +26962,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E153" s="19">
         <v>1</v>
@@ -26980,7 +26996,7 @@
         <v>184</v>
       </c>
       <c r="O153" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="P153" s="6" t="s">
         <v>27</v>
@@ -27069,18 +27085,18 @@
         <v>1.5199940748831153</v>
       </c>
     </row>
-    <row r="154" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E154" s="19">
         <v>1</v>
@@ -27103,7 +27119,7 @@
         <v>185</v>
       </c>
       <c r="O154" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>27</v>
@@ -27192,18 +27208,18 @@
         <v>0.94841385595929528</v>
       </c>
     </row>
-    <row r="155" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E155" s="19">
         <v>1</v>
@@ -27226,7 +27242,7 @@
         <v>186</v>
       </c>
       <c r="O155" s="79" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P155" s="6" t="s">
         <v>27</v>
@@ -27315,18 +27331,18 @@
         <v>2.001711919813113</v>
       </c>
     </row>
-    <row r="156" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E156" s="19">
         <v>1</v>
@@ -27349,7 +27365,7 @@
         <v>187</v>
       </c>
       <c r="O156" s="79" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>27</v>
@@ -27438,18 +27454,18 @@
         <v>2.7873981870831179</v>
       </c>
     </row>
-    <row r="157" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E157" s="19">
         <v>1</v>
@@ -27472,7 +27488,7 @@
         <v>188</v>
       </c>
       <c r="O157" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P157" s="6" t="s">
         <v>27</v>
@@ -27561,18 +27577,18 @@
         <v>1.8835744163813872</v>
       </c>
     </row>
-    <row r="158" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E158" s="19">
         <v>1</v>
@@ -27595,7 +27611,7 @@
         <v>190</v>
       </c>
       <c r="O158" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>27</v>
@@ -27684,18 +27700,18 @@
         <v>1.3178084967631456</v>
       </c>
     </row>
-    <row r="159" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E159" s="19">
         <v>1</v>
@@ -27718,7 +27734,7 @@
         <v>190</v>
       </c>
       <c r="O159" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P159" s="6" t="s">
         <v>27</v>
@@ -27807,18 +27823,18 @@
         <v>1.3730404099510281</v>
       </c>
     </row>
-    <row r="160" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E160" s="19">
         <v>1</v>
@@ -27841,7 +27857,7 @@
         <v>192</v>
       </c>
       <c r="O160" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>27</v>
@@ -27930,18 +27946,18 @@
         <v>1.3848749369337743</v>
       </c>
     </row>
-    <row r="161" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E161" s="19">
         <v>1</v>
@@ -27964,7 +27980,7 @@
         <v>193</v>
       </c>
       <c r="O161" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P161" s="6" t="s">
         <v>27</v>
@@ -28053,18 +28069,18 @@
         <v>1.3585676614027813</v>
       </c>
     </row>
-    <row r="162" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E162" s="19">
         <v>1</v>
@@ -28087,7 +28103,7 @@
         <v>194</v>
       </c>
       <c r="O162" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>80</v>
@@ -28176,18 +28192,18 @@
         <v>1.372740519264412</v>
       </c>
     </row>
-    <row r="163" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E163" s="19">
         <v>1</v>
@@ -28210,7 +28226,7 @@
         <v>195</v>
       </c>
       <c r="O163" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P163" s="6" t="s">
         <v>80</v>
@@ -28299,18 +28315,18 @@
         <v>1.3209122633460484</v>
       </c>
     </row>
-    <row r="164" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E164" s="19">
         <v>1</v>
@@ -28333,7 +28349,7 @@
         <v>197</v>
       </c>
       <c r="O164" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>27</v>
@@ -28422,18 +28438,18 @@
         <v>4.2857142857142856</v>
       </c>
     </row>
-    <row r="165" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E165" s="19">
         <v>1</v>
@@ -28456,7 +28472,7 @@
         <v>198</v>
       </c>
       <c r="O165" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P165" s="6" t="s">
         <v>27</v>
@@ -28545,18 +28561,18 @@
         <v>0.89768559755339483</v>
       </c>
     </row>
-    <row r="166" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E166" s="19">
         <v>1</v>
@@ -28579,7 +28595,7 @@
         <v>199</v>
       </c>
       <c r="O166" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>27</v>
@@ -28668,18 +28684,18 @@
         <v>0.84488056240319498</v>
       </c>
     </row>
-    <row r="167" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E167" s="19">
         <v>1</v>
@@ -28702,7 +28718,7 @@
         <v>200</v>
       </c>
       <c r="O167" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P167" s="6" t="s">
         <v>27</v>
@@ -28791,18 +28807,18 @@
         <v>0.79115858344502654</v>
       </c>
     </row>
-    <row r="168" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E168" s="19">
         <v>1</v>
@@ -28825,7 +28841,7 @@
         <v>201</v>
       </c>
       <c r="O168" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>27</v>
@@ -28914,18 +28930,18 @@
         <v>0.77406888933587614</v>
       </c>
     </row>
-    <row r="169" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E169" s="19">
         <v>1</v>
@@ -28948,7 +28964,7 @@
         <v>202</v>
       </c>
       <c r="O169" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P169" s="6" t="s">
         <v>27</v>
@@ -29037,18 +29053,18 @@
         <v>0.95007407159306967</v>
       </c>
     </row>
-    <row r="170" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E170" s="19">
         <v>1</v>
@@ -29071,7 +29087,7 @@
         <v>204</v>
       </c>
       <c r="O170" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>27</v>
@@ -29160,18 +29176,18 @@
         <v>1.6504684110205614</v>
       </c>
     </row>
-    <row r="171" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E171" s="19">
         <v>1</v>
@@ -29194,7 +29210,7 @@
         <v>205</v>
       </c>
       <c r="O171" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P171" s="6" t="s">
         <v>27</v>
@@ -29283,18 +29299,18 @@
         <v>1.5959766651655141</v>
       </c>
     </row>
-    <row r="172" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E172" s="19">
         <v>1</v>
@@ -29317,7 +29333,7 @@
         <v>206</v>
       </c>
       <c r="O172" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>27</v>
@@ -29406,18 +29422,18 @@
         <v>1.541459129098488</v>
       </c>
     </row>
-    <row r="173" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E173" s="19">
         <v>1</v>
@@ -29440,7 +29456,7 @@
         <v>207</v>
       </c>
       <c r="O173" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P173" s="6" t="s">
         <v>27</v>
@@ -29529,18 +29545,18 @@
         <v>1.4870446603133847</v>
       </c>
     </row>
-    <row r="174" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E174" s="19">
         <v>1</v>
@@ -29563,7 +29579,7 @@
         <v>209</v>
       </c>
       <c r="O174" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="P174" s="6" t="s">
         <v>27</v>
@@ -29652,18 +29668,18 @@
         <v>1.29803634535601</v>
       </c>
     </row>
-    <row r="175" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E175" s="19">
         <v>1</v>
@@ -29686,7 +29702,7 @@
         <v>210</v>
       </c>
       <c r="O175" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="P175" s="6" t="s">
         <v>27</v>
@@ -29775,18 +29791,18 @@
         <v>1.2979593269679877</v>
       </c>
     </row>
-    <row r="176" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E176" s="19">
         <v>1</v>
@@ -29809,7 +29825,7 @@
         <v>211</v>
       </c>
       <c r="O176" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="P176" s="6" t="s">
         <v>27</v>
@@ -29898,18 +29914,18 @@
         <v>1.6263477020219728</v>
       </c>
     </row>
-    <row r="177" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C177" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E177" s="19">
         <v>1</v>
@@ -29932,7 +29948,7 @@
         <v>213</v>
       </c>
       <c r="O177" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P177" s="6" t="s">
         <v>27</v>
@@ -30021,18 +30037,18 @@
         <v>1.2592386722239013</v>
       </c>
     </row>
-    <row r="178" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E178" s="19">
         <v>1</v>
@@ -30055,7 +30071,7 @@
         <v>214</v>
       </c>
       <c r="O178" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P178" s="6" t="s">
         <v>27</v>
@@ -30144,18 +30160,18 @@
         <v>1.4641218723147973</v>
       </c>
     </row>
-    <row r="179" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E179" s="19">
         <v>1</v>
@@ -30178,7 +30194,7 @@
         <v>216</v>
       </c>
       <c r="O179" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P179" s="6" t="s">
         <v>27</v>
@@ -30267,18 +30283,18 @@
         <v>1.6857797571068185</v>
       </c>
     </row>
-    <row r="180" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E180" s="19">
         <v>1</v>
@@ -30301,7 +30317,7 @@
         <v>217</v>
       </c>
       <c r="O180" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P180" s="6" t="s">
         <v>27</v>
@@ -30390,18 +30406,18 @@
         <v>1.6461735009491525</v>
       </c>
     </row>
-    <row r="181" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E181" s="19">
         <v>1</v>
@@ -30424,7 +30440,7 @@
         <v>218</v>
       </c>
       <c r="O181" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P181" s="6" t="s">
         <v>27</v>
@@ -30513,18 +30529,18 @@
         <v>1.5931435361112869</v>
       </c>
     </row>
-    <row r="182" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C182" s="15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E182" s="19">
         <v>1</v>
@@ -30547,7 +30563,7 @@
         <v>220</v>
       </c>
       <c r="O182" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>27</v>
@@ -30636,18 +30652,18 @@
         <v>1.4757143571699876</v>
       </c>
     </row>
-    <row r="183" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C183" s="15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E183" s="19">
         <v>1</v>
@@ -30670,7 +30686,7 @@
         <v>220</v>
       </c>
       <c r="O183" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P183" s="6" t="s">
         <v>27</v>
@@ -30759,18 +30775,18 @@
         <v>1.4374300869105257</v>
       </c>
     </row>
-    <row r="184" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E184" s="19">
         <v>1</v>
@@ -30793,7 +30809,7 @@
         <v>220</v>
       </c>
       <c r="O184" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P184" s="6" t="s">
         <v>27</v>
@@ -30882,18 +30898,18 @@
         <v>1.3985631033192503</v>
       </c>
     </row>
-    <row r="185" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C185" s="15" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E185" s="19">
         <v>1</v>
@@ -30916,7 +30932,7 @@
         <v>222</v>
       </c>
       <c r="O185" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P185" s="6" t="s">
         <v>27</v>
@@ -31005,18 +31021,18 @@
         <v>1.3826456374022646</v>
       </c>
     </row>
-    <row r="186" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C186" s="15" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E186" s="19">
         <v>1</v>
@@ -31039,7 +31055,7 @@
         <v>224</v>
       </c>
       <c r="O186" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>27</v>
@@ -31128,18 +31144,18 @@
         <v>0.47357002940963111</v>
       </c>
     </row>
-    <row r="187" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C187" s="15" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E187" s="19">
         <v>1</v>
@@ -31162,7 +31178,7 @@
         <v>226</v>
       </c>
       <c r="O187" s="79" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P187" s="6" t="s">
         <v>27</v>
@@ -31251,18 +31267,18 @@
         <v>1.2597354394053424</v>
       </c>
     </row>
-    <row r="188" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C188" s="15" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E188" s="19">
         <v>1</v>
@@ -31285,7 +31301,7 @@
         <v>227</v>
       </c>
       <c r="O188" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>27</v>
@@ -31374,18 +31390,18 @@
         <v>1.1675517449568096</v>
       </c>
     </row>
-    <row r="189" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C189" s="15" t="s">
         <v>28</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E189" s="19">
         <v>1</v>
@@ -31408,7 +31424,7 @@
         <v>229</v>
       </c>
       <c r="O189" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P189" s="6" t="s">
         <v>27</v>
@@ -31497,18 +31513,18 @@
         <v>1.3696411756979359</v>
       </c>
     </row>
-    <row r="190" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C190" s="15" t="s">
         <v>28</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E190" s="19">
         <v>1</v>
@@ -31531,7 +31547,7 @@
         <v>230</v>
       </c>
       <c r="O190" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P190" s="6" t="s">
         <v>27</v>
@@ -31620,18 +31636,18 @@
         <v>1.350214188462304</v>
       </c>
     </row>
-    <row r="191" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C191" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E191" s="19">
         <v>1</v>
@@ -31654,7 +31670,7 @@
         <v>50</v>
       </c>
       <c r="O191" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P191" s="6" t="s">
         <v>27</v>
@@ -31743,18 +31759,18 @@
         <v>1.2329454023052526</v>
       </c>
     </row>
-    <row r="192" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C192" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E192" s="19">
         <v>1</v>
@@ -31777,7 +31793,7 @@
         <v>233</v>
       </c>
       <c r="O192" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P192" s="6" t="s">
         <v>27</v>
@@ -31866,18 +31882,18 @@
         <v>1.1957801977735603</v>
       </c>
     </row>
-    <row r="193" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E193" s="19">
         <v>1</v>
@@ -31900,7 +31916,7 @@
         <v>52</v>
       </c>
       <c r="O193" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P193" s="6" t="s">
         <v>27</v>
@@ -31989,18 +32005,18 @@
         <v>1.1035853568830785</v>
       </c>
     </row>
-    <row r="194" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C194" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E194" s="19">
         <v>1</v>
@@ -32023,7 +32039,7 @@
         <v>53</v>
       </c>
       <c r="O194" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P194" s="6" t="s">
         <v>27</v>
@@ -32112,18 +32128,18 @@
         <v>1.0659650406849812</v>
       </c>
     </row>
-    <row r="195" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C195" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E195" s="19">
         <v>1</v>
@@ -32146,7 +32162,7 @@
         <v>54</v>
       </c>
       <c r="O195" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P195" s="6" t="s">
         <v>27</v>
@@ -32235,18 +32251,18 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="196" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E196" s="19">
         <v>1</v>
@@ -32269,7 +32285,7 @@
         <v>55</v>
       </c>
       <c r="O196" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P196" s="6" t="s">
         <v>27</v>
@@ -32358,18 +32374,18 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="197" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C197" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E197" s="19">
         <v>1</v>
@@ -32392,7 +32408,7 @@
         <v>56</v>
       </c>
       <c r="O197" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P197" s="6" t="s">
         <v>27</v>
@@ -32481,18 +32497,18 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="198" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C198" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E198" s="19">
         <v>1</v>
@@ -32515,7 +32531,7 @@
         <v>234</v>
       </c>
       <c r="O198" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>27</v>
@@ -32604,18 +32620,18 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="199" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C199" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E199" s="19">
         <v>1</v>
@@ -32638,7 +32654,7 @@
         <v>235</v>
       </c>
       <c r="O199" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P199" s="6" t="s">
         <v>27</v>
@@ -32727,18 +32743,18 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="200" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C200" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E200" s="19">
         <v>1</v>
@@ -32761,7 +32777,7 @@
         <v>236</v>
       </c>
       <c r="O200" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P200" s="6" t="s">
         <v>27</v>
@@ -32850,18 +32866,18 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="201" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C201" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E201" s="19">
         <v>1</v>
@@ -32884,7 +32900,7 @@
         <v>138</v>
       </c>
       <c r="O201" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P201" s="6" t="s">
         <v>27</v>
@@ -32972,18 +32988,18 @@
         <v>1.6566885721095854</v>
       </c>
     </row>
-    <row r="202" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C202" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E202" s="19">
         <v>1</v>
@@ -33006,7 +33022,7 @@
         <v>238</v>
       </c>
       <c r="O202" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>27</v>
@@ -33094,18 +33110,18 @@
         <v>1.6346161037144891</v>
       </c>
     </row>
-    <row r="203" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C203" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E203" s="19">
         <v>1</v>
@@ -33128,7 +33144,7 @@
         <v>50</v>
       </c>
       <c r="O203" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P203" s="6" t="s">
         <v>27</v>
@@ -33216,18 +33232,18 @@
         <v>1.5890770411330262</v>
       </c>
     </row>
-    <row r="204" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C204" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E204" s="19">
         <v>1</v>
@@ -33250,7 +33266,7 @@
         <v>51</v>
       </c>
       <c r="O204" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P204" s="6" t="s">
         <v>27</v>
@@ -33339,18 +33355,18 @@
         <v>1.6348488056211639</v>
       </c>
     </row>
-    <row r="205" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C205" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E205" s="19">
         <v>1</v>
@@ -33373,7 +33389,7 @@
         <v>138</v>
       </c>
       <c r="O205" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P205" s="6" t="s">
         <v>27</v>
@@ -33462,18 +33478,18 @@
         <v>1.3994784856987472</v>
       </c>
     </row>
-    <row r="206" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C206" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E206" s="19">
         <v>1</v>
@@ -33496,7 +33512,7 @@
         <v>238</v>
       </c>
       <c r="O206" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P206" s="6" t="s">
         <v>27</v>
@@ -33585,18 +33601,18 @@
         <v>1.3761547970799959</v>
       </c>
     </row>
-    <row r="207" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C207" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E207" s="19">
         <v>1</v>
@@ -33619,7 +33635,7 @@
         <v>50</v>
       </c>
       <c r="O207" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P207" s="6" t="s">
         <v>27</v>
@@ -33708,18 +33724,18 @@
         <v>1.2739382867033264</v>
       </c>
     </row>
-    <row r="208" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C208" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E208" s="19">
         <v>1</v>
@@ -33742,7 +33758,7 @@
         <v>233</v>
       </c>
       <c r="O208" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P208" s="6" t="s">
         <v>27</v>
@@ -33831,18 +33847,18 @@
         <v>1.2513432560545719</v>
       </c>
     </row>
-    <row r="209" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C209" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E209" s="19">
         <v>1</v>
@@ -33865,7 +33881,7 @@
         <v>51</v>
       </c>
       <c r="O209" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P209" s="6" t="s">
         <v>27</v>
@@ -33954,18 +33970,18 @@
         <v>1.2287862611479596</v>
       </c>
     </row>
-    <row r="210" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C210" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E210" s="19">
         <v>1</v>
@@ -33988,7 +34004,7 @@
         <v>52</v>
       </c>
       <c r="O210" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>27</v>
@@ -34077,18 +34093,18 @@
         <v>1.1838391039622553</v>
       </c>
     </row>
-    <row r="211" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C211" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E211" s="19">
         <v>1</v>
@@ -34111,7 +34127,7 @@
         <v>100</v>
       </c>
       <c r="O211" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P211" s="6" t="s">
         <v>80</v>
@@ -34200,18 +34216,18 @@
         <v>1.3995973831143944</v>
       </c>
     </row>
-    <row r="212" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C212" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E212" s="19">
         <v>1</v>
@@ -34234,7 +34250,7 @@
         <v>241</v>
       </c>
       <c r="O212" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>80</v>
@@ -34323,18 +34339,18 @@
         <v>1.4269474786562346</v>
       </c>
     </row>
-    <row r="213" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C213" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E213" s="19">
         <v>1</v>
@@ -34357,7 +34373,7 @@
         <v>242</v>
       </c>
       <c r="O213" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P213" s="6" t="s">
         <v>80</v>
@@ -34446,18 +34462,18 @@
         <v>1.4544075393871425</v>
       </c>
     </row>
-    <row r="214" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C214" s="15" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E214" s="19">
         <v>1</v>
@@ -34480,7 +34496,7 @@
         <v>129</v>
       </c>
       <c r="O214" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>80</v>
@@ -34569,18 +34585,18 @@
         <v>1.1915152802141717</v>
       </c>
     </row>
-    <row r="215" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C215" s="15" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E215" s="19">
         <v>1</v>
@@ -34603,7 +34619,7 @@
         <v>245</v>
       </c>
       <c r="O215" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P215" s="6" t="s">
         <v>27</v>
@@ -34691,18 +34707,18 @@
         <v>1.3027775635825822</v>
       </c>
     </row>
-    <row r="216" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E216" s="19">
         <v>1</v>
@@ -34725,7 +34741,7 @@
         <v>247</v>
       </c>
       <c r="O216" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>27</v>
@@ -34813,18 +34829,18 @@
         <v>0.81407876134588997</v>
       </c>
     </row>
-    <row r="217" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C217" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E217" s="19">
         <v>1</v>
@@ -34847,7 +34863,7 @@
         <v>50</v>
       </c>
       <c r="O217" s="31" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P217" s="30" t="s">
         <v>27</v>
@@ -34935,18 +34951,18 @@
         <v>1.1216996276148128</v>
       </c>
     </row>
-    <row r="218" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C218" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E218" s="19">
         <v>1</v>
@@ -34969,7 +34985,7 @@
         <v>249</v>
       </c>
       <c r="O218" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>27</v>
@@ -35058,18 +35074,18 @@
         <v>1.1919024331549293</v>
       </c>
     </row>
-    <row r="219" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C219" s="15" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E219" s="19">
         <v>1</v>
@@ -35094,7 +35110,7 @@
         <v>51</v>
       </c>
       <c r="O219" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P219" s="6" t="s">
         <v>27</v>
@@ -35183,18 +35199,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C220" s="15" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E220" s="19">
         <v>1</v>
@@ -35210,16 +35226,16 @@
         <v>251</v>
       </c>
       <c r="L220" s="46" t="s">
-        <v>252</v>
+        <v>737</v>
       </c>
       <c r="M220" s="106">
         <v>11775750</v>
       </c>
       <c r="N220" s="46" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O220" s="45" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P220" s="46" t="s">
         <v>27</v>
@@ -35308,18 +35324,18 @@
         <v>1.4778743985473446</v>
       </c>
     </row>
-    <row r="221" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C221" s="15" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E221" s="19">
         <v>1</v>
@@ -35335,16 +35351,16 @@
         <v>251</v>
       </c>
       <c r="L221" s="6" t="s">
-        <v>252</v>
+        <v>737</v>
       </c>
       <c r="M221" s="104">
         <v>11775750</v>
       </c>
       <c r="N221" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O221" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P221" s="6" t="s">
         <v>27</v>
@@ -35433,18 +35449,18 @@
         <v>1.4352282729652679</v>
       </c>
     </row>
-    <row r="222" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C222" s="15" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E222" s="19">
         <v>1</v>
@@ -35460,14 +35476,14 @@
         <v>24</v>
       </c>
       <c r="L222" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M222" s="104"/>
       <c r="N222" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O222" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P222" s="6" t="s">
         <v>80</v>
@@ -35550,18 +35566,18 @@
         <v>2.6923076923076925</v>
       </c>
     </row>
-    <row r="223" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C223" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E223" s="19">
         <v>1</v>
@@ -35574,17 +35590,17 @@
         <v>358</v>
       </c>
       <c r="K223" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L223" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="L223" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="M223" s="104"/>
       <c r="N223" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O223" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P223" s="6" t="s">
         <v>27</v>
@@ -35667,18 +35683,18 @@
         <v>3.378378378378379</v>
       </c>
     </row>
-    <row r="224" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C224" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E224" s="19">
         <v>1</v>
@@ -35691,17 +35707,17 @@
         <v>359</v>
       </c>
       <c r="K224" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L224" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="L224" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="M224" s="104"/>
       <c r="N224" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O224" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>27</v>
@@ -35784,18 +35800,18 @@
         <v>3.378378378378379</v>
       </c>
     </row>
-    <row r="225" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C225" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E225" s="19">
         <v>1</v>
@@ -35808,17 +35824,17 @@
         <v>360</v>
       </c>
       <c r="K225" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L225" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="L225" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="M225" s="104"/>
       <c r="N225" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O225" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P225" s="6" t="s">
         <v>27</v>
@@ -35901,18 +35917,18 @@
         <v>3.3783783783783781</v>
       </c>
     </row>
-    <row r="226" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C226" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E226" s="19">
         <v>1</v>
@@ -35925,17 +35941,17 @@
         <v>361</v>
       </c>
       <c r="K226" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L226" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="L226" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="M226" s="104"/>
       <c r="N226" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O226" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>27</v>
@@ -36018,18 +36034,18 @@
         <v>3.3783783783783781</v>
       </c>
     </row>
-    <row r="227" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C227" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E227" s="19">
         <v>1</v>
@@ -36042,17 +36058,17 @@
         <v>362</v>
       </c>
       <c r="K227" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L227" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="L227" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="M227" s="104"/>
       <c r="N227" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O227" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P227" s="6" t="s">
         <v>27</v>
@@ -36135,18 +36151,18 @@
         <v>3.3783783783783781</v>
       </c>
     </row>
-    <row r="228" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C228" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E228" s="19">
         <v>1</v>
@@ -36159,17 +36175,17 @@
         <v>363</v>
       </c>
       <c r="K228" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L228" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="L228" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="M228" s="104"/>
       <c r="N228" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O228" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P228" s="6" t="s">
         <v>27</v>
@@ -36252,18 +36268,18 @@
         <v>3.3783783783783785</v>
       </c>
     </row>
-    <row r="229" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B229" s="30" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C229" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D229" s="31" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E229" s="32">
         <v>1</v>
@@ -36276,17 +36292,17 @@
         <v>364</v>
       </c>
       <c r="K229" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L229" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="L229" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="M229" s="104"/>
       <c r="N229" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O229" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P229" s="6" t="s">
         <v>27</v>
@@ -36369,18 +36385,18 @@
         <v>3.3783783783783781</v>
       </c>
     </row>
-    <row r="230" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C230" s="69" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E230" s="19">
         <v>1</v>
@@ -36393,17 +36409,17 @@
         <v>365</v>
       </c>
       <c r="K230" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L230" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="L230" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="M230" s="104"/>
       <c r="N230" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O230" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P230" s="6" t="s">
         <v>27</v>
@@ -36486,12 +36502,12 @@
         <v>3.3783783783783785</v>
       </c>
     </row>
-    <row r="231" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A231" s="98" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C231" s="64"/>
       <c r="D231" s="99"/>
@@ -36512,7 +36528,7 @@
       <c r="M231" s="104"/>
       <c r="N231" s="66"/>
       <c r="O231" s="80" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P231" s="6" t="s">
         <v>80</v>
@@ -36591,12 +36607,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="232" spans="1:42" s="29" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:42" s="29" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A232" s="101" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C232" s="64"/>
       <c r="D232" s="100"/>
@@ -36617,7 +36633,7 @@
       <c r="M232" s="104"/>
       <c r="N232" s="80"/>
       <c r="O232" s="80" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P232" s="6" t="s">
         <v>27</v>
@@ -36692,12 +36708,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="233" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C233" s="64"/>
       <c r="D233" s="44"/>
@@ -36720,7 +36736,7 @@
         <v>26</v>
       </c>
       <c r="O233" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P233" s="6" t="s">
         <v>27</v>
@@ -36795,12 +36811,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="234" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A234" s="98" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B234" s="46" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C234" s="68"/>
       <c r="D234" s="99"/>
@@ -36812,17 +36828,17 @@
       <c r="H234" s="71"/>
       <c r="I234" s="71"/>
       <c r="K234" s="6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="L234" s="6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="M234" s="104"/>
       <c r="N234" s="6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O234" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P234" s="6" t="s">
         <v>27</v>
@@ -36897,12 +36913,12 @@
         <v>2.2839969947407965</v>
       </c>
     </row>
-    <row r="235" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A235" s="98" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C235" s="67"/>
       <c r="D235" s="99"/>
@@ -36921,10 +36937,10 @@
       </c>
       <c r="M235" s="107"/>
       <c r="N235" s="66" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="O235" s="80" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P235" s="66" t="s">
         <v>27</v>
@@ -36997,12 +37013,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="236" spans="1:42" s="81" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:42" s="81" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A236" s="98" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C236" s="67"/>
       <c r="D236" s="99"/>
@@ -37021,10 +37037,10 @@
       </c>
       <c r="M236" s="104"/>
       <c r="N236" s="82" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="O236" s="84" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P236" s="82" t="s">
         <v>80</v>
@@ -37097,12 +37113,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="237" spans="1:42" s="81" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:42" s="81" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A237" s="98" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C237" s="67"/>
       <c r="D237" s="99"/>
@@ -37124,7 +37140,7 @@
         <v>26</v>
       </c>
       <c r="O237" s="84" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P237" s="82" t="s">
         <v>80</v>
@@ -37197,12 +37213,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="238" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A238" s="98" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B238" s="87" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C238" s="44"/>
       <c r="D238" s="99"/>
@@ -37214,15 +37230,15 @@
       <c r="H238" s="71"/>
       <c r="I238" s="71"/>
       <c r="K238" s="66" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="L238" s="66" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="M238" s="107"/>
       <c r="N238" s="66"/>
       <c r="O238" s="80" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P238" s="66"/>
       <c r="Q238" s="95">
@@ -37297,12 +37313,12 @@
         <v>3.2456799398948157</v>
       </c>
     </row>
-    <row r="239" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A239" s="98" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B239" s="72" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C239" s="60"/>
       <c r="D239" s="99"/>
@@ -37317,14 +37333,14 @@
         <v>231</v>
       </c>
       <c r="L239" s="66" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="M239" s="107"/>
       <c r="N239" s="66" t="s">
         <v>26</v>
       </c>
       <c r="O239" s="80" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P239" s="66" t="s">
         <v>27</v>
@@ -37397,16 +37413,18 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="240" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A240" s="98" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B240" s="72" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C240" s="66"/>
       <c r="D240" s="99"/>
-      <c r="E240" s="66"/>
+      <c r="E240" s="19">
+        <v>1</v>
+      </c>
       <c r="F240" s="44"/>
       <c r="G240" s="44"/>
       <c r="H240" s="44"/>
@@ -37422,7 +37440,7 @@
         <v>26</v>
       </c>
       <c r="O240" s="112" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P240" s="66" t="s">
         <v>27</v>
@@ -37495,24 +37513,26 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="241" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B241" s="72" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D241" s="44"/>
-      <c r="E241" s="60"/>
+      <c r="E241" s="19">
+        <v>1</v>
+      </c>
       <c r="F241" s="44"/>
       <c r="G241" s="44"/>
       <c r="H241" s="44"/>
       <c r="I241" s="44"/>
       <c r="K241" s="66" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="L241" s="66" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="M241" s="109"/>
       <c r="N241" s="110" t="s">
@@ -37862,11 +37882,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA5B41D-754B-41F4-AE3E-2CEADDCF305E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
   </sheetData>

--- a/areas_land_bank_com_id.xlsx
+++ b/areas_land_bank_com_id.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EsteLivro" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Departamento Controladoria\3 - BT 360º\Landbank\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.castro\Documents\01 Profissional\Buriti Empreendimentos\Repositórios\land-bank-mapa-brasil-terrenos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2629E1CF-09DD-4F32-A64D-AB17E500600A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5256DE6A-6317-4F17-9C7A-ABDC3532BCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="960" windowWidth="29040" windowHeight="15720" xr2:uid="{2D7381EB-1656-47BB-A82F-14AB3B13CCCD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D7381EB-1656-47BB-A82F-14AB3B13CCCD}"/>
   </bookViews>
   <sheets>
     <sheet name="AREAS" sheetId="1" r:id="rId1"/>
@@ -5306,7 +5306,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="737">
   <si>
     <t>Nome</t>
   </si>
@@ -7529,17 +7529,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="11">
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0%_);\(0.0%\);0.0%_);@_)"/>
-    <numFmt numFmtId="165" formatCode="0.00%_);\(0.00%\);0.00%_);@_)"/>
-    <numFmt numFmtId="166" formatCode="0%_);\(0%\);0%_);@_)"/>
-    <numFmt numFmtId="167" formatCode="[$-416]mmm\-yy;@"/>
-    <numFmt numFmtId="168" formatCode="&quot;Ativo&quot;;\-#,##0;[Red]&quot;Inativo&quot;"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="0.0%"/>
-    <numFmt numFmtId="172" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.0%_);\(0.0%\);0.0%_);@_)"/>
+    <numFmt numFmtId="167" formatCode="0.00%_);\(0.00%\);0.00%_);@_)"/>
+    <numFmt numFmtId="168" formatCode="0%_);\(0%\);0%_);@_)"/>
+    <numFmt numFmtId="169" formatCode="[$-416]mmm\-yy;@"/>
+    <numFmt numFmtId="170" formatCode="&quot;Ativo&quot;;\-#,##0;[Red]&quot;Inativo&quot;"/>
+    <numFmt numFmtId="171" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="173" formatCode="0.0%"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -7866,11 +7866,11 @@
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7893,25 +7893,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7923,19 +7923,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="3" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -7944,10 +7944,10 @@
     <xf numFmtId="37" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -7959,37 +7959,37 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7998,49 +7998,49 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="6" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="6" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="3" fillId="3" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -8049,13 +8049,13 @@
     <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="8" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="8" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="4" fillId="8" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8068,34 +8068,34 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="170" fontId="4" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="172" fontId="4" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="13" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -8132,7 +8132,7 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -8157,8 +8157,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8169,13 +8168,13 @@
     <xf numFmtId="10" fontId="11" fillId="3" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
     <cellStyle name="Moeda" xfId="3" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentagem" xfId="4" builtinId="5"/>
+    <cellStyle name="Percentagem" xfId="4" builtinId="5"/>
     <cellStyle name="Vírgula" xfId="2" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -8196,10 +8195,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8521,49 +8516,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB1E7F9-B7E0-4EE5-A96E-08F27078CA81}">
   <sheetPr codeName="Folha1"/>
   <dimension ref="A1:AP241"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" customWidth="1"/>
-    <col min="2" max="2" width="58.453125" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7265625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="22.453125" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.54296875" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" customWidth="1"/>
-    <col min="11" max="11" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.6328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.26953125" style="77" customWidth="1"/>
-    <col min="14" max="14" width="53.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.08984375" style="27" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.81640625" customWidth="1"/>
-    <col min="20" max="20" width="11.54296875" customWidth="1"/>
-    <col min="21" max="21" width="11.26953125" customWidth="1"/>
+    <col min="1" max="1" width="15.21875" customWidth="1"/>
+    <col min="2" max="2" width="58.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="22.44140625" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.21875" style="77" customWidth="1"/>
+    <col min="14" max="14" width="53.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.77734375" customWidth="1"/>
+    <col min="20" max="20" width="11.5546875" customWidth="1"/>
+    <col min="21" max="21" width="11.21875" customWidth="1"/>
     <col min="22" max="22" width="14" customWidth="1"/>
-    <col min="23" max="23" width="10.26953125" customWidth="1"/>
-    <col min="24" max="24" width="10.81640625" customWidth="1"/>
-    <col min="25" max="25" width="12.7265625" customWidth="1"/>
+    <col min="23" max="23" width="10.21875" customWidth="1"/>
+    <col min="24" max="24" width="10.77734375" customWidth="1"/>
+    <col min="25" max="25" width="12.77734375" customWidth="1"/>
     <col min="26" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="11.54296875" customWidth="1"/>
-    <col min="28" max="28" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.81640625" customWidth="1"/>
-    <col min="31" max="31" width="11.1796875" customWidth="1"/>
-    <col min="32" max="32" width="12.26953125" customWidth="1"/>
-    <col min="33" max="33" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.54296875" customWidth="1"/>
+    <col min="27" max="27" width="11.5546875" customWidth="1"/>
+    <col min="28" max="28" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.77734375" customWidth="1"/>
+    <col min="31" max="31" width="11.21875" customWidth="1"/>
+    <col min="32" max="32" width="12.21875" customWidth="1"/>
+    <col min="33" max="33" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="9.5546875" customWidth="1"/>
     <col min="37" max="38" width="9" customWidth="1"/>
     <col min="39" max="39" width="16" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="12.81640625" customWidth="1"/>
-    <col min="42" max="42" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="12.77734375" customWidth="1"/>
+    <col min="42" max="42" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="52" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>568</v>
       </c>
@@ -8691,7 +8686,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="2" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
         <v>576</v>
       </c>
@@ -8810,7 +8805,7 @@
         <v>3.3809797786673061</v>
       </c>
     </row>
-    <row r="3" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="64" t="s">
         <v>577</v>
       </c>
@@ -8931,7 +8926,7 @@
         <v>4.8097271922736544</v>
       </c>
     </row>
-    <row r="4" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="64" t="s">
         <v>577</v>
       </c>
@@ -9052,7 +9047,7 @@
         <v>5.3580126643935699</v>
       </c>
     </row>
-    <row r="5" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="64" t="s">
         <v>578</v>
       </c>
@@ -9171,7 +9166,7 @@
         <v>4.5078888054094666</v>
       </c>
     </row>
-    <row r="6" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="64" t="s">
         <v>579</v>
       </c>
@@ -9290,7 +9285,7 @@
         <v>4.5078888054094675</v>
       </c>
     </row>
-    <row r="7" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="64" t="s">
         <v>579</v>
       </c>
@@ -9409,7 +9404,7 @@
         <v>4.5078888054094666</v>
       </c>
     </row>
-    <row r="8" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A8" s="64" t="s">
         <v>579</v>
       </c>
@@ -9528,7 +9523,7 @@
         <v>4.5078888054094683</v>
       </c>
     </row>
-    <row r="9" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A9" s="64" t="s">
         <v>579</v>
       </c>
@@ -9647,7 +9642,7 @@
         <v>4.5078888054094683</v>
       </c>
     </row>
-    <row r="10" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="64" t="s">
         <v>579</v>
       </c>
@@ -9766,7 +9761,7 @@
         <v>4.5078888054094683</v>
       </c>
     </row>
-    <row r="11" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="64" t="s">
         <v>570</v>
       </c>
@@ -9883,7 +9878,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A12" s="64" t="s">
         <v>571</v>
       </c>
@@ -10000,7 +9995,7 @@
         <v>3.2306536438767841</v>
       </c>
     </row>
-    <row r="13" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="64" t="s">
         <v>572</v>
       </c>
@@ -10117,7 +10112,7 @@
         <v>4.883546205860255</v>
       </c>
     </row>
-    <row r="14" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A14" s="64" t="s">
         <v>572</v>
       </c>
@@ -10234,7 +10229,7 @@
         <v>4.883546205860255</v>
       </c>
     </row>
-    <row r="15" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A15" s="64" t="s">
         <v>573</v>
       </c>
@@ -10351,7 +10346,7 @@
         <v>3.7565740045078888</v>
       </c>
     </row>
-    <row r="16" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
         <v>574</v>
       </c>
@@ -10468,7 +10463,7 @@
         <v>3.7565740045078897</v>
       </c>
     </row>
-    <row r="17" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A17" s="64" t="s">
         <v>575</v>
       </c>
@@ -10585,7 +10580,7 @@
         <v>3.7565740045078893</v>
       </c>
     </row>
-    <row r="18" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="64" t="s">
         <v>580</v>
       </c>
@@ -10702,7 +10697,7 @@
         <v>3.230653643876785</v>
       </c>
     </row>
-    <row r="19" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="64" t="s">
         <v>581</v>
       </c>
@@ -10819,7 +10814,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="20" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A20" s="64" t="s">
         <v>581</v>
       </c>
@@ -10936,7 +10931,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="21" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A21" s="64" t="s">
         <v>581</v>
       </c>
@@ -11053,7 +11048,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="22" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A22" s="64" t="s">
         <v>581</v>
       </c>
@@ -11170,7 +11165,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="23" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A23" s="64" t="s">
         <v>581</v>
       </c>
@@ -11287,7 +11282,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="24" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A24" s="64" t="s">
         <v>581</v>
       </c>
@@ -11404,7 +11399,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="25" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A25" s="64" t="s">
         <v>581</v>
       </c>
@@ -11521,7 +11516,7 @@
         <v>2.9301277235161534</v>
       </c>
     </row>
-    <row r="26" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A26" s="64" t="s">
         <v>582</v>
       </c>
@@ -11640,7 +11635,7 @@
         <v>0.83115017886351839</v>
       </c>
     </row>
-    <row r="27" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A27" s="64" t="s">
         <v>583</v>
       </c>
@@ -11757,7 +11752,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="28" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A28" s="64" t="s">
         <v>583</v>
       </c>
@@ -11873,7 +11868,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="29" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A29" s="64" t="s">
         <v>583</v>
       </c>
@@ -11990,7 +11985,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="30" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A30" s="64" t="s">
         <v>583</v>
       </c>
@@ -12107,7 +12102,7 @@
         <v>4.140625</v>
       </c>
     </row>
-    <row r="31" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A31" s="64" t="s">
         <v>583</v>
       </c>
@@ -12224,7 +12219,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="32" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A32" s="64" t="s">
         <v>583</v>
       </c>
@@ -12341,7 +12336,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="33" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A33" s="64" t="s">
         <v>583</v>
       </c>
@@ -12458,7 +12453,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="34" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A34" s="64" t="s">
         <v>583</v>
       </c>
@@ -12575,7 +12570,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="35" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A35" s="64" t="s">
         <v>583</v>
       </c>
@@ -12692,7 +12687,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="36" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A36" s="64" t="s">
         <v>583</v>
       </c>
@@ -12809,7 +12804,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="37" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A37" s="64" t="s">
         <v>583</v>
       </c>
@@ -12926,7 +12921,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="38" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A38" s="64" t="s">
         <v>583</v>
       </c>
@@ -13043,7 +13038,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="39" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A39" s="64" t="s">
         <v>583</v>
       </c>
@@ -13160,7 +13155,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="40" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A40" s="64" t="s">
         <v>583</v>
       </c>
@@ -13277,7 +13272,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="41" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A41" s="64" t="s">
         <v>583</v>
       </c>
@@ -13394,7 +13389,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="42" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A42" s="64" t="s">
         <v>583</v>
       </c>
@@ -13511,7 +13506,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="43" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="64" t="s">
         <v>583</v>
       </c>
@@ -13628,7 +13623,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="44" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="64" t="s">
         <v>583</v>
       </c>
@@ -13745,7 +13740,7 @@
         <v>4.296875</v>
       </c>
     </row>
-    <row r="45" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A45" s="64" t="s">
         <v>583</v>
       </c>
@@ -13862,7 +13857,7 @@
         <v>3.90625</v>
       </c>
     </row>
-    <row r="46" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A46" s="64" t="s">
         <v>584</v>
       </c>
@@ -13985,7 +13980,7 @@
         <v>1.5033333068541384</v>
       </c>
     </row>
-    <row r="47" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A47" s="64" t="s">
         <v>584</v>
       </c>
@@ -14108,7 +14103,7 @@
         <v>1.5033333068541381</v>
       </c>
     </row>
-    <row r="48" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A48" s="64" t="s">
         <v>584</v>
       </c>
@@ -14231,7 +14226,7 @@
         <v>1.1881369949110563</v>
       </c>
     </row>
-    <row r="49" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A49" s="64" t="s">
         <v>584</v>
       </c>
@@ -14354,7 +14349,7 @@
         <v>1.1629101414416052</v>
       </c>
     </row>
-    <row r="50" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A50" s="64" t="s">
         <v>585</v>
       </c>
@@ -14470,7 +14465,7 @@
         <v>3.9062500000000004</v>
       </c>
     </row>
-    <row r="51" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A51" s="64" t="s">
         <v>587</v>
       </c>
@@ -14587,7 +14582,7 @@
         <v>4.6875000000000009</v>
       </c>
     </row>
-    <row r="52" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A52" s="64" t="s">
         <v>681</v>
       </c>
@@ -14704,7 +14699,7 @@
         <v>3.2407407407407409</v>
       </c>
     </row>
-    <row r="53" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A53" s="64" t="s">
         <v>586</v>
       </c>
@@ -14821,7 +14816,7 @@
         <v>3.2407407407407409</v>
       </c>
     </row>
-    <row r="54" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A54" s="64" t="s">
         <v>588</v>
       </c>
@@ -14938,7 +14933,7 @@
         <v>6.2499999999999991</v>
       </c>
     </row>
-    <row r="55" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A55" s="64" t="s">
         <v>589</v>
       </c>
@@ -15056,7 +15051,7 @@
         <v>3.7037037037037033</v>
       </c>
     </row>
-    <row r="56" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A56" s="64" t="s">
         <v>591</v>
       </c>
@@ -15181,7 +15176,7 @@
         <v>2.0794444816235882</v>
       </c>
     </row>
-    <row r="57" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A57" s="64" t="s">
         <v>591</v>
       </c>
@@ -15305,7 +15300,7 @@
         <v>0.682062825375507</v>
       </c>
     </row>
-    <row r="58" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A58" s="64" t="s">
         <v>590</v>
       </c>
@@ -15428,7 +15423,7 @@
         <v>1.584067227618178</v>
       </c>
     </row>
-    <row r="59" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A59" s="64" t="s">
         <v>592</v>
       </c>
@@ -15551,7 +15546,7 @@
         <v>1.2626874796242238</v>
       </c>
     </row>
-    <row r="60" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A60" s="64" t="s">
         <v>593</v>
       </c>
@@ -15674,7 +15669,7 @@
         <v>1.165542478997921</v>
       </c>
     </row>
-    <row r="61" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A61" s="64" t="s">
         <v>593</v>
       </c>
@@ -15797,7 +15792,7 @@
         <v>1.1453025708336924</v>
       </c>
     </row>
-    <row r="62" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A62" s="64" t="s">
         <v>594</v>
       </c>
@@ -15920,7 +15915,7 @@
         <v>1.0499523822058021</v>
       </c>
     </row>
-    <row r="63" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A63" s="64" t="s">
         <v>595</v>
       </c>
@@ -16037,7 +16032,7 @@
         <v>3.9384920139218527</v>
       </c>
     </row>
-    <row r="64" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A64" s="64" t="s">
         <v>595</v>
       </c>
@@ -16154,7 +16149,7 @@
         <v>3.9384920139218527</v>
       </c>
     </row>
-    <row r="65" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A65" s="64" t="s">
         <v>595</v>
       </c>
@@ -16271,7 +16266,7 @@
         <v>3.9384920139218527</v>
       </c>
     </row>
-    <row r="66" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A66" s="64" t="s">
         <v>596</v>
       </c>
@@ -16390,7 +16385,7 @@
         <v>3.5833333333333335</v>
       </c>
     </row>
-    <row r="67" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A67" s="64" t="s">
         <v>597</v>
       </c>
@@ -16509,7 +16504,7 @@
         <v>3.8333333333333335</v>
       </c>
     </row>
-    <row r="68" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A68" s="64" t="s">
         <v>598</v>
       </c>
@@ -16628,7 +16623,7 @@
         <v>3.5833333333333335</v>
       </c>
     </row>
-    <row r="69" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A69" s="64" t="s">
         <v>598</v>
       </c>
@@ -16747,7 +16742,7 @@
         <v>3.5833333333333335</v>
       </c>
     </row>
-    <row r="70" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A70" s="64" t="s">
         <v>599</v>
       </c>
@@ -16871,7 +16866,7 @@
         <v>1.6840907460634127</v>
       </c>
     </row>
-    <row r="71" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A71" s="64" t="s">
         <v>600</v>
       </c>
@@ -16995,7 +16990,7 @@
         <v>1.7104564330775569</v>
       </c>
     </row>
-    <row r="72" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A72" s="64" t="s">
         <v>600</v>
       </c>
@@ -17119,7 +17114,7 @@
         <v>1.6579735962048303</v>
       </c>
     </row>
-    <row r="73" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A73" s="64" t="s">
         <v>601</v>
       </c>
@@ -17241,7 +17236,7 @@
         <v>2.5287610566591523</v>
       </c>
     </row>
-    <row r="74" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A74" s="64" t="s">
         <v>601</v>
       </c>
@@ -17363,7 +17358,7 @@
         <v>2.4793535855822042</v>
       </c>
     </row>
-    <row r="75" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A75" s="64" t="s">
         <v>602</v>
       </c>
@@ -17488,7 +17483,7 @@
         <v>1.890388055872956</v>
       </c>
     </row>
-    <row r="76" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A76" s="64" t="s">
         <v>602</v>
       </c>
@@ -17613,7 +17608,7 @@
         <v>1.8605083275965164</v>
       </c>
     </row>
-    <row r="77" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A77" s="64" t="s">
         <v>603</v>
       </c>
@@ -17738,7 +17733,7 @@
         <v>1.8523399895648596</v>
       </c>
     </row>
-    <row r="78" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A78" s="64" t="s">
         <v>603</v>
       </c>
@@ -17863,7 +17858,7 @@
         <v>1.7669888872138106</v>
       </c>
     </row>
-    <row r="79" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A79" s="64" t="s">
         <v>604</v>
       </c>
@@ -17986,7 +17981,7 @@
         <v>0.64100515446669049</v>
       </c>
     </row>
-    <row r="80" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A80" s="64" t="s">
         <v>604</v>
       </c>
@@ -18109,7 +18104,7 @@
         <v>0.62670976763932151</v>
       </c>
     </row>
-    <row r="81" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A81" s="64" t="s">
         <v>605</v>
       </c>
@@ -18232,7 +18227,7 @@
         <v>0.76883870310314895</v>
       </c>
     </row>
-    <row r="82" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A82" s="64" t="s">
         <v>606</v>
       </c>
@@ -18355,7 +18350,7 @@
         <v>1.4269848890125221</v>
       </c>
     </row>
-    <row r="83" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A83" s="64" t="s">
         <v>607</v>
       </c>
@@ -18478,7 +18473,7 @@
         <v>0.83525452781953513</v>
       </c>
     </row>
-    <row r="84" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A84" s="64" t="s">
         <v>607</v>
       </c>
@@ -18601,7 +18596,7 @@
         <v>0.81799598953212038</v>
       </c>
     </row>
-    <row r="85" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A85" s="64" t="s">
         <v>607</v>
       </c>
@@ -18724,7 +18719,7 @@
         <v>0.78388138912123639</v>
       </c>
     </row>
-    <row r="86" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A86" s="64" t="s">
         <v>608</v>
       </c>
@@ -18847,7 +18842,7 @@
         <v>1.1501266268686077</v>
       </c>
     </row>
-    <row r="87" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A87" s="64" t="s">
         <v>609</v>
       </c>
@@ -18972,7 +18967,7 @@
         <v>0.23299756298435631</v>
       </c>
     </row>
-    <row r="88" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A88" s="64" t="s">
         <v>609</v>
       </c>
@@ -19097,7 +19092,7 @@
         <v>1.2387943662501089</v>
       </c>
     </row>
-    <row r="89" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A89" s="64" t="s">
         <v>610</v>
       </c>
@@ -19220,7 +19215,7 @@
         <v>1.5149909654595908</v>
       </c>
     </row>
-    <row r="90" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A90" s="64" t="s">
         <v>682</v>
       </c>
@@ -19343,7 +19338,7 @@
         <v>1.2046020634661616</v>
       </c>
     </row>
-    <row r="91" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A91" s="64" t="s">
         <v>611</v>
       </c>
@@ -19466,7 +19461,7 @@
         <v>1.2072988815514583</v>
       </c>
     </row>
-    <row r="92" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A92" s="64" t="s">
         <v>611</v>
       </c>
@@ -19589,7 +19584,7 @@
         <v>1.4090811331942312</v>
       </c>
     </row>
-    <row r="93" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A93" s="64" t="s">
         <v>611</v>
       </c>
@@ -19712,7 +19707,7 @@
         <v>1.1397336017719824</v>
       </c>
     </row>
-    <row r="94" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A94" s="64" t="s">
         <v>611</v>
       </c>
@@ -19835,7 +19830,7 @@
         <v>1.0959959051299162</v>
       </c>
     </row>
-    <row r="95" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A95" s="64" t="s">
         <v>611</v>
       </c>
@@ -19958,7 +19953,7 @@
         <v>1.0527200029561115</v>
       </c>
     </row>
-    <row r="96" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A96" s="64" t="s">
         <v>612</v>
       </c>
@@ -20083,7 +20078,7 @@
         <v>2.1202973983797322</v>
       </c>
     </row>
-    <row r="97" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A97" s="64" t="s">
         <v>613</v>
       </c>
@@ -20208,7 +20203,7 @@
         <v>2.0772596632135061</v>
       </c>
     </row>
-    <row r="98" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A98" s="64" t="s">
         <v>615</v>
       </c>
@@ -20331,7 +20326,7 @@
         <v>1.5361651825388483</v>
       </c>
     </row>
-    <row r="99" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A99" s="64" t="s">
         <v>615</v>
       </c>
@@ -20454,7 +20449,7 @@
         <v>1.5065784699927574</v>
       </c>
     </row>
-    <row r="100" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A100" s="64" t="s">
         <v>615</v>
       </c>
@@ -20577,7 +20572,7 @@
         <v>1.4478450040383797</v>
       </c>
     </row>
-    <row r="101" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A101" s="64" t="s">
         <v>614</v>
       </c>
@@ -20700,7 +20695,7 @@
         <v>1.0994472988394468</v>
       </c>
     </row>
-    <row r="102" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A102" s="64" t="s">
         <v>614</v>
       </c>
@@ -20823,7 +20818,7 @@
         <v>1.0586916755795146</v>
       </c>
     </row>
-    <row r="103" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A103" s="64" t="s">
         <v>616</v>
       </c>
@@ -20946,7 +20941,7 @@
         <v>1.6691380981214541</v>
       </c>
     </row>
-    <row r="104" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A104" s="64" t="s">
         <v>616</v>
       </c>
@@ -21069,7 +21064,7 @@
         <v>1.6065963825333243</v>
       </c>
     </row>
-    <row r="105" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A105" s="64" t="s">
         <v>617</v>
       </c>
@@ -21192,7 +21187,7 @@
         <v>0.90690345120653837</v>
       </c>
     </row>
-    <row r="106" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A106" s="64" t="s">
         <v>618</v>
       </c>
@@ -21315,7 +21310,7 @@
         <v>0.87259450365707092</v>
       </c>
     </row>
-    <row r="107" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A107" s="64" t="s">
         <v>619</v>
       </c>
@@ -21438,7 +21433,7 @@
         <v>0.83860953776262182</v>
       </c>
     </row>
-    <row r="108" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A108" s="64" t="s">
         <v>619</v>
       </c>
@@ -21561,7 +21556,7 @@
         <v>0.80502313984963059</v>
       </c>
     </row>
-    <row r="109" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A109" s="64" t="s">
         <v>619</v>
       </c>
@@ -21684,7 +21679,7 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="110" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A110" s="64" t="s">
         <v>619</v>
       </c>
@@ -21807,7 +21802,7 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="111" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A111" s="64" t="s">
         <v>619</v>
       </c>
@@ -21930,7 +21925,7 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="112" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A112" s="64" t="s">
         <v>619</v>
       </c>
@@ -22053,7 +22048,7 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="113" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A113" s="64" t="s">
         <v>619</v>
       </c>
@@ -22176,7 +22171,7 @@
         <v>2.024472392638037</v>
       </c>
     </row>
-    <row r="114" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A114" s="64" t="s">
         <v>620</v>
       </c>
@@ -22299,7 +22294,7 @@
         <v>0.73245167478536033</v>
       </c>
     </row>
-    <row r="115" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A115" s="64" t="s">
         <v>621</v>
       </c>
@@ -22422,7 +22417,7 @@
         <v>0.70127185350915722</v>
       </c>
     </row>
-    <row r="116" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A116" s="64" t="s">
         <v>621</v>
       </c>
@@ -22545,7 +22540,7 @@
         <v>0.6706877524292354</v>
       </c>
     </row>
-    <row r="117" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A117" s="64" t="s">
         <v>621</v>
       </c>
@@ -22668,7 +22663,7 @@
         <v>0.64075267145675929</v>
       </c>
     </row>
-    <row r="118" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A118" s="64" t="s">
         <v>621</v>
       </c>
@@ -22791,7 +22786,7 @@
         <v>0.61151467271213211</v>
       </c>
     </row>
-    <row r="119" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A119" s="64" t="s">
         <v>621</v>
       </c>
@@ -22914,7 +22909,7 @@
         <v>1.9492775508164899</v>
       </c>
     </row>
-    <row r="120" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A120" s="64" t="s">
         <v>622</v>
       </c>
@@ -23037,7 +23032,7 @@
         <v>1.2292115404911319</v>
       </c>
     </row>
-    <row r="121" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A121" s="64" t="s">
         <v>623</v>
       </c>
@@ -23160,7 +23155,7 @@
         <v>1.2413630323963301</v>
       </c>
     </row>
-    <row r="122" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A122" s="64" t="s">
         <v>624</v>
       </c>
@@ -23283,7 +23278,7 @@
         <v>1.2561653093904881</v>
       </c>
     </row>
-    <row r="123" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A123" s="64" t="s">
         <v>625</v>
       </c>
@@ -23406,7 +23401,7 @@
         <v>1.2113560025023844</v>
       </c>
     </row>
-    <row r="124" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A124" s="64" t="s">
         <v>626</v>
       </c>
@@ -23529,7 +23524,7 @@
         <v>2.613496932515337</v>
       </c>
     </row>
-    <row r="125" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A125" s="64" t="s">
         <v>626</v>
       </c>
@@ -23652,7 +23647,7 @@
         <v>2.6134969325153379</v>
       </c>
     </row>
-    <row r="126" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A126" s="64" t="s">
         <v>627</v>
       </c>
@@ -23775,7 +23770,7 @@
         <v>1.3821716627734322</v>
       </c>
     </row>
-    <row r="127" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A127" s="64" t="s">
         <v>628</v>
       </c>
@@ -23898,7 +23893,7 @@
         <v>1.3508286832235206</v>
       </c>
     </row>
-    <row r="128" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A128" s="64" t="s">
         <v>628</v>
       </c>
@@ -24021,7 +24016,7 @@
         <v>1.3273996567144928</v>
       </c>
     </row>
-    <row r="129" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A129" s="64" t="s">
         <v>629</v>
       </c>
@@ -24144,7 +24139,7 @@
         <v>1.1478379123898736</v>
       </c>
     </row>
-    <row r="130" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A130" s="64" t="s">
         <v>630</v>
       </c>
@@ -24267,7 +24262,7 @@
         <v>1.1873209657838852</v>
       </c>
     </row>
-    <row r="131" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A131" s="64" t="s">
         <v>630</v>
       </c>
@@ -24390,7 +24385,7 @@
         <v>1.1478379123898732</v>
       </c>
     </row>
-    <row r="132" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A132" s="64" t="s">
         <v>631</v>
       </c>
@@ -24513,7 +24508,7 @@
         <v>1.1697737528257561</v>
       </c>
     </row>
-    <row r="133" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A133" s="64" t="s">
         <v>632</v>
       </c>
@@ -24636,7 +24631,7 @@
         <v>1.1478379123898734</v>
       </c>
     </row>
-    <row r="134" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A134" s="64" t="s">
         <v>633</v>
       </c>
@@ -24759,7 +24754,7 @@
         <v>1.1917791466511929</v>
       </c>
     </row>
-    <row r="135" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A135" s="64" t="s">
         <v>633</v>
       </c>
@@ -24882,7 +24877,7 @@
         <v>1.1697737528257561</v>
       </c>
     </row>
-    <row r="136" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A136" s="64" t="s">
         <v>633</v>
       </c>
@@ -25005,7 +25000,7 @@
         <v>1.1478379123898732</v>
       </c>
     </row>
-    <row r="137" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A137" s="64" t="s">
         <v>634</v>
       </c>
@@ -25127,7 +25122,7 @@
         <v>1.100201380402013</v>
       </c>
     </row>
-    <row r="138" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A138" s="64" t="s">
         <v>634</v>
       </c>
@@ -25244,7 +25239,7 @@
         <v>3.4285714285714284</v>
       </c>
     </row>
-    <row r="139" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A139" s="64" t="s">
         <v>634</v>
       </c>
@@ -25366,7 +25361,7 @@
         <v>1.5534532233799874</v>
       </c>
     </row>
-    <row r="140" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A140" s="64" t="s">
         <v>634</v>
       </c>
@@ -25483,7 +25478,7 @@
         <v>3.4285714285714284</v>
       </c>
     </row>
-    <row r="141" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A141" s="64" t="s">
         <v>635</v>
       </c>
@@ -25606,7 +25601,7 @@
         <v>1.3402722285622568</v>
       </c>
     </row>
-    <row r="142" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A142" s="64" t="s">
         <v>635</v>
       </c>
@@ -25729,7 +25724,7 @@
         <v>1.1069472501692708</v>
       </c>
     </row>
-    <row r="143" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A143" s="64" t="s">
         <v>635</v>
       </c>
@@ -25852,7 +25847,7 @@
         <v>1.3096934841312509</v>
       </c>
     </row>
-    <row r="144" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A144" s="64" t="s">
         <v>636</v>
       </c>
@@ -25975,7 +25970,7 @@
         <v>1.2649802836537249</v>
       </c>
     </row>
-    <row r="145" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A145" s="64" t="s">
         <v>637</v>
       </c>
@@ -26098,7 +26093,7 @@
         <v>1.242648133063637</v>
       </c>
     </row>
-    <row r="146" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A146" s="64" t="s">
         <v>638</v>
       </c>
@@ -26221,7 +26216,7 @@
         <v>0.90074899958421728</v>
       </c>
     </row>
-    <row r="147" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A147" s="64" t="s">
         <v>638</v>
       </c>
@@ -26344,7 +26339,7 @@
         <v>0.86471997316517379</v>
       </c>
     </row>
-    <row r="148" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A148" s="64" t="s">
         <v>638</v>
       </c>
@@ -26467,7 +26462,7 @@
         <v>0.8291908931927453</v>
       </c>
     </row>
-    <row r="149" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A149" s="64" t="s">
         <v>638</v>
       </c>
@@ -26590,7 +26585,7 @@
         <v>0.82391222601076908</v>
       </c>
     </row>
-    <row r="150" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A150" s="64" t="s">
         <v>638</v>
       </c>
@@ -26713,7 +26708,7 @@
         <v>1.307592918802565</v>
       </c>
     </row>
-    <row r="151" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A151" s="64" t="s">
         <v>638</v>
       </c>
@@ -26836,7 +26831,7 @@
         <v>1.259710619839457</v>
       </c>
     </row>
-    <row r="152" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A152" s="64" t="s">
         <v>638</v>
       </c>
@@ -26953,7 +26948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A153" s="64" t="s">
         <v>638</v>
       </c>
@@ -27076,7 +27071,7 @@
         <v>1.5199940748831153</v>
       </c>
     </row>
-    <row r="154" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A154" s="64" t="s">
         <v>638</v>
       </c>
@@ -27199,7 +27194,7 @@
         <v>0.94841385595929528</v>
       </c>
     </row>
-    <row r="155" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A155" s="64" t="s">
         <v>639</v>
       </c>
@@ -27322,7 +27317,7 @@
         <v>2.001711919813113</v>
       </c>
     </row>
-    <row r="156" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A156" s="64" t="s">
         <v>639</v>
       </c>
@@ -27445,7 +27440,7 @@
         <v>2.7873981870831179</v>
       </c>
     </row>
-    <row r="157" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A157" s="64" t="s">
         <v>639</v>
       </c>
@@ -27568,7 +27563,7 @@
         <v>1.8835744163813872</v>
       </c>
     </row>
-    <row r="158" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A158" s="64" t="s">
         <v>684</v>
       </c>
@@ -27691,7 +27686,7 @@
         <v>1.3178084967631456</v>
       </c>
     </row>
-    <row r="159" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A159" s="64" t="s">
         <v>683</v>
       </c>
@@ -27814,7 +27809,7 @@
         <v>1.3730404099510281</v>
       </c>
     </row>
-    <row r="160" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A160" s="64" t="s">
         <v>640</v>
       </c>
@@ -27937,7 +27932,7 @@
         <v>1.3848749369337743</v>
       </c>
     </row>
-    <row r="161" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A161" s="64" t="s">
         <v>641</v>
       </c>
@@ -28060,7 +28055,7 @@
         <v>1.3585676614027813</v>
       </c>
     </row>
-    <row r="162" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A162" s="64" t="s">
         <v>642</v>
       </c>
@@ -28183,7 +28178,7 @@
         <v>1.372740519264412</v>
       </c>
     </row>
-    <row r="163" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A163" s="64" t="s">
         <v>643</v>
       </c>
@@ -28306,7 +28301,7 @@
         <v>1.3209122633460484</v>
       </c>
     </row>
-    <row r="164" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A164" s="64" t="s">
         <v>644</v>
       </c>
@@ -28429,7 +28424,7 @@
         <v>4.2857142857142856</v>
       </c>
     </row>
-    <row r="165" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A165" s="64" t="s">
         <v>645</v>
       </c>
@@ -28552,7 +28547,7 @@
         <v>0.89768559755339483</v>
       </c>
     </row>
-    <row r="166" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A166" s="64" t="s">
         <v>646</v>
       </c>
@@ -28675,7 +28670,7 @@
         <v>0.84488056240319498</v>
       </c>
     </row>
-    <row r="167" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A167" s="64" t="s">
         <v>647</v>
       </c>
@@ -28798,7 +28793,7 @@
         <v>0.79115858344502654</v>
       </c>
     </row>
-    <row r="168" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A168" s="64" t="s">
         <v>648</v>
       </c>
@@ -28921,7 +28916,7 @@
         <v>0.77406888933587614</v>
       </c>
     </row>
-    <row r="169" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A169" s="64" t="s">
         <v>649</v>
       </c>
@@ -29044,7 +29039,7 @@
         <v>0.95007407159306967</v>
       </c>
     </row>
-    <row r="170" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A170" s="64" t="s">
         <v>650</v>
       </c>
@@ -29167,7 +29162,7 @@
         <v>1.6504684110205614</v>
       </c>
     </row>
-    <row r="171" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A171" s="64" t="s">
         <v>650</v>
       </c>
@@ -29290,7 +29285,7 @@
         <v>1.5959766651655141</v>
       </c>
     </row>
-    <row r="172" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A172" s="64" t="s">
         <v>650</v>
       </c>
@@ -29413,7 +29408,7 @@
         <v>1.541459129098488</v>
       </c>
     </row>
-    <row r="173" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A173" s="64" t="s">
         <v>650</v>
       </c>
@@ -29536,7 +29531,7 @@
         <v>1.4870446603133847</v>
       </c>
     </row>
-    <row r="174" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A174" s="64" t="s">
         <v>651</v>
       </c>
@@ -29659,7 +29654,7 @@
         <v>1.29803634535601</v>
       </c>
     </row>
-    <row r="175" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A175" s="64" t="s">
         <v>652</v>
       </c>
@@ -29782,7 +29777,7 @@
         <v>1.2979593269679877</v>
       </c>
     </row>
-    <row r="176" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A176" s="64" t="s">
         <v>653</v>
       </c>
@@ -29905,7 +29900,7 @@
         <v>1.6263477020219728</v>
       </c>
     </row>
-    <row r="177" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A177" s="64" t="s">
         <v>654</v>
       </c>
@@ -30028,7 +30023,7 @@
         <v>1.2592386722239013</v>
       </c>
     </row>
-    <row r="178" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A178" s="64" t="s">
         <v>655</v>
       </c>
@@ -30151,7 +30146,7 @@
         <v>1.4641218723147973</v>
       </c>
     </row>
-    <row r="179" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A179" s="64" t="s">
         <v>656</v>
       </c>
@@ -30274,7 +30269,7 @@
         <v>1.6857797571068185</v>
       </c>
     </row>
-    <row r="180" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A180" s="64" t="s">
         <v>656</v>
       </c>
@@ -30397,7 +30392,7 @@
         <v>1.6461735009491525</v>
       </c>
     </row>
-    <row r="181" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A181" s="64" t="s">
         <v>657</v>
       </c>
@@ -30520,7 +30515,7 @@
         <v>1.5931435361112869</v>
       </c>
     </row>
-    <row r="182" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A182" s="64" t="s">
         <v>658</v>
       </c>
@@ -30643,7 +30638,7 @@
         <v>1.4757143571699876</v>
       </c>
     </row>
-    <row r="183" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A183" s="64" t="s">
         <v>658</v>
       </c>
@@ -30766,7 +30761,7 @@
         <v>1.4374300869105257</v>
       </c>
     </row>
-    <row r="184" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A184" s="64" t="s">
         <v>658</v>
       </c>
@@ -30889,7 +30884,7 @@
         <v>1.3985631033192503</v>
       </c>
     </row>
-    <row r="185" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A185" s="64" t="s">
         <v>659</v>
       </c>
@@ -31012,7 +31007,7 @@
         <v>1.3826456374022646</v>
       </c>
     </row>
-    <row r="186" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A186" s="64" t="s">
         <v>660</v>
       </c>
@@ -31135,7 +31130,7 @@
         <v>0.47357002940963111</v>
       </c>
     </row>
-    <row r="187" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A187" s="64" t="s">
         <v>661</v>
       </c>
@@ -31258,7 +31253,7 @@
         <v>1.2597354394053424</v>
       </c>
     </row>
-    <row r="188" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A188" s="64" t="s">
         <v>662</v>
       </c>
@@ -31381,7 +31376,7 @@
         <v>1.1675517449568096</v>
       </c>
     </row>
-    <row r="189" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A189" s="64" t="s">
         <v>663</v>
       </c>
@@ -31504,7 +31499,7 @@
         <v>1.3696411756979359</v>
       </c>
     </row>
-    <row r="190" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A190" s="64" t="s">
         <v>663</v>
       </c>
@@ -31627,7 +31622,7 @@
         <v>1.350214188462304</v>
       </c>
     </row>
-    <row r="191" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A191" s="64" t="s">
         <v>664</v>
       </c>
@@ -31750,7 +31745,7 @@
         <v>1.2329454023052526</v>
       </c>
     </row>
-    <row r="192" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A192" s="64" t="s">
         <v>664</v>
       </c>
@@ -31873,7 +31868,7 @@
         <v>1.1957801977735603</v>
       </c>
     </row>
-    <row r="193" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A193" s="64" t="s">
         <v>665</v>
       </c>
@@ -31996,7 +31991,7 @@
         <v>1.1035853568830785</v>
       </c>
     </row>
-    <row r="194" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A194" s="64" t="s">
         <v>665</v>
       </c>
@@ -32119,7 +32114,7 @@
         <v>1.0659650406849812</v>
       </c>
     </row>
-    <row r="195" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A195" s="64" t="s">
         <v>665</v>
       </c>
@@ -32242,7 +32237,7 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="196" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A196" s="64" t="s">
         <v>665</v>
       </c>
@@ -32365,7 +32360,7 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="197" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A197" s="64" t="s">
         <v>665</v>
       </c>
@@ -32488,7 +32483,7 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="198" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A198" s="64" t="s">
         <v>665</v>
       </c>
@@ -32611,7 +32606,7 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="199" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A199" s="64" t="s">
         <v>665</v>
       </c>
@@ -32734,7 +32729,7 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="200" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A200" s="64" t="s">
         <v>665</v>
       </c>
@@ -32857,7 +32852,7 @@
         <v>2.1875</v>
       </c>
     </row>
-    <row r="201" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A201" s="64" t="s">
         <v>666</v>
       </c>
@@ -32979,7 +32974,7 @@
         <v>1.6566885721095854</v>
       </c>
     </row>
-    <row r="202" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A202" s="64" t="s">
         <v>666</v>
       </c>
@@ -33101,7 +33096,7 @@
         <v>1.6346161037144891</v>
       </c>
     </row>
-    <row r="203" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A203" s="64" t="s">
         <v>667</v>
       </c>
@@ -33223,7 +33218,7 @@
         <v>1.5890770411330262</v>
       </c>
     </row>
-    <row r="204" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A204" s="64" t="s">
         <v>668</v>
       </c>
@@ -33346,7 +33341,7 @@
         <v>1.6348488056211639</v>
       </c>
     </row>
-    <row r="205" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A205" s="64" t="s">
         <v>669</v>
       </c>
@@ -33469,7 +33464,7 @@
         <v>1.3994784856987472</v>
       </c>
     </row>
-    <row r="206" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A206" s="64" t="s">
         <v>669</v>
       </c>
@@ -33592,7 +33587,7 @@
         <v>1.3761547970799959</v>
       </c>
     </row>
-    <row r="207" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A207" s="64" t="s">
         <v>670</v>
       </c>
@@ -33715,7 +33710,7 @@
         <v>1.2739382867033264</v>
       </c>
     </row>
-    <row r="208" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A208" s="64" t="s">
         <v>670</v>
       </c>
@@ -33838,7 +33833,7 @@
         <v>1.2513432560545719</v>
       </c>
     </row>
-    <row r="209" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A209" s="64" t="s">
         <v>670</v>
       </c>
@@ -33961,7 +33956,7 @@
         <v>1.2287862611479596</v>
       </c>
     </row>
-    <row r="210" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A210" s="64" t="s">
         <v>670</v>
       </c>
@@ -34084,7 +34079,7 @@
         <v>1.1838391039622553</v>
       </c>
     </row>
-    <row r="211" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A211" s="64" t="s">
         <v>671</v>
       </c>
@@ -34207,7 +34202,7 @@
         <v>1.3995973831143944</v>
       </c>
     </row>
-    <row r="212" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A212" s="64" t="s">
         <v>671</v>
       </c>
@@ -34330,7 +34325,7 @@
         <v>1.4269474786562346</v>
       </c>
     </row>
-    <row r="213" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A213" s="64" t="s">
         <v>672</v>
       </c>
@@ -34453,7 +34448,7 @@
         <v>1.4544075393871425</v>
       </c>
     </row>
-    <row r="214" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A214" s="64" t="s">
         <v>673</v>
       </c>
@@ -34576,7 +34571,7 @@
         <v>1.1915152802141717</v>
       </c>
     </row>
-    <row r="215" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A215" s="64" t="s">
         <v>674</v>
       </c>
@@ -34698,7 +34693,7 @@
         <v>1.3027775635825822</v>
       </c>
     </row>
-    <row r="216" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A216" s="64" t="s">
         <v>675</v>
       </c>
@@ -34820,7 +34815,7 @@
         <v>0.81407876134588997</v>
       </c>
     </row>
-    <row r="217" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A217" s="64" t="s">
         <v>676</v>
       </c>
@@ -34942,7 +34937,7 @@
         <v>1.1216996276148128</v>
       </c>
     </row>
-    <row r="218" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A218" s="64" t="s">
         <v>677</v>
       </c>
@@ -35065,7 +35060,7 @@
         <v>1.1919024331549293</v>
       </c>
     </row>
-    <row r="219" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A219" s="64" t="s">
         <v>678</v>
       </c>
@@ -35190,7 +35185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A220" s="64" t="s">
         <v>569</v>
       </c>
@@ -35315,7 +35310,7 @@
         <v>1.4778743985473446</v>
       </c>
     </row>
-    <row r="221" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A221" s="64" t="s">
         <v>569</v>
       </c>
@@ -35440,7 +35435,7 @@
         <v>1.4352282729652679</v>
       </c>
     </row>
-    <row r="222" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A222" s="64" t="s">
         <v>679</v>
       </c>
@@ -35557,7 +35552,7 @@
         <v>2.6923076923076925</v>
       </c>
     </row>
-    <row r="223" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A223" s="64" t="s">
         <v>680</v>
       </c>
@@ -35674,7 +35669,7 @@
         <v>3.378378378378379</v>
       </c>
     </row>
-    <row r="224" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A224" s="64" t="s">
         <v>680</v>
       </c>
@@ -35791,7 +35786,7 @@
         <v>3.378378378378379</v>
       </c>
     </row>
-    <row r="225" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A225" s="64" t="s">
         <v>680</v>
       </c>
@@ -35908,7 +35903,7 @@
         <v>3.3783783783783781</v>
       </c>
     </row>
-    <row r="226" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A226" s="64" t="s">
         <v>680</v>
       </c>
@@ -36025,7 +36020,7 @@
         <v>3.3783783783783781</v>
       </c>
     </row>
-    <row r="227" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A227" s="64" t="s">
         <v>680</v>
       </c>
@@ -36142,7 +36137,7 @@
         <v>3.3783783783783781</v>
       </c>
     </row>
-    <row r="228" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A228" s="64" t="s">
         <v>680</v>
       </c>
@@ -36259,7 +36254,7 @@
         <v>3.3783783783783785</v>
       </c>
     </row>
-    <row r="229" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A229" s="64" t="s">
         <v>680</v>
       </c>
@@ -36376,7 +36371,7 @@
         <v>3.3783783783783781</v>
       </c>
     </row>
-    <row r="230" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A230" s="64" t="s">
         <v>680</v>
       </c>
@@ -36493,7 +36488,7 @@
         <v>3.3783783783783785</v>
       </c>
     </row>
-    <row r="231" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A231" s="83" t="s">
         <v>720</v>
       </c>
@@ -36517,7 +36512,9 @@
         <v>196</v>
       </c>
       <c r="M231" s="74"/>
-      <c r="N231" s="65"/>
+      <c r="N231" s="65" t="s">
+        <v>26</v>
+      </c>
       <c r="O231" s="67" t="s">
         <v>712</v>
       </c>
@@ -36598,7 +36595,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="232" spans="1:42" s="95" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:42" s="95" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A232" s="89" t="s">
         <v>721</v>
       </c>
@@ -36622,7 +36619,9 @@
         <v>212</v>
       </c>
       <c r="M232" s="74"/>
-      <c r="N232" s="67"/>
+      <c r="N232" s="65" t="s">
+        <v>26</v>
+      </c>
       <c r="O232" s="67" t="s">
         <v>711</v>
       </c>
@@ -36699,7 +36698,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="233" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A233" s="64" t="s">
         <v>729</v>
       </c>
@@ -36723,7 +36722,7 @@
         <v>221</v>
       </c>
       <c r="M233" s="74"/>
-      <c r="N233" s="6" t="s">
+      <c r="N233" s="65" t="s">
         <v>26</v>
       </c>
       <c r="O233" s="5" t="s">
@@ -36802,7 +36801,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="234" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A234" s="83" t="s">
         <v>722</v>
       </c>
@@ -36904,7 +36903,7 @@
         <v>2.2839969947407965</v>
       </c>
     </row>
-    <row r="235" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A235" s="83" t="s">
         <v>723</v>
       </c>
@@ -37004,7 +37003,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="236" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A236" s="83" t="s">
         <v>724</v>
       </c>
@@ -37104,7 +37103,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="237" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A237" s="83" t="s">
         <v>725</v>
       </c>
@@ -37204,7 +37203,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="238" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A238" s="83" t="s">
         <v>726</v>
       </c>
@@ -37227,7 +37226,9 @@
         <v>708</v>
       </c>
       <c r="M238" s="99"/>
-      <c r="N238" s="65"/>
+      <c r="N238" s="65" t="s">
+        <v>26</v>
+      </c>
       <c r="O238" s="67" t="s">
         <v>712</v>
       </c>
@@ -37304,7 +37305,7 @@
         <v>3.2456799398948157</v>
       </c>
     </row>
-    <row r="239" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A239" s="83" t="s">
         <v>727</v>
       </c>
@@ -37404,7 +37405,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="240" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A240" s="83" t="s">
         <v>728</v>
       </c>
@@ -37504,7 +37505,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="241" spans="1:42" s="64" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:42" s="64" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A241" s="64" t="s">
         <v>733</v>
       </c>
@@ -37526,20 +37527,20 @@
         <v>732</v>
       </c>
       <c r="M241" s="110"/>
-      <c r="N241" s="111" t="s">
+      <c r="N241" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="O241" s="112"/>
-      <c r="P241" s="113" t="s">
+      <c r="O241" s="111"/>
+      <c r="P241" s="112" t="s">
         <v>27</v>
       </c>
       <c r="R241" s="103">
         <v>0.72499999999999998</v>
       </c>
-      <c r="S241" s="114">
+      <c r="S241" s="113">
         <v>0.27500000000000002</v>
       </c>
-      <c r="T241" s="115">
+      <c r="T241" s="114">
         <f t="shared" si="39"/>
         <v>1</v>
       </c>
@@ -37553,7 +37554,7 @@
       <c r="AB241" s="78">
         <v>1669.242</v>
       </c>
-      <c r="AC241" s="116"/>
+      <c r="AC241" s="115"/>
       <c r="AD241" s="68"/>
       <c r="AE241" s="68"/>
       <c r="AF241" s="68"/>
@@ -37873,9 +37874,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA5B41D-754B-41F4-AE3E-2CEADDCF305E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>568</v>
       </c>

--- a/areas_land_bank_com_id.xlsx
+++ b/areas_land_bank_com_id.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.castro\Documents\01 Profissional\Buriti Empreendimentos\Repositórios\land-bank-mapa-brasil-terrenos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5256DE6A-6317-4F17-9C7A-ABDC3532BCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C596D42-BED9-49AD-8EFE-00C9C890A74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D7381EB-1656-47BB-A82F-14AB3B13CCCD}"/>
   </bookViews>
@@ -5306,7 +5306,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="738">
   <si>
     <t>Nome</t>
   </si>
@@ -7522,6 +7522,9 @@
   </si>
   <si>
     <t>CENTRO-OESTE</t>
+  </si>
+  <si>
+    <t>a DEFINIR</t>
   </si>
 </sst>
 </file>
@@ -7870,7 +7873,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8158,6 +8161,7 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8551,7 +8555,8 @@
     <col min="32" max="32" width="12.21875" customWidth="1"/>
     <col min="33" max="33" width="8.77734375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.5546875" customWidth="1"/>
+    <col min="35" max="35" width="10.77734375" customWidth="1"/>
+    <col min="36" max="36" width="9.5546875" customWidth="1"/>
     <col min="37" max="38" width="9" customWidth="1"/>
     <col min="39" max="39" width="16" bestFit="1" customWidth="1"/>
     <col min="40" max="41" width="12.77734375" customWidth="1"/>
@@ -36512,8 +36517,8 @@
         <v>196</v>
       </c>
       <c r="M231" s="74"/>
-      <c r="N231" s="65" t="s">
-        <v>26</v>
+      <c r="N231" s="101" t="s">
+        <v>737</v>
       </c>
       <c r="O231" s="67" t="s">
         <v>712</v>
@@ -36619,8 +36624,8 @@
         <v>212</v>
       </c>
       <c r="M232" s="74"/>
-      <c r="N232" s="65" t="s">
-        <v>26</v>
+      <c r="N232" s="101" t="s">
+        <v>737</v>
       </c>
       <c r="O232" s="67" t="s">
         <v>711</v>
@@ -36722,7 +36727,7 @@
         <v>221</v>
       </c>
       <c r="M233" s="74"/>
-      <c r="N233" s="65" t="s">
+      <c r="N233" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O233" s="5" t="s">
@@ -37226,8 +37231,8 @@
         <v>708</v>
       </c>
       <c r="M238" s="99"/>
-      <c r="N238" s="65" t="s">
-        <v>26</v>
+      <c r="N238" s="101" t="s">
+        <v>737</v>
       </c>
       <c r="O238" s="67" t="s">
         <v>712</v>
@@ -37527,20 +37532,20 @@
         <v>732</v>
       </c>
       <c r="M241" s="110"/>
-      <c r="N241" s="65" t="s">
+      <c r="N241" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="O241" s="111"/>
-      <c r="P241" s="112" t="s">
+      <c r="O241" s="112"/>
+      <c r="P241" s="113" t="s">
         <v>27</v>
       </c>
       <c r="R241" s="103">
         <v>0.72499999999999998</v>
       </c>
-      <c r="S241" s="113">
+      <c r="S241" s="114">
         <v>0.27500000000000002</v>
       </c>
-      <c r="T241" s="114">
+      <c r="T241" s="115">
         <f t="shared" si="39"/>
         <v>1</v>
       </c>
@@ -37554,7 +37559,7 @@
       <c r="AB241" s="78">
         <v>1669.242</v>
       </c>
-      <c r="AC241" s="115"/>
+      <c r="AC241" s="116"/>
       <c r="AD241" s="68"/>
       <c r="AE241" s="68"/>
       <c r="AF241" s="68"/>

--- a/areas_land_bank_com_id.xlsx
+++ b/areas_land_bank_com_id.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Departamento Controladoria\3 - BT 360º\Landbank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527FC402-853E-414E-9886-EC808F900A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058A33A0-DEE3-47FE-8F5A-E5A2CA5ABC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="960" windowWidth="29040" windowHeight="15720" xr2:uid="{2D7381EB-1656-47BB-A82F-14AB3B13CCCD}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha2" sheetId="3" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AREAS!$A$1:$AK$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AREAS!$A$1:$AK$244</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5328,7 +5328,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2389" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2651" uniqueCount="795">
   <si>
     <t>Nome</t>
   </si>
@@ -7704,6 +7704,33 @@
   </si>
   <si>
     <t>MAP134</t>
+  </si>
+  <si>
+    <t>MUNARO EMPREENDIMENTOS IMOBILIÁRIOS LTDA</t>
+  </si>
+  <si>
+    <t>Status da área</t>
+  </si>
+  <si>
+    <t>Estudo de viabilidade</t>
+  </si>
+  <si>
+    <t>LandBank</t>
+  </si>
+  <si>
+    <t>GUARANTÃ DO NORTE</t>
+  </si>
+  <si>
+    <t>PERGENTINO DE VASCONCELOS JUNIOR</t>
+  </si>
+  <si>
+    <t>SEDESTE</t>
+  </si>
+  <si>
+    <t>MAP135</t>
+  </si>
+  <si>
+    <t>MAP136</t>
   </si>
 </sst>
 </file>
@@ -7831,7 +7858,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7877,12 +7904,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7969,7 +7990,7 @@
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -8056,7 +8077,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="37" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -8072,7 +8093,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -8080,9 +8101,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -8105,26 +8126,25 @@
     <xf numFmtId="49" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -8136,7 +8156,23 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -8491,7 +8527,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB1E7F9-B7E0-4EE5-A96E-08F27078CA81}">
   <sheetPr codeName="Folha1"/>
-  <dimension ref="A1:AN242"/>
+  <dimension ref="A1:AO244"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
@@ -8508,7 +8544,7 @@
     <col min="13" max="13" width="53.36328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.453125" style="3" customWidth="1"/>
     <col min="15" max="15" width="14.54296875" customWidth="1"/>
-    <col min="16" max="16" width="9.1796875" customWidth="1"/>
+    <col min="16" max="16" width="9.1796875" style="3" customWidth="1"/>
     <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.81640625" customWidth="1"/>
     <col min="19" max="19" width="11.54296875" customWidth="1"/>
@@ -8531,9 +8567,10 @@
     <col min="37" max="37" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="38" max="39" width="12.81640625" customWidth="1"/>
     <col min="40" max="40" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="23.08984375" style="76" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="50" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" ht="50" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>432</v>
       </c>
@@ -8654,8 +8691,11 @@
       <c r="AN1" s="9" t="s">
         <v>550</v>
       </c>
+      <c r="AO1" s="74" t="s">
+        <v>787</v>
+      </c>
     </row>
-    <row r="2" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>440</v>
       </c>
@@ -8769,8 +8809,11 @@
         <f>AI2*AM2/(AD2+AB2)</f>
         <v>3.3809797786673061</v>
       </c>
+      <c r="AO2" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="3" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>441</v>
       </c>
@@ -8864,7 +8907,7 @@
         <v>384.77817538189237</v>
       </c>
       <c r="AI3" s="21">
-        <f t="shared" ref="AI2:AI65" si="6">(AH3*AG3*AF3)/10^6</f>
+        <f t="shared" ref="AI3:AI65" si="6">(AH3*AG3*AF3)/10^6</f>
         <v>4.3</v>
       </c>
       <c r="AJ3" s="21">
@@ -8886,8 +8929,11 @@
         <f t="shared" ref="AN3:AN66" si="8">AI3*AM3/(AD3+AB3)</f>
         <v>4.8097271922736544</v>
       </c>
+      <c r="AO3" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="4" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>441</v>
       </c>
@@ -9003,8 +9049,11 @@
         <f t="shared" si="8"/>
         <v>5.3580126643935699</v>
       </c>
+      <c r="AO4" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="5" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>493</v>
       </c>
@@ -9124,8 +9173,11 @@
         <f t="shared" si="8"/>
         <v>1.1478379123898736</v>
       </c>
+      <c r="AO5" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="6" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>481</v>
       </c>
@@ -9245,8 +9297,11 @@
         <f t="shared" si="8"/>
         <v>0.90690345120653837</v>
       </c>
+      <c r="AO6" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="7" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>482</v>
       </c>
@@ -9366,8 +9421,11 @@
         <f t="shared" si="8"/>
         <v>0.87259450365707092</v>
       </c>
+      <c r="AO7" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="8" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>483</v>
       </c>
@@ -9487,8 +9545,11 @@
         <f t="shared" si="8"/>
         <v>0.83860953776262182</v>
       </c>
+      <c r="AO8" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>483</v>
       </c>
@@ -9608,8 +9669,11 @@
         <f t="shared" si="8"/>
         <v>0.80502313984963059</v>
       </c>
+      <c r="AO9" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>483</v>
       </c>
@@ -9729,8 +9793,11 @@
         <f t="shared" si="8"/>
         <v>2.024472392638037</v>
       </c>
+      <c r="AO10" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>434</v>
       </c>
@@ -9841,11 +9908,14 @@
         <v>1</v>
       </c>
       <c r="AN11" s="51" t="e">
-        <f t="shared" si="8"/>
+        <f>AI11*AM11/(AD11+AB11)</f>
         <v>#DIV/0!</v>
       </c>
+      <c r="AO11" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="12" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>435</v>
       </c>
@@ -9959,8 +10029,11 @@
         <f t="shared" si="8"/>
         <v>3.2306536438767841</v>
       </c>
+      <c r="AO12" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>436</v>
       </c>
@@ -10074,8 +10147,11 @@
         <f t="shared" si="8"/>
         <v>4.883546205860255</v>
       </c>
+      <c r="AO13" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>436</v>
       </c>
@@ -10189,8 +10265,11 @@
         <f t="shared" si="8"/>
         <v>4.883546205860255</v>
       </c>
+      <c r="AO14" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>437</v>
       </c>
@@ -10304,8 +10383,11 @@
         <f t="shared" si="8"/>
         <v>3.7565740045078888</v>
       </c>
+      <c r="AO15" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>438</v>
       </c>
@@ -10419,8 +10501,11 @@
         <f t="shared" si="8"/>
         <v>3.7565740045078897</v>
       </c>
+      <c r="AO16" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="17" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>439</v>
       </c>
@@ -10534,8 +10619,11 @@
         <f t="shared" si="8"/>
         <v>3.7565740045078893</v>
       </c>
+      <c r="AO17" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="18" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>444</v>
       </c>
@@ -10649,8 +10737,11 @@
         <f t="shared" si="8"/>
         <v>3.230653643876785</v>
       </c>
+      <c r="AO18" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="19" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>445</v>
       </c>
@@ -10764,8 +10855,11 @@
         <f t="shared" si="8"/>
         <v>2.9301277235161534</v>
       </c>
+      <c r="AO19" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="20" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>445</v>
       </c>
@@ -10879,8 +10973,11 @@
         <f t="shared" si="8"/>
         <v>2.9301277235161534</v>
       </c>
+      <c r="AO20" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="21" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>445</v>
       </c>
@@ -10994,8 +11091,11 @@
         <f t="shared" si="8"/>
         <v>2.9301277235161534</v>
       </c>
+      <c r="AO21" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="22" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>445</v>
       </c>
@@ -11109,8 +11209,11 @@
         <f t="shared" si="8"/>
         <v>2.9301277235161534</v>
       </c>
+      <c r="AO22" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="23" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>445</v>
       </c>
@@ -11224,8 +11327,11 @@
         <f t="shared" si="8"/>
         <v>2.9301277235161534</v>
       </c>
+      <c r="AO23" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="24" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>445</v>
       </c>
@@ -11339,8 +11445,11 @@
         <f t="shared" si="8"/>
         <v>2.9301277235161534</v>
       </c>
+      <c r="AO24" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="25" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>445</v>
       </c>
@@ -11454,8 +11563,11 @@
         <f t="shared" si="8"/>
         <v>2.9301277235161534</v>
       </c>
+      <c r="AO25" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="26" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>446</v>
       </c>
@@ -11569,8 +11681,11 @@
         <f t="shared" si="8"/>
         <v>0.83115017886351839</v>
       </c>
+      <c r="AO26" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="27" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>447</v>
       </c>
@@ -11684,8 +11799,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO27" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="28" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>447</v>
       </c>
@@ -11798,8 +11916,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO28" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="29" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>447</v>
       </c>
@@ -11913,8 +12034,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO29" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="30" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>447</v>
       </c>
@@ -12028,8 +12152,11 @@
         <f t="shared" si="8"/>
         <v>4.140625</v>
       </c>
+      <c r="AO30" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="31" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>447</v>
       </c>
@@ -12143,8 +12270,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO31" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="32" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>447</v>
       </c>
@@ -12258,8 +12388,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO32" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="33" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>447</v>
       </c>
@@ -12373,8 +12506,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO33" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="34" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>447</v>
       </c>
@@ -12488,8 +12624,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO34" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="35" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>447</v>
       </c>
@@ -12603,8 +12742,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO35" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="36" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>447</v>
       </c>
@@ -12718,8 +12860,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO36" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="37" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>447</v>
       </c>
@@ -12833,8 +12978,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO37" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="38" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>447</v>
       </c>
@@ -12948,8 +13096,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO38" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="39" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>447</v>
       </c>
@@ -13063,8 +13214,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO39" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="40" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>447</v>
       </c>
@@ -13178,8 +13332,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO40" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="41" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>447</v>
       </c>
@@ -13293,8 +13450,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO41" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="42" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>447</v>
       </c>
@@ -13408,8 +13568,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO42" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="43" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>447</v>
       </c>
@@ -13523,8 +13686,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO43" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="44" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>447</v>
       </c>
@@ -13638,8 +13804,11 @@
         <f t="shared" si="8"/>
         <v>4.296875</v>
       </c>
+      <c r="AO44" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="45" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>447</v>
       </c>
@@ -13753,8 +13922,11 @@
         <f t="shared" si="8"/>
         <v>3.90625</v>
       </c>
+      <c r="AO45" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="46" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>448</v>
       </c>
@@ -13874,8 +14046,11 @@
         <f t="shared" si="8"/>
         <v>1.5033333068541384</v>
       </c>
+      <c r="AO46" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="47" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>448</v>
       </c>
@@ -13995,8 +14170,11 @@
         <f t="shared" si="8"/>
         <v>1.5033333068541381</v>
       </c>
+      <c r="AO47" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="48" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>448</v>
       </c>
@@ -14116,8 +14294,11 @@
         <f t="shared" si="8"/>
         <v>1.1881369949110563</v>
       </c>
+      <c r="AO48" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="49" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>448</v>
       </c>
@@ -14237,8 +14418,11 @@
         <f t="shared" si="8"/>
         <v>1.1629101414416052</v>
       </c>
+      <c r="AO49" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="50" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>449</v>
       </c>
@@ -14351,8 +14535,11 @@
         <f t="shared" si="8"/>
         <v>3.9062500000000004</v>
       </c>
+      <c r="AO50" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="51" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>451</v>
       </c>
@@ -14466,8 +14653,11 @@
         <f t="shared" si="8"/>
         <v>4.6875000000000009</v>
       </c>
+      <c r="AO51" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="52" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>483</v>
       </c>
@@ -14587,8 +14777,11 @@
         <f t="shared" si="8"/>
         <v>2.024472392638037</v>
       </c>
+      <c r="AO52" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="53" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>483</v>
       </c>
@@ -14708,8 +14901,11 @@
         <f t="shared" si="8"/>
         <v>2.024472392638037</v>
       </c>
+      <c r="AO53" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="54" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>483</v>
       </c>
@@ -14829,8 +15025,11 @@
         <f t="shared" si="8"/>
         <v>2.024472392638037</v>
       </c>
+      <c r="AO54" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="55" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>483</v>
       </c>
@@ -14950,8 +15149,11 @@
         <f t="shared" si="8"/>
         <v>2.024472392638037</v>
       </c>
+      <c r="AO55" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="56" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>455</v>
       </c>
@@ -15071,8 +15273,11 @@
         <f t="shared" si="8"/>
         <v>2.0794444816235882</v>
       </c>
+      <c r="AO56" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="57" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>455</v>
       </c>
@@ -15191,8 +15396,11 @@
         <f t="shared" si="8"/>
         <v>0.682062825375507</v>
       </c>
+      <c r="AO57" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="58" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>454</v>
       </c>
@@ -15312,8 +15520,11 @@
         <f t="shared" si="8"/>
         <v>1.584067227618178</v>
       </c>
+      <c r="AO58" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="59" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>456</v>
       </c>
@@ -15433,8 +15644,11 @@
         <f t="shared" si="8"/>
         <v>1.2626874796242238</v>
       </c>
+      <c r="AO59" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="60" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>457</v>
       </c>
@@ -15554,8 +15768,11 @@
         <f t="shared" si="8"/>
         <v>1.165542478997921</v>
       </c>
+      <c r="AO60" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="61" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>457</v>
       </c>
@@ -15675,8 +15892,11 @@
         <f t="shared" si="8"/>
         <v>1.1453025708336924</v>
       </c>
+      <c r="AO61" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="62" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>458</v>
       </c>
@@ -15796,8 +16016,11 @@
         <f t="shared" si="8"/>
         <v>1.0499523822058021</v>
       </c>
+      <c r="AO62" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="63" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>459</v>
       </c>
@@ -15911,8 +16134,11 @@
         <f t="shared" si="8"/>
         <v>3.9384920139218527</v>
       </c>
+      <c r="AO63" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="64" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>459</v>
       </c>
@@ -16026,8 +16252,11 @@
         <f t="shared" si="8"/>
         <v>3.9384920139218527</v>
       </c>
+      <c r="AO64" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="65" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>459</v>
       </c>
@@ -16141,8 +16370,11 @@
         <f t="shared" si="8"/>
         <v>3.9384920139218527</v>
       </c>
+      <c r="AO65" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="66" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>460</v>
       </c>
@@ -16256,8 +16488,11 @@
         <f t="shared" si="8"/>
         <v>3.5833333333333335</v>
       </c>
+      <c r="AO66" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="67" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>461</v>
       </c>
@@ -16371,8 +16606,11 @@
         <f t="shared" ref="AN67:AN130" si="19">AI67*AM67/(AD67+AB67)</f>
         <v>3.8333333333333335</v>
       </c>
+      <c r="AO67" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="68" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>462</v>
       </c>
@@ -16486,8 +16724,11 @@
         <f t="shared" si="19"/>
         <v>3.5833333333333335</v>
       </c>
+      <c r="AO68" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="69" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>462</v>
       </c>
@@ -16601,8 +16842,11 @@
         <f t="shared" si="19"/>
         <v>3.5833333333333335</v>
       </c>
+      <c r="AO69" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="70" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>463</v>
       </c>
@@ -16721,8 +16965,11 @@
         <f t="shared" si="19"/>
         <v>1.6840907460634127</v>
       </c>
+      <c r="AO70" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="71" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>464</v>
       </c>
@@ -16841,8 +17088,11 @@
         <f t="shared" si="19"/>
         <v>1.7104564330775569</v>
       </c>
+      <c r="AO71" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="72" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>464</v>
       </c>
@@ -16961,8 +17211,11 @@
         <f t="shared" si="19"/>
         <v>1.6579735962048303</v>
       </c>
+      <c r="AO72" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="73" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>465</v>
       </c>
@@ -17081,8 +17334,11 @@
         <f t="shared" si="19"/>
         <v>2.5287610566591523</v>
       </c>
+      <c r="AO73" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="74" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>465</v>
       </c>
@@ -17201,8 +17457,11 @@
         <f t="shared" si="19"/>
         <v>2.4793535855822042</v>
       </c>
+      <c r="AO74" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="75" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>466</v>
       </c>
@@ -17324,8 +17583,11 @@
         <f t="shared" si="19"/>
         <v>1.890388055872956</v>
       </c>
+      <c r="AO75" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="76" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>466</v>
       </c>
@@ -17447,8 +17709,11 @@
         <f t="shared" si="19"/>
         <v>1.8605083275965164</v>
       </c>
+      <c r="AO76" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="77" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>467</v>
       </c>
@@ -17570,8 +17835,11 @@
         <f t="shared" si="19"/>
         <v>1.8523399895648596</v>
       </c>
+      <c r="AO77" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="78" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>467</v>
       </c>
@@ -17693,8 +17961,11 @@
         <f t="shared" si="19"/>
         <v>1.7669888872138106</v>
       </c>
+      <c r="AO78" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="79" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>468</v>
       </c>
@@ -17814,8 +18085,11 @@
         <f t="shared" si="19"/>
         <v>0.64100515446669049</v>
       </c>
+      <c r="AO79" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="80" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>468</v>
       </c>
@@ -17935,8 +18209,11 @@
         <f t="shared" si="19"/>
         <v>0.62670976763932151</v>
       </c>
+      <c r="AO80" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="81" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>469</v>
       </c>
@@ -18056,8 +18333,11 @@
         <f t="shared" si="19"/>
         <v>0.76883870310314895</v>
       </c>
+      <c r="AO81" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="82" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
         <v>475</v>
       </c>
@@ -18177,8 +18457,11 @@
         <f t="shared" si="19"/>
         <v>1.2072988815514583</v>
       </c>
+      <c r="AO82" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="83" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
         <v>471</v>
       </c>
@@ -18298,8 +18581,11 @@
         <f t="shared" si="19"/>
         <v>0.83525452781953513</v>
       </c>
+      <c r="AO83" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="84" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>471</v>
       </c>
@@ -18419,8 +18705,11 @@
         <f t="shared" si="19"/>
         <v>0.81799598953212038</v>
       </c>
+      <c r="AO84" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="85" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
         <v>471</v>
       </c>
@@ -18540,8 +18829,11 @@
         <f t="shared" si="19"/>
         <v>0.78388138912123639</v>
       </c>
+      <c r="AO85" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="86" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
         <v>472</v>
       </c>
@@ -18661,8 +18953,11 @@
         <f t="shared" si="19"/>
         <v>1.1501266268686077</v>
       </c>
+      <c r="AO86" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="87" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
         <v>473</v>
       </c>
@@ -18782,8 +19077,11 @@
         <f t="shared" si="19"/>
         <v>0.23299756298435631</v>
       </c>
+      <c r="AO87" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="88" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
         <v>473</v>
       </c>
@@ -18903,8 +19201,11 @@
         <f t="shared" si="19"/>
         <v>1.2387943662501089</v>
       </c>
+      <c r="AO88" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="89" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>474</v>
       </c>
@@ -19024,8 +19325,11 @@
         <f t="shared" si="19"/>
         <v>1.5149909654595908</v>
       </c>
+      <c r="AO89" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="90" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>546</v>
       </c>
@@ -19145,8 +19449,11 @@
         <f t="shared" si="19"/>
         <v>1.2046020634661616</v>
       </c>
+      <c r="AO90" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="91" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
         <v>475</v>
       </c>
@@ -19266,8 +19573,11 @@
         <f t="shared" si="19"/>
         <v>1.4090811331942312</v>
       </c>
+      <c r="AO91" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="92" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>475</v>
       </c>
@@ -19387,8 +19697,11 @@
         <f t="shared" si="19"/>
         <v>1.1397336017719824</v>
       </c>
+      <c r="AO92" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="93" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
         <v>475</v>
       </c>
@@ -19508,8 +19821,11 @@
         <f t="shared" si="19"/>
         <v>1.0959959051299162</v>
       </c>
+      <c r="AO93" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="94" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
         <v>475</v>
       </c>
@@ -19629,8 +19945,11 @@
         <f t="shared" si="19"/>
         <v>1.0527200029561115</v>
       </c>
+      <c r="AO94" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="95" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
         <v>545</v>
       </c>
@@ -19744,8 +20063,11 @@
         <f t="shared" si="19"/>
         <v>3.2407407407407409</v>
       </c>
+      <c r="AO95" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="96" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
         <v>476</v>
       </c>
@@ -19865,8 +20187,11 @@
         <f t="shared" si="19"/>
         <v>2.1202973983797322</v>
       </c>
+      <c r="AO96" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="97" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
         <v>477</v>
       </c>
@@ -19986,8 +20311,11 @@
         <f t="shared" si="19"/>
         <v>2.0772596632135061</v>
       </c>
+      <c r="AO97" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="98" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
         <v>450</v>
       </c>
@@ -20101,8 +20429,11 @@
         <f t="shared" si="19"/>
         <v>3.2407407407407409</v>
       </c>
+      <c r="AO98" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="99" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
         <v>452</v>
       </c>
@@ -20216,8 +20547,11 @@
         <f t="shared" si="19"/>
         <v>6.2499999999999991</v>
       </c>
+      <c r="AO99" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="100" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
         <v>479</v>
       </c>
@@ -20337,8 +20671,11 @@
         <f t="shared" si="19"/>
         <v>1.5361651825388483</v>
       </c>
+      <c r="AO100" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="101" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
         <v>479</v>
       </c>
@@ -20458,8 +20795,11 @@
         <f t="shared" si="19"/>
         <v>1.5065784699927574</v>
       </c>
+      <c r="AO101" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="102" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
         <v>479</v>
       </c>
@@ -20579,8 +20919,11 @@
         <f t="shared" si="19"/>
         <v>1.4478450040383797</v>
       </c>
+      <c r="AO102" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="103" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
         <v>480</v>
       </c>
@@ -20700,8 +21043,11 @@
         <f t="shared" si="19"/>
         <v>1.6691380981214541</v>
       </c>
+      <c r="AO103" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="104" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>480</v>
       </c>
@@ -20821,8 +21167,11 @@
         <f t="shared" si="19"/>
         <v>1.6065963825333243</v>
       </c>
+      <c r="AO104" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="105" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
         <v>478</v>
       </c>
@@ -20942,8 +21291,11 @@
         <f t="shared" si="19"/>
         <v>1.0994472988394468</v>
       </c>
+      <c r="AO105" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="106" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
         <v>478</v>
       </c>
@@ -21063,8 +21415,11 @@
         <f t="shared" si="19"/>
         <v>1.0586916755795146</v>
       </c>
+      <c r="AO106" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="107" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
         <v>442</v>
       </c>
@@ -21178,8 +21533,11 @@
         <f t="shared" si="19"/>
         <v>4.5078888054094666</v>
       </c>
+      <c r="AO107" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="108" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
         <v>443</v>
       </c>
@@ -21293,8 +21651,11 @@
         <f t="shared" si="19"/>
         <v>4.5078888054094675</v>
       </c>
+      <c r="AO108" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="109" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
         <v>443</v>
       </c>
@@ -21408,8 +21769,11 @@
         <f t="shared" si="19"/>
         <v>4.5078888054094666</v>
       </c>
+      <c r="AO109" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="110" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
         <v>443</v>
       </c>
@@ -21523,8 +21887,11 @@
         <f t="shared" si="19"/>
         <v>4.5078888054094683</v>
       </c>
+      <c r="AO110" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="111" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
         <v>443</v>
       </c>
@@ -21638,8 +22005,11 @@
         <f t="shared" si="19"/>
         <v>4.5078888054094683</v>
       </c>
+      <c r="AO111" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="112" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
         <v>443</v>
       </c>
@@ -21753,8 +22123,11 @@
         <f t="shared" si="19"/>
         <v>4.5078888054094683</v>
       </c>
+      <c r="AO112" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="113" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
         <v>453</v>
       </c>
@@ -21867,8 +22240,11 @@
         <f t="shared" si="19"/>
         <v>3.7037037037037033</v>
       </c>
+      <c r="AO113" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="114" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
         <v>484</v>
       </c>
@@ -21988,8 +22364,11 @@
         <f t="shared" si="19"/>
         <v>0.73245167478536033</v>
       </c>
+      <c r="AO114" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="115" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
         <v>485</v>
       </c>
@@ -22109,8 +22488,11 @@
         <f t="shared" si="19"/>
         <v>0.70127185350915722</v>
       </c>
+      <c r="AO115" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="116" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
         <v>485</v>
       </c>
@@ -22230,8 +22612,11 @@
         <f t="shared" si="19"/>
         <v>0.6706877524292354</v>
       </c>
+      <c r="AO116" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="117" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
         <v>485</v>
       </c>
@@ -22351,8 +22736,11 @@
         <f t="shared" si="19"/>
         <v>0.64075267145675929</v>
       </c>
+      <c r="AO117" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="118" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
         <v>485</v>
       </c>
@@ -22472,8 +22860,11 @@
         <f t="shared" si="19"/>
         <v>0.61151467271213211</v>
       </c>
+      <c r="AO118" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="119" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
         <v>485</v>
       </c>
@@ -22593,8 +22984,11 @@
         <f t="shared" si="19"/>
         <v>1.9492775508164899</v>
       </c>
+      <c r="AO119" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="120" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
         <v>486</v>
       </c>
@@ -22714,8 +23108,11 @@
         <f t="shared" si="19"/>
         <v>1.2292115404911319</v>
       </c>
+      <c r="AO120" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="121" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
         <v>487</v>
       </c>
@@ -22835,8 +23232,11 @@
         <f t="shared" si="19"/>
         <v>1.2413630323963301</v>
       </c>
+      <c r="AO121" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="122" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
         <v>488</v>
       </c>
@@ -22956,8 +23356,11 @@
         <f t="shared" si="19"/>
         <v>1.2561653093904881</v>
       </c>
+      <c r="AO122" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="123" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
         <v>489</v>
       </c>
@@ -23077,8 +23480,11 @@
         <f t="shared" si="19"/>
         <v>1.2113560025023844</v>
       </c>
+      <c r="AO123" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="124" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
         <v>490</v>
       </c>
@@ -23198,8 +23604,11 @@
         <f t="shared" si="19"/>
         <v>2.613496932515337</v>
       </c>
+      <c r="AO124" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="125" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
         <v>490</v>
       </c>
@@ -23319,8 +23728,11 @@
         <f t="shared" si="19"/>
         <v>2.6134969325153379</v>
       </c>
+      <c r="AO125" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="126" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
         <v>491</v>
       </c>
@@ -23440,8 +23852,11 @@
         <f t="shared" si="19"/>
         <v>1.3821716627734322</v>
       </c>
+      <c r="AO126" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="127" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
         <v>492</v>
       </c>
@@ -23561,8 +23976,11 @@
         <f t="shared" si="19"/>
         <v>1.3508286832235206</v>
       </c>
+      <c r="AO127" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="128" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
         <v>492</v>
       </c>
@@ -23682,8 +24100,11 @@
         <f t="shared" si="19"/>
         <v>1.3273996567144928</v>
       </c>
+      <c r="AO128" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="129" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A129" s="6" t="s">
         <v>520</v>
       </c>
@@ -23803,8 +24224,11 @@
         <f t="shared" si="19"/>
         <v>1.6857797571068185</v>
       </c>
+      <c r="AO129" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="130" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
         <v>494</v>
       </c>
@@ -23924,8 +24348,11 @@
         <f t="shared" si="19"/>
         <v>1.1873209657838852</v>
       </c>
+      <c r="AO130" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="131" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
         <v>494</v>
       </c>
@@ -24045,8 +24472,11 @@
         <f t="shared" ref="AN131:AN194" si="29">AI131*AM131/(AD131+AB131)</f>
         <v>1.1478379123898732</v>
       </c>
+      <c r="AO131" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="132" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
         <v>495</v>
       </c>
@@ -24166,8 +24596,11 @@
         <f t="shared" si="29"/>
         <v>1.1697737528257561</v>
       </c>
+      <c r="AO132" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="133" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
         <v>520</v>
       </c>
@@ -24287,8 +24720,11 @@
         <f t="shared" si="29"/>
         <v>1.6461735009491525</v>
       </c>
+      <c r="AO133" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="134" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
         <v>497</v>
       </c>
@@ -24408,8 +24844,11 @@
         <f t="shared" si="29"/>
         <v>1.1917791466511929</v>
       </c>
+      <c r="AO134" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="135" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
         <v>497</v>
       </c>
@@ -24529,8 +24968,11 @@
         <f t="shared" si="29"/>
         <v>1.1697737528257561</v>
       </c>
+      <c r="AO135" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="136" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
         <v>497</v>
       </c>
@@ -24650,8 +25092,11 @@
         <f t="shared" si="29"/>
         <v>1.1478379123898732</v>
       </c>
+      <c r="AO136" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="137" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
         <v>498</v>
       </c>
@@ -24770,8 +25215,11 @@
         <f t="shared" si="29"/>
         <v>1.100201380402013</v>
       </c>
+      <c r="AO137" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="138" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
         <v>498</v>
       </c>
@@ -24885,8 +25333,11 @@
         <f t="shared" si="29"/>
         <v>3.4285714285714284</v>
       </c>
+      <c r="AO138" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="139" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
         <v>498</v>
       </c>
@@ -25005,8 +25456,11 @@
         <f t="shared" si="29"/>
         <v>1.5534532233799874</v>
       </c>
+      <c r="AO139" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="140" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
         <v>498</v>
       </c>
@@ -25120,8 +25574,11 @@
         <f t="shared" si="29"/>
         <v>3.4285714285714284</v>
       </c>
+      <c r="AO140" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="141" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
         <v>499</v>
       </c>
@@ -25241,8 +25698,11 @@
         <f t="shared" si="29"/>
         <v>1.3402722285622568</v>
       </c>
+      <c r="AO141" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="142" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
         <v>499</v>
       </c>
@@ -25362,8 +25822,11 @@
         <f t="shared" si="29"/>
         <v>1.1069472501692708</v>
       </c>
+      <c r="AO142" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="143" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
         <v>499</v>
       </c>
@@ -25483,8 +25946,11 @@
         <f t="shared" si="29"/>
         <v>1.3096934841312509</v>
       </c>
+      <c r="AO143" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="144" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
         <v>500</v>
       </c>
@@ -25604,8 +26070,11 @@
         <f t="shared" si="29"/>
         <v>1.2649802836537249</v>
       </c>
+      <c r="AO144" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="145" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
         <v>501</v>
       </c>
@@ -25725,8 +26194,11 @@
         <f t="shared" si="29"/>
         <v>1.242648133063637</v>
       </c>
+      <c r="AO145" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="146" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
         <v>502</v>
       </c>
@@ -25846,8 +26318,11 @@
         <f t="shared" si="29"/>
         <v>0.90074899958421728</v>
       </c>
+      <c r="AO146" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="147" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
         <v>502</v>
       </c>
@@ -25967,8 +26442,11 @@
         <f t="shared" si="29"/>
         <v>0.86471997316517379</v>
       </c>
+      <c r="AO147" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="148" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
         <v>502</v>
       </c>
@@ -26088,8 +26566,11 @@
         <f t="shared" si="29"/>
         <v>0.8291908931927453</v>
       </c>
+      <c r="AO148" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="149" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
         <v>502</v>
       </c>
@@ -26209,8 +26690,11 @@
         <f t="shared" si="29"/>
         <v>0.82391222601076908</v>
       </c>
+      <c r="AO149" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="150" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
         <v>502</v>
       </c>
@@ -26330,8 +26814,11 @@
         <f t="shared" si="29"/>
         <v>1.307592918802565</v>
       </c>
+      <c r="AO150" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="151" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
         <v>502</v>
       </c>
@@ -26451,8 +26938,11 @@
         <f t="shared" si="29"/>
         <v>1.259710619839457</v>
       </c>
+      <c r="AO151" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="152" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
         <v>502</v>
       </c>
@@ -26566,8 +27056,11 @@
         <f t="shared" si="29"/>
         <v>2</v>
       </c>
+      <c r="AO152" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="153" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
         <v>502</v>
       </c>
@@ -26687,8 +27180,11 @@
         <f t="shared" si="29"/>
         <v>1.5199940748831153</v>
       </c>
+      <c r="AO153" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="154" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
         <v>502</v>
       </c>
@@ -26808,8 +27304,11 @@
         <f t="shared" si="29"/>
         <v>0.94841385595929528</v>
       </c>
+      <c r="AO154" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="155" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
         <v>503</v>
       </c>
@@ -26929,8 +27428,11 @@
         <f t="shared" si="29"/>
         <v>2.001711919813113</v>
       </c>
+      <c r="AO155" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="156" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
         <v>503</v>
       </c>
@@ -27050,8 +27552,11 @@
         <f t="shared" si="29"/>
         <v>2.7873981870831179</v>
       </c>
+      <c r="AO156" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="157" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
         <v>503</v>
       </c>
@@ -27171,8 +27676,11 @@
         <f t="shared" si="29"/>
         <v>1.8835744163813872</v>
       </c>
+      <c r="AO157" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="158" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
         <v>548</v>
       </c>
@@ -27292,8 +27800,11 @@
         <f t="shared" si="29"/>
         <v>1.3178084967631456</v>
       </c>
+      <c r="AO158" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="159" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
         <v>547</v>
       </c>
@@ -27413,8 +27924,11 @@
         <f t="shared" si="29"/>
         <v>1.3730404099510281</v>
       </c>
+      <c r="AO159" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="160" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
         <v>504</v>
       </c>
@@ -27534,8 +28048,11 @@
         <f t="shared" si="29"/>
         <v>1.3848749369337743</v>
       </c>
+      <c r="AO160" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="161" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
         <v>505</v>
       </c>
@@ -27655,8 +28172,11 @@
         <f t="shared" si="29"/>
         <v>1.3585676614027813</v>
       </c>
+      <c r="AO161" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="162" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
         <v>506</v>
       </c>
@@ -27776,8 +28296,11 @@
         <f t="shared" si="29"/>
         <v>1.372740519264412</v>
       </c>
+      <c r="AO162" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="163" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
         <v>507</v>
       </c>
@@ -27897,8 +28420,11 @@
         <f t="shared" si="29"/>
         <v>1.3209122633460484</v>
       </c>
+      <c r="AO163" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="164" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
         <v>508</v>
       </c>
@@ -28018,8 +28544,11 @@
         <f t="shared" si="29"/>
         <v>4.2857142857142856</v>
       </c>
+      <c r="AO164" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="165" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
         <v>509</v>
       </c>
@@ -28139,8 +28668,11 @@
         <f t="shared" si="29"/>
         <v>0.89768559755339483</v>
       </c>
+      <c r="AO165" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="166" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
         <v>510</v>
       </c>
@@ -28260,8 +28792,11 @@
         <f t="shared" si="29"/>
         <v>0.84488056240319498</v>
       </c>
+      <c r="AO166" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="167" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A167" s="6" t="s">
         <v>511</v>
       </c>
@@ -28381,8 +28916,11 @@
         <f t="shared" si="29"/>
         <v>0.79115858344502654</v>
       </c>
+      <c r="AO167" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="168" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A168" s="6" t="s">
         <v>512</v>
       </c>
@@ -28502,8 +29040,11 @@
         <f t="shared" si="29"/>
         <v>0.77406888933587614</v>
       </c>
+      <c r="AO168" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="169" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A169" s="6" t="s">
         <v>513</v>
       </c>
@@ -28623,8 +29164,11 @@
         <f t="shared" si="29"/>
         <v>0.95007407159306967</v>
       </c>
+      <c r="AO169" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="170" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A170" s="6" t="s">
         <v>514</v>
       </c>
@@ -28744,8 +29288,11 @@
         <f t="shared" si="29"/>
         <v>1.6504684110205614</v>
       </c>
+      <c r="AO170" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="171" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A171" s="6" t="s">
         <v>514</v>
       </c>
@@ -28865,8 +29412,11 @@
         <f t="shared" si="29"/>
         <v>1.5959766651655141</v>
       </c>
+      <c r="AO171" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="172" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A172" s="6" t="s">
         <v>514</v>
       </c>
@@ -28986,8 +29536,11 @@
         <f t="shared" si="29"/>
         <v>1.541459129098488</v>
       </c>
+      <c r="AO172" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="173" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A173" s="6" t="s">
         <v>514</v>
       </c>
@@ -29107,8 +29660,11 @@
         <f t="shared" si="29"/>
         <v>1.4870446603133847</v>
       </c>
+      <c r="AO173" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="174" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A174" s="6" t="s">
         <v>515</v>
       </c>
@@ -29228,8 +29784,11 @@
         <f t="shared" si="29"/>
         <v>1.29803634535601</v>
       </c>
+      <c r="AO174" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="175" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A175" s="6" t="s">
         <v>516</v>
       </c>
@@ -29349,8 +29908,11 @@
         <f t="shared" si="29"/>
         <v>1.2979593269679877</v>
       </c>
+      <c r="AO175" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="176" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A176" s="6" t="s">
         <v>517</v>
       </c>
@@ -29470,8 +30032,11 @@
         <f t="shared" si="29"/>
         <v>1.6263477020219728</v>
       </c>
+      <c r="AO176" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="177" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
         <v>518</v>
       </c>
@@ -29591,8 +30156,11 @@
         <f t="shared" si="29"/>
         <v>1.2592386722239013</v>
       </c>
+      <c r="AO177" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="178" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
         <v>519</v>
       </c>
@@ -29712,8 +30280,11 @@
         <f t="shared" si="29"/>
         <v>1.4641218723147973</v>
       </c>
+      <c r="AO178" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="179" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
         <v>521</v>
       </c>
@@ -29833,12 +30404,15 @@
         <f t="shared" si="29"/>
         <v>1.5931435361112869</v>
       </c>
+      <c r="AO179" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="180" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="B180" s="53" t="s">
+      <c r="B180" s="6" t="s">
         <v>734</v>
       </c>
       <c r="C180" s="36" t="s">
@@ -29954,8 +30528,11 @@
         <f t="shared" si="29"/>
         <v>1.4269848890125221</v>
       </c>
+      <c r="AO180" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="181" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
         <v>535</v>
       </c>
@@ -30075,8 +30652,11 @@
         <f t="shared" si="29"/>
         <v>1.3995973831143944</v>
       </c>
+      <c r="AO181" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="182" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A182" s="6" t="s">
         <v>522</v>
       </c>
@@ -30196,8 +30776,11 @@
         <f t="shared" si="29"/>
         <v>1.4757143571699876</v>
       </c>
+      <c r="AO182" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="183" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
         <v>522</v>
       </c>
@@ -30317,8 +30900,11 @@
         <f t="shared" si="29"/>
         <v>1.4374300869105257</v>
       </c>
+      <c r="AO183" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="184" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
         <v>522</v>
       </c>
@@ -30438,8 +31024,11 @@
         <f t="shared" si="29"/>
         <v>1.3985631033192503</v>
       </c>
+      <c r="AO184" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="185" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A185" s="6" t="s">
         <v>523</v>
       </c>
@@ -30559,8 +31148,11 @@
         <f t="shared" si="29"/>
         <v>1.3826456374022646</v>
       </c>
+      <c r="AO185" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="186" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A186" s="6" t="s">
         <v>524</v>
       </c>
@@ -30680,8 +31272,11 @@
         <f t="shared" si="29"/>
         <v>0.47357002940963111</v>
       </c>
+      <c r="AO186" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="187" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A187" s="6" t="s">
         <v>525</v>
       </c>
@@ -30801,8 +31396,11 @@
         <f t="shared" si="29"/>
         <v>1.2597354394053424</v>
       </c>
+      <c r="AO187" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="188" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
         <v>526</v>
       </c>
@@ -30922,8 +31520,11 @@
         <f t="shared" si="29"/>
         <v>1.1675517449568096</v>
       </c>
+      <c r="AO188" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="189" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
         <v>527</v>
       </c>
@@ -31043,8 +31644,11 @@
         <f t="shared" si="29"/>
         <v>1.3696411756979359</v>
       </c>
+      <c r="AO189" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="190" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
         <v>527</v>
       </c>
@@ -31164,8 +31768,11 @@
         <f t="shared" si="29"/>
         <v>1.350214188462304</v>
       </c>
+      <c r="AO190" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="191" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
         <v>528</v>
       </c>
@@ -31285,8 +31892,11 @@
         <f t="shared" si="29"/>
         <v>1.2329454023052526</v>
       </c>
+      <c r="AO191" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="192" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
         <v>528</v>
       </c>
@@ -31406,8 +32016,11 @@
         <f t="shared" si="29"/>
         <v>1.1957801977735603</v>
       </c>
+      <c r="AO192" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="193" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
         <v>529</v>
       </c>
@@ -31527,8 +32140,11 @@
         <f t="shared" si="29"/>
         <v>1.1035853568830785</v>
       </c>
+      <c r="AO193" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="194" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
         <v>529</v>
       </c>
@@ -31606,7 +32222,7 @@
         <v>39.066288080668613</v>
       </c>
       <c r="AC194" s="20">
-        <f t="shared" ref="AC194:AC237" si="33">IF(AI194=0,0,AB194/AI194)</f>
+        <f t="shared" ref="AC194:AC236" si="33">IF(AI194=0,0,AB194/AI194)</f>
         <v>0.33668194854700417</v>
       </c>
       <c r="AD194" s="21">
@@ -31641,15 +32257,18 @@
         <v>43225.410942956936</v>
       </c>
       <c r="AM194" s="2">
-        <f t="shared" ref="AM194:AM242" si="38">Q194+X194</f>
+        <f t="shared" ref="AM194:AM241" si="38">Q194+X194</f>
         <v>0.7</v>
       </c>
       <c r="AN194" s="51">
         <f t="shared" si="29"/>
         <v>1.0659650406849812</v>
       </c>
+      <c r="AO194" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="195" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
         <v>529</v>
       </c>
@@ -31769,8 +32388,11 @@
         <f t="shared" ref="AN195:AN239" si="39">AI195*AM195/(AD195+AB195)</f>
         <v>2.1875</v>
       </c>
+      <c r="AO195" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="196" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
         <v>529</v>
       </c>
@@ -31890,8 +32512,11 @@
         <f t="shared" si="39"/>
         <v>2.1875</v>
       </c>
+      <c r="AO196" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="197" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A197" s="6" t="s">
         <v>529</v>
       </c>
@@ -32011,8 +32636,11 @@
         <f t="shared" si="39"/>
         <v>2.1875</v>
       </c>
+      <c r="AO197" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="198" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
         <v>529</v>
       </c>
@@ -32132,8 +32760,11 @@
         <f t="shared" si="39"/>
         <v>2.1875</v>
       </c>
+      <c r="AO198" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="199" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
         <v>529</v>
       </c>
@@ -32253,8 +32884,11 @@
         <f t="shared" si="39"/>
         <v>2.1875</v>
       </c>
+      <c r="AO199" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="200" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
         <v>529</v>
       </c>
@@ -32374,8 +33008,11 @@
         <f t="shared" si="39"/>
         <v>2.1875</v>
       </c>
+      <c r="AO200" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="201" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
         <v>530</v>
       </c>
@@ -32494,8 +33131,11 @@
         <f t="shared" si="39"/>
         <v>1.6566885721095854</v>
       </c>
+      <c r="AO201" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="202" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
         <v>530</v>
       </c>
@@ -32614,8 +33254,11 @@
         <f t="shared" si="39"/>
         <v>1.6346161037144891</v>
       </c>
+      <c r="AO202" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="203" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
         <v>531</v>
       </c>
@@ -32734,8 +33377,11 @@
         <f t="shared" si="39"/>
         <v>1.5890770411330262</v>
       </c>
+      <c r="AO203" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="204" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
         <v>532</v>
       </c>
@@ -32855,8 +33501,11 @@
         <f t="shared" si="39"/>
         <v>1.6348488056211639</v>
       </c>
+      <c r="AO204" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="205" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
         <v>533</v>
       </c>
@@ -32976,8 +33625,11 @@
         <f t="shared" si="39"/>
         <v>1.3994784856987472</v>
       </c>
+      <c r="AO205" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="206" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A206" s="6" t="s">
         <v>533</v>
       </c>
@@ -33097,8 +33749,11 @@
         <f t="shared" si="39"/>
         <v>1.3761547970799959</v>
       </c>
+      <c r="AO206" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="207" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A207" s="6" t="s">
         <v>534</v>
       </c>
@@ -33218,8 +33873,11 @@
         <f t="shared" si="39"/>
         <v>1.2739382867033264</v>
       </c>
+      <c r="AO207" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="208" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
         <v>534</v>
       </c>
@@ -33339,8 +33997,11 @@
         <f t="shared" si="39"/>
         <v>1.2513432560545719</v>
       </c>
+      <c r="AO208" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="209" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A209" s="6" t="s">
         <v>534</v>
       </c>
@@ -33460,8 +34121,11 @@
         <f t="shared" si="39"/>
         <v>1.2287862611479596</v>
       </c>
+      <c r="AO209" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="210" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A210" s="6" t="s">
         <v>534</v>
       </c>
@@ -33581,8 +34245,11 @@
         <f t="shared" si="39"/>
         <v>1.1838391039622553</v>
       </c>
+      <c r="AO210" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="211" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
         <v>535</v>
       </c>
@@ -33702,8 +34369,11 @@
         <f t="shared" si="39"/>
         <v>1.4269474786562346</v>
       </c>
+      <c r="AO211" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="212" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
         <v>536</v>
       </c>
@@ -33823,8 +34493,11 @@
         <f t="shared" si="39"/>
         <v>1.4544075393871425</v>
       </c>
+      <c r="AO212" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="213" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A213" s="28" t="s">
         <v>579</v>
       </c>
@@ -33858,7 +34531,7 @@
       <c r="O213" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="P213" s="37"/>
+      <c r="P213" s="45"/>
       <c r="Q213" s="29">
         <v>0.7</v>
       </c>
@@ -33924,8 +34597,11 @@
         <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AO213" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="214" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A214" s="6" t="s">
         <v>537</v>
       </c>
@@ -34045,8 +34721,11 @@
         <f t="shared" si="39"/>
         <v>1.1915152802141717</v>
       </c>
+      <c r="AO214" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="215" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A215" s="6" t="s">
         <v>538</v>
       </c>
@@ -34165,8 +34844,11 @@
         <f t="shared" si="39"/>
         <v>1.3027775635825822</v>
       </c>
+      <c r="AO215" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="216" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A216" s="6" t="s">
         <v>539</v>
       </c>
@@ -34285,8 +34967,11 @@
         <f t="shared" si="39"/>
         <v>0.81407876134588997</v>
       </c>
+      <c r="AO216" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="217" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A217" s="6" t="s">
         <v>540</v>
       </c>
@@ -34405,8 +35090,11 @@
         <f t="shared" si="39"/>
         <v>1.1216996276148128</v>
       </c>
+      <c r="AO217" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="218" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A218" s="6" t="s">
         <v>541</v>
       </c>
@@ -34526,8 +35214,11 @@
         <f t="shared" si="39"/>
         <v>1.1919024331549293</v>
       </c>
+      <c r="AO218" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="219" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A219" s="6" t="s">
         <v>542</v>
       </c>
@@ -34647,8 +35338,11 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
+      <c r="AO219" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="220" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A220" s="6" t="s">
         <v>433</v>
       </c>
@@ -34768,8 +35462,11 @@
         <f t="shared" si="39"/>
         <v>1.4778743985473446</v>
       </c>
+      <c r="AO220" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="221" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A221" s="6" t="s">
         <v>433</v>
       </c>
@@ -34889,8 +35586,11 @@
         <f t="shared" si="39"/>
         <v>1.4352282729652679</v>
       </c>
+      <c r="AO221" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="222" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
         <v>543</v>
       </c>
@@ -35004,8 +35704,11 @@
         <f t="shared" si="39"/>
         <v>2.6923076923076925</v>
       </c>
+      <c r="AO222" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="223" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
         <v>544</v>
       </c>
@@ -35119,8 +35822,11 @@
         <f t="shared" si="39"/>
         <v>3.378378378378379</v>
       </c>
+      <c r="AO223" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="224" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
         <v>544</v>
       </c>
@@ -35234,8 +35940,11 @@
         <f t="shared" si="39"/>
         <v>3.378378378378379</v>
       </c>
+      <c r="AO224" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="225" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A225" s="6" t="s">
         <v>544</v>
       </c>
@@ -35349,8 +36058,11 @@
         <f t="shared" si="39"/>
         <v>3.3783783783783781</v>
       </c>
+      <c r="AO225" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="226" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A226" s="6" t="s">
         <v>544</v>
       </c>
@@ -35464,8 +36176,11 @@
         <f t="shared" si="39"/>
         <v>3.3783783783783781</v>
       </c>
+      <c r="AO226" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="227" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
         <v>544</v>
       </c>
@@ -35579,8 +36294,11 @@
         <f t="shared" si="39"/>
         <v>3.3783783783783781</v>
       </c>
+      <c r="AO227" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="228" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
         <v>544</v>
       </c>
@@ -35694,8 +36412,11 @@
         <f t="shared" si="39"/>
         <v>3.3783783783783785</v>
       </c>
+      <c r="AO228" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="229" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
         <v>544</v>
       </c>
@@ -35809,8 +36530,11 @@
         <f t="shared" si="39"/>
         <v>3.3783783783783781</v>
       </c>
+      <c r="AO229" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="230" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A230" s="6" t="s">
         <v>544</v>
       </c>
@@ -35924,8 +36648,11 @@
         <f t="shared" si="39"/>
         <v>3.3783783783783785</v>
       </c>
+      <c r="AO230" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="231" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A231" s="28" t="s">
         <v>575</v>
       </c>
@@ -36020,7 +36747,7 @@
         <v>723899.17</v>
       </c>
       <c r="AL231" s="22">
-        <f t="shared" ref="AL231:AL242" si="42">AE231*AF231</f>
+        <f t="shared" ref="AL231:AL241" si="42">AE231*AF231</f>
         <v>0</v>
       </c>
       <c r="AM231" s="2">
@@ -36031,8 +36758,11 @@
         <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AO231" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="232" spans="1:40" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:41" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A232" s="31" t="s">
         <v>576</v>
       </c>
@@ -36134,8 +36864,11 @@
         <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AO232" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="233" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
         <v>584</v>
       </c>
@@ -36169,7 +36902,7 @@
       <c r="O233" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="P233" s="37">
+      <c r="P233" s="45">
         <v>2029</v>
       </c>
       <c r="Q233" s="29">
@@ -36237,8 +36970,11 @@
         <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AO233" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="234" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A234" s="28" t="s">
         <v>577</v>
       </c>
@@ -36272,7 +37008,7 @@
       <c r="O234" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="P234" s="37"/>
+      <c r="P234" s="45"/>
       <c r="Q234" s="29">
         <v>0.8</v>
       </c>
@@ -36340,8 +37076,11 @@
         <f t="shared" si="39"/>
         <v>2.2839969947407965</v>
       </c>
+      <c r="AO234" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="235" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A235" s="28" t="s">
         <v>578</v>
       </c>
@@ -36375,7 +37114,7 @@
       <c r="O235" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P235" s="37"/>
+      <c r="P235" s="45"/>
       <c r="Q235" s="29">
         <v>0.7</v>
       </c>
@@ -36441,8 +37180,11 @@
         <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AO235" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="236" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A236" s="28" t="s">
         <v>580</v>
       </c>
@@ -36476,7 +37218,7 @@
       <c r="O236" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="P236" s="37"/>
+      <c r="P236" s="45"/>
       <c r="Q236" s="29">
         <v>0.7</v>
       </c>
@@ -36542,8 +37284,11 @@
         <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AO236" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="237" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
         <v>496</v>
       </c>
@@ -36663,8 +37408,11 @@
         <f t="shared" si="39"/>
         <v>1.1478379123898734</v>
       </c>
+      <c r="AO237" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="238" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A238" s="28" t="s">
         <v>581</v>
       </c>
@@ -36696,7 +37444,7 @@
         <v>613</v>
       </c>
       <c r="O238" s="6"/>
-      <c r="P238" s="37">
+      <c r="P238" s="45">
         <v>2026</v>
       </c>
       <c r="Q238" s="29">
@@ -36706,7 +37454,7 @@
         <v>0.2</v>
       </c>
       <c r="S238" s="40">
-        <f t="shared" ref="S238:S242" si="43">SUM(Q238:R238)</f>
+        <f t="shared" ref="S238:S244" si="43">SUM(Q238:R238)</f>
         <v>1</v>
       </c>
       <c r="T238" s="37"/>
@@ -36724,11 +37472,11 @@
         <v>0</v>
       </c>
       <c r="AC238" s="20">
-        <f t="shared" ref="AC238:AC240" si="45">IF(AI238=0,0,AB238/AI238)</f>
+        <f t="shared" ref="AC238:AC244" si="45">IF(AI238=0,0,AB238/AI238)</f>
         <v>0</v>
       </c>
       <c r="AD238" s="21">
-        <f t="shared" ref="AD238:AD240" si="46">(AE238*AF238*AG238)/10^6</f>
+        <f t="shared" ref="AD238:AD244" si="46">(AE238*AF238*AG238)/10^6</f>
         <v>53.243993000000003</v>
       </c>
       <c r="AE238" s="13">
@@ -36744,11 +37492,11 @@
         <v>540</v>
       </c>
       <c r="AI238" s="21">
-        <f t="shared" ref="AI238:AI242" si="47">(AH238*AG238*AF238)/10^6</f>
+        <f t="shared" ref="AI238:AI241" si="47">(AH238*AG238*AF238)/10^6</f>
         <v>216.0162</v>
       </c>
       <c r="AJ238" s="21">
-        <f t="shared" ref="AJ238:AJ242" si="48">AI238*Q238</f>
+        <f t="shared" ref="AJ238:AJ241" si="48">AI238*Q238</f>
         <v>172.81296</v>
       </c>
       <c r="AK238" s="30">
@@ -36766,8 +37514,11 @@
         <f t="shared" si="39"/>
         <v>3.2456799398948157</v>
       </c>
+      <c r="AO238" s="75" t="s">
+        <v>789</v>
+      </c>
     </row>
-    <row r="239" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A239" s="28" t="s">
         <v>582</v>
       </c>
@@ -36801,7 +37552,7 @@
       <c r="O239" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P239" s="37"/>
+      <c r="P239" s="45"/>
       <c r="Q239" s="47">
         <v>0.8</v>
       </c>
@@ -36867,8 +37618,11 @@
         <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="AO239" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="240" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A240" s="28" t="s">
         <v>583</v>
       </c>
@@ -36902,7 +37656,7 @@
       <c r="O240" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P240" s="6"/>
+      <c r="P240" s="77"/>
       <c r="Q240" s="47">
         <v>0.72</v>
       </c>
@@ -36968,8 +37722,11 @@
         <f>AI240*AM240/(AD240+AB240)</f>
         <v>#DIV/0!</v>
       </c>
+      <c r="AO240" s="75" t="s">
+        <v>788</v>
+      </c>
     </row>
-    <row r="241" spans="1:40" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:41" s="4" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
         <v>587</v>
       </c>
@@ -37001,7 +37758,7 @@
       <c r="O241" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P241" s="37"/>
+      <c r="P241" s="45"/>
       <c r="Q241" s="47">
         <v>0.72499999999999998</v>
       </c>
@@ -37022,9 +37779,17 @@
       <c r="AA241" s="19">
         <v>1669.242</v>
       </c>
-      <c r="AB241" s="37"/>
-      <c r="AC241" s="37"/>
-      <c r="AD241" s="37"/>
+      <c r="AB241" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC241" s="20">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AD241" s="21">
+        <f>(AE241*AF241*AG241)/10^6</f>
+        <v>196.54908</v>
+      </c>
       <c r="AE241" s="13">
         <v>240</v>
       </c>
@@ -37056,23 +37821,28 @@
         <f t="shared" si="38"/>
         <v>0.72499999999999998</v>
       </c>
-      <c r="AN241" s="51" t="e">
+      <c r="AN241" s="51">
         <f>AI241*AM241/(AD241+AB241)</f>
-        <v>#DIV/0!</v>
+        <v>1.5708333333333331</v>
+      </c>
+      <c r="AO241" s="75" t="s">
+        <v>789</v>
       </c>
     </row>
-    <row r="242" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A242" s="6" t="s">
         <v>785</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>782</v>
       </c>
-      <c r="D242" s="12"/>
-      <c r="E242" s="74"/>
-      <c r="F242" s="74"/>
-      <c r="G242" s="74"/>
-      <c r="H242" s="74"/>
+      <c r="D242" s="12">
+        <v>1</v>
+      </c>
+      <c r="E242" s="73"/>
+      <c r="F242" s="73"/>
+      <c r="G242" s="73"/>
+      <c r="H242" s="73"/>
       <c r="I242" s="37"/>
       <c r="J242" s="34" t="s">
         <v>598</v>
@@ -37092,7 +37862,7 @@
       <c r="O242" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="P242" s="37" t="s">
+      <c r="P242" s="45" t="s">
         <v>28</v>
       </c>
       <c r="Q242" s="47">
@@ -37105,19 +37875,27 @@
         <f t="shared" si="43"/>
         <v>1</v>
       </c>
-      <c r="T242" s="73"/>
-      <c r="U242" s="73"/>
-      <c r="V242" s="73"/>
-      <c r="W242" s="73"/>
-      <c r="X242" s="73"/>
-      <c r="Y242" s="73"/>
-      <c r="Z242" s="73"/>
+      <c r="T242" s="72"/>
+      <c r="U242" s="72"/>
+      <c r="V242" s="72"/>
+      <c r="W242" s="72"/>
+      <c r="X242" s="72"/>
+      <c r="Y242" s="72"/>
+      <c r="Z242" s="72"/>
       <c r="AA242" s="19">
         <v>184681</v>
       </c>
-      <c r="AB242" s="73"/>
-      <c r="AC242" s="20"/>
-      <c r="AD242" s="21"/>
+      <c r="AB242" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC242" s="20">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AD242" s="21">
+        <f>(AE242*AF242*AG242)/10^6</f>
+        <v>72.25</v>
+      </c>
       <c r="AE242" s="13">
         <v>500</v>
       </c>
@@ -37149,13 +37927,224 @@
         <f>Q242+X242</f>
         <v>0.56999999999999995</v>
       </c>
-      <c r="AN242" s="51" t="e">
+      <c r="AN242" s="51">
         <f>AI242*AM242/(AD242+AB242)</f>
+        <v>3.9899999999999998</v>
+      </c>
+      <c r="AO242" s="75" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="243" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A243" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="D243" s="12">
+        <v>1</v>
+      </c>
+      <c r="E243" s="73"/>
+      <c r="F243" s="73"/>
+      <c r="G243" s="73"/>
+      <c r="H243" s="73"/>
+      <c r="I243" s="72"/>
+      <c r="J243" s="34" t="s">
+        <v>603</v>
+      </c>
+      <c r="K243" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="L243" s="6" t="s">
+        <v>790</v>
+      </c>
+      <c r="M243" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="N243" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="O243" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P243" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q243" s="47">
+        <v>0.75</v>
+      </c>
+      <c r="R243" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="S243" s="40">
+        <f t="shared" si="43"/>
+        <v>1</v>
+      </c>
+      <c r="T243" s="72"/>
+      <c r="U243" s="72"/>
+      <c r="V243" s="72"/>
+      <c r="W243" s="72"/>
+      <c r="X243" s="72"/>
+      <c r="Y243" s="72"/>
+      <c r="Z243" s="72"/>
+      <c r="AA243" s="79">
+        <v>780000</v>
+      </c>
+      <c r="AB243" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC243" s="20">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AD243" s="21">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AE243" s="72"/>
+      <c r="AF243" s="48">
+        <v>200</v>
+      </c>
+      <c r="AG243" s="48">
+        <v>2145</v>
+      </c>
+      <c r="AH243" s="48">
+        <v>550</v>
+      </c>
+      <c r="AI243" s="49">
+        <f t="shared" ref="AI243:AI244" si="49">(AH243*AG243*AF243)/10^6</f>
+        <v>235.95</v>
+      </c>
+      <c r="AJ243" s="21">
+        <f t="shared" ref="AJ243:AJ244" si="50">AI243*Q243</f>
+        <v>176.96249999999998</v>
+      </c>
+      <c r="AK243" s="30">
+        <v>110000</v>
+      </c>
+      <c r="AL243" s="22">
+        <f t="shared" ref="AL243:AL244" si="51">AE243*AF243</f>
+        <v>0</v>
+      </c>
+      <c r="AM243" s="2">
+        <f t="shared" ref="AM243:AM244" si="52">Q243+X243</f>
+        <v>0.75</v>
+      </c>
+      <c r="AN243" s="51" t="e">
+        <f>AI243*AM243/(AD243+AB243)</f>
         <v>#DIV/0!</v>
+      </c>
+      <c r="AO243" s="76" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="244" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A244" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="D244" s="12">
+        <v>1</v>
+      </c>
+      <c r="E244" s="73"/>
+      <c r="F244" s="73"/>
+      <c r="G244" s="73"/>
+      <c r="H244" s="73"/>
+      <c r="I244" s="72"/>
+      <c r="J244" s="34" t="s">
+        <v>599</v>
+      </c>
+      <c r="K244" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="L244" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="M244" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="N244" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="O244" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P244" s="78" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q244" s="47">
+        <v>0.67</v>
+      </c>
+      <c r="R244" s="47">
+        <v>0.33</v>
+      </c>
+      <c r="S244" s="40">
+        <f t="shared" si="43"/>
+        <v>1</v>
+      </c>
+      <c r="T244" s="72"/>
+      <c r="U244" s="72"/>
+      <c r="V244" s="72"/>
+      <c r="W244" s="72"/>
+      <c r="X244" s="72"/>
+      <c r="Y244" s="72"/>
+      <c r="Z244" s="72"/>
+      <c r="AA244" s="79">
+        <v>444727</v>
+      </c>
+      <c r="AB244" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC244" s="20">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AD244" s="21">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AE244" s="72"/>
+      <c r="AF244" s="48">
+        <v>250</v>
+      </c>
+      <c r="AG244" s="48">
+        <v>720</v>
+      </c>
+      <c r="AH244" s="48">
+        <v>700</v>
+      </c>
+      <c r="AI244" s="49">
+        <f>(AH244*AG244*AF244)/10^6</f>
+        <v>126</v>
+      </c>
+      <c r="AJ244" s="21">
+        <f>AI244*Q244</f>
+        <v>84.42</v>
+      </c>
+      <c r="AK244" s="30">
+        <v>175000</v>
+      </c>
+      <c r="AL244" s="22">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="AM244" s="2">
+        <f t="shared" si="52"/>
+        <v>0.67</v>
+      </c>
+      <c r="AN244" s="51" t="e">
+        <f t="shared" ref="AN243:AN244" si="53">AI244*AM244/(AD244+AB244)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AO244" s="76" t="s">
+        <v>788</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK242" xr:uid="{9BB1E7F9-B7E0-4EE5-A96E-08F27078CA81}"/>
+  <autoFilter ref="A1:AK244" xr:uid="{9BB1E7F9-B7E0-4EE5-A96E-08F27078CA81}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C13" r:id="rId1" xr:uid="{20D620E2-00D1-4632-9A20-0409C8AFCC74}"/>
@@ -37224,17 +38213,17 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:26" x14ac:dyDescent="0.35">
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="67" t="s">
         <v>745</v>
       </c>
-      <c r="O3" s="66"/>
-      <c r="P3" s="67" t="s">
+      <c r="O3" s="65"/>
+      <c r="P3" s="66" t="s">
         <v>753</v>
       </c>
-      <c r="Q3" s="67" t="s">
+      <c r="Q3" s="66" t="s">
         <v>754</v>
       </c>
     </row>
@@ -37247,39 +38236,39 @@
         <f t="array" ref="D4:D21">_xlfn.UNIQUE(AREAS!J2:J241)</f>
         <v>PA</v>
       </c>
-      <c r="F4" s="56" t="s">
+      <c r="F4" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="56">
+      <c r="G4" s="55">
         <f>COUNTA(_xlfn.ANCHORARRAY(C4))</f>
         <v>74</v>
       </c>
-      <c r="I4" s="56" t="s">
+      <c r="I4" s="55" t="s">
         <v>747</v>
       </c>
-      <c r="J4" s="57">
+      <c r="J4" s="56">
         <f>SUM(AREAS!AG2:AG1048576)</f>
-        <v>205570.0182683983</v>
-      </c>
-      <c r="L4" s="62" t="s">
+        <v>208435.0182683983</v>
+      </c>
+      <c r="L4" s="61" t="s">
         <v>748</v>
       </c>
-      <c r="M4" s="63">
+      <c r="M4" s="62">
         <f>M5/10000</f>
-        <v>5149.951158333477</v>
-      </c>
-      <c r="O4" s="56" t="s">
+        <v>5272.4238583334763</v>
+      </c>
+      <c r="O4" s="55" t="s">
         <v>751</v>
       </c>
-      <c r="P4" s="61">
+      <c r="P4" s="60">
         <f>SUM(AREAS!AI3:AI1048576)</f>
-        <v>33052.463694610124</v>
-      </c>
-      <c r="Q4" s="61">
+        <v>33414.413694610121</v>
+      </c>
+      <c r="Q4" s="60">
         <f>SUBTOTAL(9,AREAS!AI:AI)</f>
-        <v>33089.423694610115</v>
-      </c>
-      <c r="R4" s="55"/>
+        <v>33451.373694610113</v>
+      </c>
+      <c r="R4" s="54"/>
       <c r="T4" s="3">
         <f>COUNTA(T6:T77)</f>
         <v>72</v>
@@ -37292,49 +38281,49 @@
       <c r="D5" t="str">
         <v>SP</v>
       </c>
-      <c r="F5" s="56" t="s">
+      <c r="F5" s="55" t="s">
         <v>745</v>
       </c>
-      <c r="G5" s="56">
+      <c r="G5" s="55">
         <f>COUNTA(_xlfn.ANCHORARRAY(D4))</f>
         <v>18</v>
       </c>
-      <c r="L5" s="64" t="s">
+      <c r="L5" s="63" t="s">
         <v>749</v>
       </c>
-      <c r="M5" s="65">
+      <c r="M5" s="64">
         <f>SUM(AREAS!AA2:AA1048576)</f>
-        <v>51499511.583334766</v>
-      </c>
-      <c r="O5" s="56" t="s">
+        <v>52724238.583334766</v>
+      </c>
+      <c r="O5" s="55" t="s">
         <v>752</v>
       </c>
-      <c r="P5" s="61">
+      <c r="P5" s="60">
         <f>SUM(AREAS!AJ3:AJ1048576)</f>
-        <v>20751.134361209992</v>
-      </c>
-      <c r="Q5" s="61">
+        <v>21012.516861209991</v>
+      </c>
+      <c r="Q5" s="60">
         <f>SUBTOTAL(9,AREAS!AJ:AJ)</f>
-        <v>20788.094361209991</v>
-      </c>
-      <c r="R5" s="55"/>
-      <c r="T5" s="71" t="s">
+        <v>21049.476861209991</v>
+      </c>
+      <c r="R5" s="54"/>
+      <c r="T5" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="U5" s="71" t="s">
+      <c r="U5" s="70" t="s">
         <v>756</v>
       </c>
-      <c r="V5" s="71" t="s">
+      <c r="V5" s="70" t="s">
         <v>746</v>
       </c>
-      <c r="X5" s="69" t="s">
+      <c r="X5" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="Y5" s="70">
+      <c r="Y5" s="69">
         <f>COUNTIF(AREAS!L:L,Planilha2!X5)</f>
         <v>1</v>
       </c>
-      <c r="Z5" s="70">
+      <c r="Z5" s="69">
         <f>_xlfn.XLOOKUP(X5,AREAS!L:L,AREAS!D:D,"não")</f>
         <v>0</v>
       </c>
@@ -37346,7 +38335,7 @@
       <c r="D6" t="str">
         <v>TO</v>
       </c>
-      <c r="S6" s="72" t="s">
+      <c r="S6" s="71" t="s">
         <v>175</v>
       </c>
       <c r="T6" t="s">
@@ -37360,13 +38349,13 @@
         <f>_xlfn.XLOOKUP(T6,AREAS!L:L,AREAS!D:D,"não")</f>
         <v>1</v>
       </c>
-      <c r="X6" s="69" t="s">
+      <c r="X6" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="Y6" s="70">
+      <c r="Y6" s="69">
         <v>5</v>
       </c>
-      <c r="Z6" s="70">
+      <c r="Z6" s="69">
         <v>0</v>
       </c>
     </row>
@@ -37377,17 +38366,17 @@
       <c r="D7" t="str">
         <v>BA</v>
       </c>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="58" t="s">
         <v>588</v>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="58">
         <v>0</v>
       </c>
       <c r="G7">
         <f>COUNTIF(AREAS!D:D,Planilha2!F7)</f>
         <v>8</v>
       </c>
-      <c r="S7" s="72" t="s">
+      <c r="S7" s="71" t="s">
         <v>95</v>
       </c>
       <c r="T7" t="s">
@@ -37401,14 +38390,14 @@
         <f>_xlfn.XLOOKUP(T7,AREAS!L:L,AREAS!D:D,"não")</f>
         <v>1</v>
       </c>
-      <c r="X7" s="69" t="s">
+      <c r="X7" s="68" t="s">
         <v>153</v>
       </c>
-      <c r="Y7" s="70">
+      <c r="Y7" s="69">
         <f>COUNTIF(AREAS!L:L,Planilha2!X7)</f>
         <v>2</v>
       </c>
-      <c r="Z7" s="70">
+      <c r="Z7" s="69">
         <f>_xlfn.XLOOKUP(X7,AREAS!L:L,AREAS!D:D,"não")</f>
         <v>0</v>
       </c>
@@ -37420,20 +38409,20 @@
       <c r="D8" t="str">
         <v>GO</v>
       </c>
-      <c r="E8" s="60" t="s">
+      <c r="E8" s="59" t="s">
         <v>746</v>
       </c>
-      <c r="F8" s="60">
+      <c r="F8" s="59">
         <v>1</v>
       </c>
       <c r="G8">
         <f>COUNTIF(AREAS!D:D,Planilha2!F8)</f>
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H8">
         <v>240</v>
       </c>
-      <c r="S8" s="72" t="s">
+      <c r="S8" s="71" t="s">
         <v>98</v>
       </c>
       <c r="T8" t="s">
@@ -37455,15 +38444,15 @@
       <c r="D9" t="str">
         <v>AL</v>
       </c>
-      <c r="F9" s="58" t="s">
+      <c r="F9" s="57" t="s">
         <v>750</v>
       </c>
-      <c r="G9" s="54">
+      <c r="G9" s="53">
         <f>SUM(G7:G8)</f>
-        <v>240</v>
-      </c>
-      <c r="P9" s="55"/>
-      <c r="S9" s="72" t="s">
+        <v>243</v>
+      </c>
+      <c r="P9" s="54"/>
+      <c r="S9" s="71" t="s">
         <v>103</v>
       </c>
       <c r="T9" t="s">
@@ -37485,8 +38474,8 @@
       <c r="D10" t="str">
         <v>PB</v>
       </c>
-      <c r="P10" s="55"/>
-      <c r="S10" s="72" t="s">
+      <c r="P10" s="54"/>
+      <c r="S10" s="71" t="s">
         <v>100</v>
       </c>
       <c r="T10" t="s">
@@ -37513,9 +38502,9 @@
       </c>
       <c r="G11">
         <f>G9</f>
-        <v>240</v>
-      </c>
-      <c r="S11" s="72" t="s">
+        <v>243</v>
+      </c>
+      <c r="S11" s="71" t="s">
         <v>757</v>
       </c>
       <c r="T11" t="s">
@@ -37537,7 +38526,7 @@
       <c r="D12" t="str">
         <v>CE</v>
       </c>
-      <c r="S12" s="72" t="s">
+      <c r="S12" s="71" t="s">
         <v>758</v>
       </c>
       <c r="T12" t="s">
@@ -37559,7 +38548,7 @@
       <c r="D13" t="str">
         <v>MA</v>
       </c>
-      <c r="S13" s="72" t="s">
+      <c r="S13" s="71" t="s">
         <v>90</v>
       </c>
       <c r="T13" t="s">
@@ -37581,7 +38570,7 @@
       <c r="D14" t="str">
         <v>MG</v>
       </c>
-      <c r="S14" s="72" t="s">
+      <c r="S14" s="71" t="s">
         <v>109</v>
       </c>
       <c r="T14" t="s">
@@ -37603,7 +38592,7 @@
       <c r="D15" t="str">
         <v>RJ</v>
       </c>
-      <c r="S15" s="72" t="s">
+      <c r="S15" s="71" t="s">
         <v>111</v>
       </c>
       <c r="T15" t="s">
@@ -37625,7 +38614,7 @@
       <c r="D16" t="str">
         <v>ES</v>
       </c>
-      <c r="S16" s="72" t="s">
+      <c r="S16" s="71" t="s">
         <v>113</v>
       </c>
       <c r="T16" t="s">
@@ -37647,7 +38636,7 @@
       <c r="D17" t="str">
         <v>RS</v>
       </c>
-      <c r="S17" s="72" t="s">
+      <c r="S17" s="71" t="s">
         <v>122</v>
       </c>
       <c r="T17" t="s">
@@ -37669,7 +38658,7 @@
       <c r="D18" t="str">
         <v>PR</v>
       </c>
-      <c r="S18" s="72" t="s">
+      <c r="S18" s="71" t="s">
         <v>589</v>
       </c>
       <c r="T18" t="s">
@@ -37691,7 +38680,7 @@
       <c r="D19" t="str">
         <v>AC</v>
       </c>
-      <c r="S19" s="72" t="s">
+      <c r="S19" s="71" t="s">
         <v>586</v>
       </c>
       <c r="T19" t="s">
@@ -37713,7 +38702,7 @@
       <c r="D20" t="str">
         <v>MT</v>
       </c>
-      <c r="S20" s="72" t="s">
+      <c r="S20" s="71" t="s">
         <v>91</v>
       </c>
       <c r="T20" t="s">
@@ -37735,7 +38724,7 @@
       <c r="D21" t="str">
         <v>RO</v>
       </c>
-      <c r="S21" s="72" t="s">
+      <c r="S21" s="71" t="s">
         <v>198</v>
       </c>
       <c r="T21" t="s">
@@ -37754,7 +38743,7 @@
       <c r="C22" t="str">
         <v>BARRA DOS COQUEIROS</v>
       </c>
-      <c r="S22" s="72" t="s">
+      <c r="S22" s="71" t="s">
         <v>569</v>
       </c>
       <c r="T22" t="s">
@@ -37773,7 +38762,7 @@
       <c r="C23" t="str">
         <v>CRATO</v>
       </c>
-      <c r="S23" s="72" t="s">
+      <c r="S23" s="71" t="s">
         <v>759</v>
       </c>
       <c r="T23" t="s">
@@ -37792,7 +38781,7 @@
       <c r="C24" t="str">
         <v>ITAPIPOCA</v>
       </c>
-      <c r="S24" s="72" t="s">
+      <c r="S24" s="71" t="s">
         <v>760</v>
       </c>
       <c r="T24" t="s">
@@ -37811,7 +38800,7 @@
       <c r="C25" t="str">
         <v>TAUÁ</v>
       </c>
-      <c r="S25" s="72" t="s">
+      <c r="S25" s="71" t="s">
         <v>761</v>
       </c>
       <c r="T25" t="s">
@@ -37830,7 +38819,7 @@
       <c r="C26" t="str">
         <v>BALSAS</v>
       </c>
-      <c r="S26" s="72" t="s">
+      <c r="S26" s="71" t="s">
         <v>116</v>
       </c>
       <c r="T26" t="s">
@@ -37849,7 +38838,7 @@
       <c r="C27" t="str">
         <v>MONTES CLAROS</v>
       </c>
-      <c r="S27" s="72" t="s">
+      <c r="S27" s="71" t="s">
         <v>119</v>
       </c>
       <c r="T27" t="s">
@@ -37868,7 +38857,7 @@
       <c r="C28" t="str">
         <v>ITATIAIA</v>
       </c>
-      <c r="S28" s="72" t="s">
+      <c r="S28" s="71" t="s">
         <v>762</v>
       </c>
       <c r="T28" t="s">
@@ -37887,7 +38876,7 @@
       <c r="C29" t="str">
         <v>COLATINA</v>
       </c>
-      <c r="S29" s="72" t="s">
+      <c r="S29" s="71" t="s">
         <v>763</v>
       </c>
       <c r="T29" t="s">
@@ -37906,7 +38895,7 @@
       <c r="C30" t="str">
         <v>VARGEM GRANDE</v>
       </c>
-      <c r="S30" s="72" t="s">
+      <c r="S30" s="71" t="s">
         <v>764</v>
       </c>
       <c r="T30" t="s">
@@ -37914,7 +38903,7 @@
       </c>
       <c r="U30" s="3">
         <f>COUNTIF(AREAS!L:L,Planilha2!T30)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V30" s="3">
         <f>_xlfn.XLOOKUP(T30,AREAS!L:L,AREAS!D:D,"não")</f>
@@ -37925,7 +38914,7 @@
       <c r="C31" t="str">
         <v>DUQUE DE CAXIAS</v>
       </c>
-      <c r="S31" s="72" t="s">
+      <c r="S31" s="71" t="s">
         <v>573</v>
       </c>
       <c r="T31" t="s">
@@ -37944,7 +38933,7 @@
       <c r="C32" t="str">
         <v>LUZIMANGUES</v>
       </c>
-      <c r="S32" s="72" t="s">
+      <c r="S32" s="71" t="s">
         <v>186</v>
       </c>
       <c r="T32" t="s">
@@ -37963,7 +38952,7 @@
       <c r="C33" t="str">
         <v>ITABORAÍ</v>
       </c>
-      <c r="S33" s="72" t="s">
+      <c r="S33" s="71" t="s">
         <v>180</v>
       </c>
       <c r="T33" t="s">
@@ -37982,7 +38971,7 @@
       <c r="C34" t="str">
         <v>MACAE</v>
       </c>
-      <c r="S34" s="72" t="s">
+      <c r="S34" s="71" t="s">
         <v>182</v>
       </c>
       <c r="T34" t="s">
@@ -38001,7 +38990,7 @@
       <c r="C35" t="str">
         <v>ARRAIAL DO CABO</v>
       </c>
-      <c r="S35" s="72" t="s">
+      <c r="S35" s="71" t="s">
         <v>765</v>
       </c>
       <c r="T35" t="s">
@@ -38020,7 +39009,7 @@
       <c r="C36" t="str">
         <v xml:space="preserve">PARAUAPEBAS </v>
       </c>
-      <c r="S36" s="72" t="s">
+      <c r="S36" s="71" t="s">
         <v>766</v>
       </c>
       <c r="T36" t="s">
@@ -38039,16 +39028,16 @@
       <c r="C37" t="str">
         <v xml:space="preserve">PORANGATU </v>
       </c>
-      <c r="S37" s="72" t="s">
+      <c r="S37" s="71" t="s">
         <v>196</v>
       </c>
-      <c r="T37" s="69" t="s">
+      <c r="T37" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="U37" s="70">
-        <v>1</v>
-      </c>
-      <c r="V37" s="70">
+      <c r="U37" s="69">
+        <v>1</v>
+      </c>
+      <c r="V37" s="69">
         <f>_xlfn.XLOOKUP(T37,AREAS!L:L,AREAS!D:D,"não")</f>
         <v>1</v>
       </c>
@@ -38057,7 +39046,7 @@
       <c r="C38" t="str">
         <v>LORENA</v>
       </c>
-      <c r="S38" s="72" t="s">
+      <c r="S38" s="71" t="s">
         <v>767</v>
       </c>
       <c r="T38" t="s">
@@ -38076,7 +39065,7 @@
       <c r="C39" t="str">
         <v>PRESIDENTE PRUDENTE</v>
       </c>
-      <c r="S39" s="72" t="s">
+      <c r="S39" s="71" t="s">
         <v>768</v>
       </c>
       <c r="T39" t="s">
@@ -38095,7 +39084,7 @@
       <c r="C40" t="str">
         <v>CAÇAPAVA</v>
       </c>
-      <c r="S40" s="72" t="s">
+      <c r="S40" s="71" t="s">
         <v>769</v>
       </c>
       <c r="T40" t="s">
@@ -38114,7 +39103,7 @@
       <c r="C41" t="str">
         <v>AVARÉ</v>
       </c>
-      <c r="S41" s="72" t="s">
+      <c r="S41" s="71" t="s">
         <v>57</v>
       </c>
       <c r="T41" t="s">
@@ -38133,7 +39122,7 @@
       <c r="C42" t="str">
         <v>RIO GRANDE DO SUL</v>
       </c>
-      <c r="S42" s="72" t="s">
+      <c r="S42" s="71" t="s">
         <v>29</v>
       </c>
       <c r="T42" t="s">
@@ -38152,7 +39141,7 @@
       <c r="C43" t="str">
         <v>POÇOS DE CALDAS</v>
       </c>
-      <c r="S43" s="72" t="s">
+      <c r="S43" s="71" t="s">
         <v>770</v>
       </c>
       <c r="T43" t="s">
@@ -38171,7 +39160,7 @@
       <c r="C44" t="str">
         <v>RIO DE JANEIRO</v>
       </c>
-      <c r="S44" s="72" t="s">
+      <c r="S44" s="71" t="s">
         <v>39</v>
       </c>
       <c r="T44" t="s">
@@ -38190,7 +39179,7 @@
       <c r="C45" t="str">
         <v>CABO FRIO</v>
       </c>
-      <c r="S45" s="72" t="s">
+      <c r="S45" s="71" t="s">
         <v>49</v>
       </c>
       <c r="T45" t="s">
@@ -38209,7 +39198,7 @@
       <c r="C46" t="str">
         <v>CACHOEIRA DO SUL</v>
       </c>
-      <c r="S46" s="72" t="s">
+      <c r="S46" s="71" t="s">
         <v>42</v>
       </c>
       <c r="T46" t="s">
@@ -38228,7 +39217,7 @@
       <c r="C47" t="str">
         <v>GUAÍBA</v>
       </c>
-      <c r="S47" s="72" t="s">
+      <c r="S47" s="71" t="s">
         <v>771</v>
       </c>
       <c r="T47" t="s">
@@ -38247,7 +39236,7 @@
       <c r="C48" t="str">
         <v>PORTO ALEGRE</v>
       </c>
-      <c r="S48" s="72" t="s">
+      <c r="S48" s="71" t="s">
         <v>772</v>
       </c>
       <c r="T48" t="s">
@@ -38266,7 +39255,7 @@
       <c r="C49" t="str">
         <v>SANTA CRUZ DO SUL</v>
       </c>
-      <c r="S49" s="72" t="s">
+      <c r="S49" s="71" t="s">
         <v>47</v>
       </c>
       <c r="T49" t="s">
@@ -38285,7 +39274,7 @@
       <c r="C50" t="str">
         <v>SÃO LEOPOLDO</v>
       </c>
-      <c r="S50" s="72" t="s">
+      <c r="S50" s="71" t="s">
         <v>172</v>
       </c>
       <c r="T50" t="s">
@@ -38304,7 +39293,7 @@
       <c r="C51" t="str">
         <v>CAXIAS DO SUL</v>
       </c>
-      <c r="S51" s="72" t="s">
+      <c r="S51" s="71" t="s">
         <v>173</v>
       </c>
       <c r="T51" t="s">
@@ -38323,7 +39312,7 @@
       <c r="C52" t="str">
         <v>CANELA</v>
       </c>
-      <c r="S52" s="72" t="s">
+      <c r="S52" s="71" t="s">
         <v>134</v>
       </c>
       <c r="T52" t="s">
@@ -38342,7 +39331,7 @@
       <c r="C53" t="str">
         <v>VIAMÃO</v>
       </c>
-      <c r="S53" s="72" t="s">
+      <c r="S53" s="71" t="s">
         <v>157</v>
       </c>
       <c r="T53" t="s">
@@ -38361,7 +39350,7 @@
       <c r="C54" t="str">
         <v>PELOTAS</v>
       </c>
-      <c r="S54" s="72" t="s">
+      <c r="S54" s="71" t="s">
         <v>127</v>
       </c>
       <c r="T54" t="s">
@@ -38380,7 +39369,7 @@
       <c r="C55" t="str">
         <v xml:space="preserve">UBERABA </v>
       </c>
-      <c r="S55" s="72" t="s">
+      <c r="S55" s="71" t="s">
         <v>130</v>
       </c>
       <c r="T55" t="s">
@@ -38399,7 +39388,7 @@
       <c r="C56" t="str">
         <v>VARZEA GRANDE</v>
       </c>
-      <c r="S56" s="72" t="s">
+      <c r="S56" s="71" t="s">
         <v>609</v>
       </c>
       <c r="T56" t="s">
@@ -38418,7 +39407,7 @@
       <c r="C57" t="str">
         <v>ALVORADA</v>
       </c>
-      <c r="S57" s="72" t="s">
+      <c r="S57" s="71" t="s">
         <v>773</v>
       </c>
       <c r="T57" t="s">
@@ -38437,7 +39426,7 @@
       <c r="C58" t="str">
         <v>SAPIRANGA</v>
       </c>
-      <c r="S58" s="72" t="s">
+      <c r="S58" s="71" t="s">
         <v>154</v>
       </c>
       <c r="T58" t="s">
@@ -38456,7 +39445,7 @@
       <c r="C59" t="str">
         <v>TORRES</v>
       </c>
-      <c r="S59" s="72" t="s">
+      <c r="S59" s="71" t="s">
         <v>774</v>
       </c>
       <c r="T59" t="s">
@@ -38475,7 +39464,7 @@
       <c r="C60" t="str">
         <v>GUARAPUAVA</v>
       </c>
-      <c r="S60" s="72" t="s">
+      <c r="S60" s="71" t="s">
         <v>775</v>
       </c>
       <c r="T60" t="s">
@@ -38494,7 +39483,7 @@
       <c r="C61" t="str">
         <v>VITORINO</v>
       </c>
-      <c r="S61" s="72" t="s">
+      <c r="S61" s="71" t="s">
         <v>776</v>
       </c>
       <c r="T61" t="s">
@@ -38513,7 +39502,7 @@
       <c r="C62" t="str">
         <v>RIO BRANCO</v>
       </c>
-      <c r="S62" s="72" t="s">
+      <c r="S62" s="71" t="s">
         <v>193</v>
       </c>
       <c r="T62" t="s">
@@ -38532,7 +39521,7 @@
       <c r="C63" t="str">
         <v>CÁCERES</v>
       </c>
-      <c r="S63" s="72" t="s">
+      <c r="S63" s="71" t="s">
         <v>187</v>
       </c>
       <c r="T63" t="s">
@@ -38551,7 +39540,7 @@
       <c r="C64" t="str">
         <v>TANGARÁ DA SERRA</v>
       </c>
-      <c r="S64" s="72" t="s">
+      <c r="S64" s="71" t="s">
         <v>189</v>
       </c>
       <c r="T64" t="s">
@@ -38570,7 +39559,7 @@
       <c r="C65" t="str">
         <v>CUIABÁ</v>
       </c>
-      <c r="S65" s="72" t="s">
+      <c r="S65" s="71" t="s">
         <v>565</v>
       </c>
       <c r="T65" t="s">
@@ -38589,7 +39578,7 @@
       <c r="C66" t="str">
         <v>CACOAL</v>
       </c>
-      <c r="S66" s="72" t="s">
+      <c r="S66" s="71" t="s">
         <v>191</v>
       </c>
       <c r="T66" t="s">
@@ -38608,7 +39597,7 @@
       <c r="C67" t="str">
         <v>JI-PARANÁ</v>
       </c>
-      <c r="S67" s="72" t="s">
+      <c r="S67" s="71" t="s">
         <v>169</v>
       </c>
       <c r="T67" t="s">
@@ -38627,7 +39616,7 @@
       <c r="C68" t="str">
         <v>ROLIM DE MOURA</v>
       </c>
-      <c r="S68" s="72" t="s">
+      <c r="S68" s="71" t="s">
         <v>159</v>
       </c>
       <c r="T68" t="s">
@@ -38646,7 +39635,7 @@
       <c r="C69" t="str">
         <v>ARIQUEMES</v>
       </c>
-      <c r="S69" s="72" t="s">
+      <c r="S69" s="71" t="s">
         <v>165</v>
       </c>
       <c r="T69" t="s">
@@ -38665,7 +39654,7 @@
       <c r="C70" t="str">
         <v>BELA VISTA DE GOIÁS</v>
       </c>
-      <c r="S70" s="72" t="s">
+      <c r="S70" s="71" t="s">
         <v>164</v>
       </c>
       <c r="T70" t="s">
@@ -38684,7 +39673,7 @@
       <c r="C71" t="str">
         <v>CONCEIÇÃO DO ARAGUAIA</v>
       </c>
-      <c r="S71" s="72" t="s">
+      <c r="S71" s="71" t="s">
         <v>160</v>
       </c>
       <c r="T71" t="s">
@@ -38703,7 +39692,7 @@
       <c r="C72" t="str">
         <v>GOIÂNIA</v>
       </c>
-      <c r="S72" s="72" t="s">
+      <c r="S72" s="71" t="s">
         <v>167</v>
       </c>
       <c r="T72" t="s">
@@ -38722,7 +39711,7 @@
       <c r="C73" t="str">
         <v>PORTO VELHO</v>
       </c>
-      <c r="S73" s="72" t="s">
+      <c r="S73" s="71" t="s">
         <v>161</v>
       </c>
       <c r="T73" t="s">
@@ -38741,7 +39730,7 @@
       <c r="C74" t="str">
         <v xml:space="preserve">XEREM </v>
       </c>
-      <c r="S74" s="72" t="s">
+      <c r="S74" s="71" t="s">
         <v>777</v>
       </c>
       <c r="T74" t="s">
@@ -38760,7 +39749,7 @@
       <c r="C75" t="str">
         <v>NOVO GAMA</v>
       </c>
-      <c r="S75" s="72" t="s">
+      <c r="S75" s="71" t="s">
         <v>162</v>
       </c>
       <c r="T75" t="s">
@@ -38779,7 +39768,7 @@
       <c r="C76" t="str">
         <v>CHAPADA DOS GUIMARÃES</v>
       </c>
-      <c r="S76" s="72" t="s">
+      <c r="S76" s="71" t="s">
         <v>170</v>
       </c>
       <c r="T76" t="s">
@@ -38798,7 +39787,7 @@
       <c r="C77" t="str">
         <v>CALDAS NOVAS</v>
       </c>
-      <c r="S77" s="72" t="s">
+      <c r="S77" s="71" t="s">
         <v>163</v>
       </c>
       <c r="T77" t="s">
@@ -38814,76 +39803,76 @@
       </c>
     </row>
     <row r="78" spans="3:22" x14ac:dyDescent="0.35">
-      <c r="S78" s="72" t="s">
+      <c r="S78" s="71" t="s">
         <v>171</v>
       </c>
       <c r="U78" s="3">
         <f>SUM(U6:U77)</f>
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="79" spans="3:22" x14ac:dyDescent="0.35">
-      <c r="S79" s="72" t="s">
+      <c r="S79" s="71" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="80" spans="3:22" x14ac:dyDescent="0.35">
-      <c r="S80" s="72" t="s">
+      <c r="S80" s="71" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="81" spans="19:19" x14ac:dyDescent="0.35">
-      <c r="S81" s="72" t="s">
+      <c r="S81" s="71" t="s">
         <v>778</v>
       </c>
     </row>
     <row r="82" spans="19:19" x14ac:dyDescent="0.35">
-      <c r="S82" s="72" t="s">
+      <c r="S82" s="71" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="83" spans="19:19" x14ac:dyDescent="0.35">
-      <c r="S83" s="72" t="s">
+      <c r="S83" s="71" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="84" spans="19:19" x14ac:dyDescent="0.35">
-      <c r="S84" s="72" t="s">
+      <c r="S84" s="71" t="s">
         <v>779</v>
       </c>
     </row>
     <row r="85" spans="19:19" x14ac:dyDescent="0.35">
-      <c r="S85" s="72" t="s">
+      <c r="S85" s="71" t="s">
         <v>611</v>
       </c>
     </row>
     <row r="86" spans="19:19" x14ac:dyDescent="0.35">
-      <c r="S86" s="72" t="s">
+      <c r="S86" s="71" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="87" spans="19:19" x14ac:dyDescent="0.35">
-      <c r="S87" s="72" t="s">
+      <c r="S87" s="71" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="88" spans="19:19" x14ac:dyDescent="0.35">
-      <c r="S88" s="72" t="s">
+      <c r="S88" s="71" t="s">
         <v>780</v>
       </c>
     </row>
     <row r="89" spans="19:19" x14ac:dyDescent="0.35">
-      <c r="S89" s="72" t="s">
+      <c r="S89" s="71" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="90" spans="19:19" x14ac:dyDescent="0.35">
-      <c r="S90" s="72" t="s">
+      <c r="S90" s="71" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="91" spans="19:19" x14ac:dyDescent="0.35">
-      <c r="S91" s="72" t="s">
+      <c r="S91" s="71" t="s">
         <v>781</v>
       </c>
     </row>
